--- a/manual test/Open cert/OpenCartFrontend.xlsx
+++ b/manual test/Open cert/OpenCartFrontend.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22110" windowHeight="12180" firstSheet="1" activeTab="4"/>
+    <workbookView windowWidth="25380" windowHeight="12180" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="282">
   <si>
     <t>Open Cart Frontend</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Validate the working of 'Header' options' functionality</t>
   </si>
   <si>
+    <t>Need FRS clearification</t>
+  </si>
+  <si>
     <t>TS032</t>
   </si>
   <si>
@@ -281,6 +284,9 @@
   </si>
   <si>
     <t>Validate the Application functionality for different currency' functionality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total = </t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -323,38 +329,19 @@
 Validate the working of 'Home page' functionality</t>
   </si>
   <si>
-    <t>Validate header</t>
+    <t>Validate top menu</t>
   </si>
   <si>
     <t>Open https://demo.opencart.com</t>
   </si>
   <si>
-    <t>1. Verify that header is displayed correctly</t>
+    <t>1. Verify that top menu is displayed correctly (Validate ER-1)</t>
   </si>
   <si>
     <t>No Applicable</t>
   </si>
   <si>
-    <t>Header should displayed at top of the page and contain following elements:
-Store logo
-Currency block
-Shopping Cart
-Search box
-Links
-Telephone
-My Account</t>
-  </si>
-  <si>
-    <t>TC_HP_002</t>
-  </si>
-  <si>
-    <t>Validate top menu</t>
-  </si>
-  <si>
-    <t>1. Verify that top menu is displayed correctly</t>
-  </si>
-  <si>
-    <t>Top menu should displayed at top of the page under header which contain top parent categories of products as following :
+    <t>1) Top menu should displayed at top of the page under header which contain top parent categories of products as following :
 Desktops
 Laptop &amp; Notebooks
 Components
@@ -365,90 +352,96 @@
 MP3 Players</t>
   </si>
   <si>
+    <t>TC_HP_002</t>
+  </si>
+  <si>
+    <t>Validate 'Direct back to home page' from product page</t>
+  </si>
+  <si>
+    <t>1. Select product from 'Featured products(Validate ER-1)
+2. Click store logo at top right corner on header (Validate ER-2)</t>
+  </si>
+  <si>
+    <t>1) User should redirect to product page
+2) User should redirect back to home page</t>
+  </si>
+  <si>
     <t>TC_HP_003</t>
   </si>
   <si>
-    <t>Validate 'Direct back to home page' from product page</t>
-  </si>
-  <si>
-    <t>1. Select product from 'Featured products'
-2. Click store logo at top right corner on header</t>
-  </si>
-  <si>
-    <t>User should redirect back to home page</t>
+    <t>Validate 'Direct back to home page' from shopping cart page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click 'Shopping Cart' (Validate ER-1)
+2. Click store logo at top right corner on header (Validate ER-2)
+</t>
+  </si>
+  <si>
+    <t>1) User should redirect to shopping cart page
+2) User should redirect back to home page</t>
   </si>
   <si>
     <t>TC_HP_004</t>
   </si>
   <si>
-    <t>Validate 'Direct back to home page' from shopping cart page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click 'Shopping Cart'
-2. Click store logo at top right corner on header
-</t>
+    <t>Slideshow display image</t>
+  </si>
+  <si>
+    <t>1. Verify display image (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>1) All Selected images will appear in slideshow</t>
   </si>
   <si>
     <t>TC_HP_005</t>
   </si>
   <si>
-    <t>Slideshow display image</t>
-  </si>
-  <si>
-    <t>1. Verify display image</t>
-  </si>
-  <si>
-    <t>All Selected images will appear in slideshow</t>
+    <t>Slideshow automatically change image</t>
+  </si>
+  <si>
+    <t>1. Verify display image
+2. Wait a certain amount of time (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>1) image should shift to the next one</t>
   </si>
   <si>
     <t>TC_HP_006</t>
   </si>
   <si>
-    <t>Slideshow automatically change image</t>
-  </si>
-  <si>
-    <t>1. Verify display image
-2. Wait a certain amount of time</t>
-  </si>
-  <si>
-    <t>image should shift to the next one</t>
+    <t>Slideshow manually change image</t>
+  </si>
+  <si>
+    <t>1. Verify display image (Validate ER-1)
+2. Select another dot under image (Validate ER-2)</t>
+  </si>
+  <si>
+    <t>1) image should display correctly
+2) image should shift to the selected one</t>
   </si>
   <si>
     <t>TC_HP_007</t>
   </si>
   <si>
-    <t>Slideshow manually change image</t>
-  </si>
-  <si>
-    <t>1. Verify display image
-2. Select another dot under image</t>
-  </si>
-  <si>
-    <t>image should shift to the selected one</t>
+    <t>Slideshow select product</t>
+  </si>
+  <si>
+    <t>1. Click display image (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>1) User should redirect to product page of selected product</t>
   </si>
   <si>
     <t>TC_HP_008</t>
   </si>
   <si>
-    <t>Slideshow select product</t>
-  </si>
-  <si>
-    <t>1. Click display image</t>
-  </si>
-  <si>
-    <t>User should redirect to product page of selected product</t>
-  </si>
-  <si>
-    <t>TC_HP_009</t>
-  </si>
-  <si>
     <t>Validate 'Featured products' details</t>
   </si>
   <si>
-    <t>1. Verify featured product display correctly</t>
-  </si>
-  <si>
-    <t>Featured product should display under slideshow contain following elements:
+    <t>1. Verify featured product display correctly (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>1) Featured product should display under slideshow contain following elements:
 1. Item Box
 2. Product image
 3. Product name
@@ -458,40 +451,40 @@
 7. 'Compare product' button</t>
   </si>
   <si>
+    <t>TC_HP_009</t>
+  </si>
+  <si>
+    <t>Validate 'Featured products' switch list of product</t>
+  </si>
+  <si>
+    <t>1. Click another dot under displayed featured (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>1) Featured product should shift to another set of displayed product</t>
+  </si>
+  <si>
     <t>TC_HP_010</t>
   </si>
   <si>
-    <t>Validate 'Featured products' switch list of product</t>
-  </si>
-  <si>
-    <t>1. Click another dot under displayed featured</t>
-  </si>
-  <si>
-    <t>Featured product should shift to another set of displayed product</t>
+    <t>Select product from 'Featured products'</t>
+  </si>
+  <si>
+    <t>1. Select product from 'Featured' (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Product : MacBook</t>
   </si>
   <si>
     <t>TC_HP_011</t>
   </si>
   <si>
-    <t>Select product from 'Featured products'</t>
-  </si>
-  <si>
-    <t>1. Select product from 'Featured'</t>
-  </si>
-  <si>
-    <t>Product : MacBook</t>
-  </si>
-  <si>
-    <t>TC_HP_012</t>
-  </si>
-  <si>
     <t>Validate footer</t>
   </si>
   <si>
-    <t>1. Verify that footer is displayed correctly</t>
-  </si>
-  <si>
-    <t>Footer should displayed at bottom of the page and divided into following section :
+    <t>1. Verify that footer is displayed correctly (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>1) Footer should displayed at bottom of the page and divided into following section :
 Information : About Us, Delivery Information, Privacy Policy, Term &amp; Conditions
 Customer Services : Contact Us, Returns, Site Map
 Extra : Brands, Gift Voucher, Affiliate, Specials
@@ -509,6 +502,9 @@
   </si>
   <si>
     <t>Validate header on homepage</t>
+  </si>
+  <si>
+    <t>1. Verify that header is displayed correctly</t>
   </si>
   <si>
     <t>Header should displayed at top of the page and contain following options
@@ -567,8 +563,50 @@
     <t>TC_HD_005</t>
   </si>
   <si>
-    <t>(TS013)
-Validate the working of 'Header' options</t>
+    <t>Validate store logo funtionality when in home page</t>
+  </si>
+  <si>
+    <t>1. Click store logo</t>
+  </si>
+  <si>
+    <t>Should reload the current page (home page)</t>
+  </si>
+  <si>
+    <t>TC_HD_006</t>
+  </si>
+  <si>
+    <t>Validate store logo funtionality when in product page</t>
+  </si>
+  <si>
+    <t>1. Click on selected product
+2. Click store logo</t>
+  </si>
+  <si>
+    <t>Should redirect to home page</t>
+  </si>
+  <si>
+    <t>TC_HD_007</t>
+  </si>
+  <si>
+    <t>Validate store logo funtionality when in shopping cart page</t>
+  </si>
+  <si>
+    <t>1. Click on 'Shopping Cart' button
+2. Click store logo</t>
+  </si>
+  <si>
+    <t>TC_HD_008</t>
+  </si>
+  <si>
+    <t>Validate store logo funtionality when in checkout page</t>
+  </si>
+  <si>
+    <t>1. Click 'ADD TO CART' on selected product
+2. Click 'Checkout' button on homepage header
+3. Click store logo</t>
+  </si>
+  <si>
+    <t>TC_HD_009</t>
   </si>
   <si>
     <t>Validate currency functionality</t>
@@ -581,74 +619,147 @@
     <t>Correct 2 available option should be USD($) and EUR(€)</t>
   </si>
   <si>
-    <t>TC_HD_006</t>
-  </si>
-  <si>
-    <t>(TS014)
-Validate the working of 'Header' options</t>
+    <t>TC_HD_010</t>
   </si>
   <si>
     <t>Validate telephone display</t>
   </si>
   <si>
-    <t>1.Verify company telephone number</t>
+    <t>1. Verify company telephone number</t>
   </si>
   <si>
     <t>Company telephone number should be '123456789'</t>
   </si>
   <si>
-    <t>TC_HD_007</t>
-  </si>
-  <si>
-    <t>(TS015)
-Validate the working of 'Header' options</t>
-  </si>
-  <si>
-    <t>Validate My Account button</t>
-  </si>
-  <si>
-    <t>1.Click on 'My Account' button</t>
+    <t>TC_HD_011</t>
+  </si>
+  <si>
+    <t>Validate 'My Account' button</t>
+  </si>
+  <si>
+    <t>1. Click on 'My Account' button</t>
   </si>
   <si>
     <t>Should display dropdown list 'login' and 'register'</t>
   </si>
   <si>
-    <t>TC_HD_008</t>
-  </si>
-  <si>
-    <t>(TS016)
-Validate the working of 'Header' options</t>
-  </si>
-  <si>
-    <t>Validate wish list button</t>
-  </si>
-  <si>
-    <t>TC_HD_009</t>
-  </si>
-  <si>
-    <t>(TS017)
-Validate the working of 'Header' options</t>
-  </si>
-  <si>
-    <t>TC_HD_010</t>
-  </si>
-  <si>
-    <t>(TS018)
-Validate the working of 'Header' options</t>
-  </si>
-  <si>
-    <t>TC_HD_011</t>
-  </si>
-  <si>
-    <t>(TS019)
-Validate the working of 'Header' options</t>
-  </si>
-  <si>
     <t>TC_HD_012</t>
   </si>
   <si>
-    <t>(TS020)
-Validate the working of 'Header' options</t>
+    <t>Validate 'My Account' login option</t>
+  </si>
+  <si>
+    <t>Open https://demo.opencart.com
+Click on 'My Account' button</t>
+  </si>
+  <si>
+    <t>1. Click on 'login'</t>
+  </si>
+  <si>
+    <t>Should redirect to login page</t>
+  </si>
+  <si>
+    <t>TC_HD_013</t>
+  </si>
+  <si>
+    <t>Validate 'My Account' register option</t>
+  </si>
+  <si>
+    <t>1. Click on 'register' button</t>
+  </si>
+  <si>
+    <t>Should redirect to register page</t>
+  </si>
+  <si>
+    <t>TC_HD_014</t>
+  </si>
+  <si>
+    <t>Validate 'Wish List' button (default)</t>
+  </si>
+  <si>
+    <t>1.Verify 'Wish List' button</t>
+  </si>
+  <si>
+    <t>Default dispay should have '(0)' added after Wish List which is Wish List(0)</t>
+  </si>
+  <si>
+    <t>Requirment have overlap function that is following:
+1. all these button is the link that click then go to thier own page
+2. all these button have thier own action
+Need Clearify on SRS</t>
+  </si>
+  <si>
+    <t>TC_HD_015</t>
+  </si>
+  <si>
+    <t>Validate 'Wish List' button after added item</t>
+  </si>
+  <si>
+    <t>1 .Click hearth symbol which displayed on product
+2. Verify 'Wish List' button</t>
+  </si>
+  <si>
+    <t>Product : Canon EOS 5D</t>
+  </si>
+  <si>
+    <t>Wish List' button should change to Wish List(1)</t>
+  </si>
+  <si>
+    <t>Requirment have overlap function that is following:
+1. all these button is the link that click then go to thier own page
+2. all these button have thier own action
+Need Clearify on SRS</t>
+  </si>
+  <si>
+    <t>TC_HD_016</t>
+  </si>
+  <si>
+    <t>Validate 'Wish List' button after added item (multiple)</t>
+  </si>
+  <si>
+    <t>1. Click hearth symbol which displayed on multiple product
+2. Verify 'Wish List' button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product : iPhone, MacBook, Apple Cinema 30"
+</t>
+  </si>
+  <si>
+    <t>Wish List' button should display Wish List(3)</t>
+  </si>
+  <si>
+    <t>TC_HD_017</t>
+  </si>
+  <si>
+    <t>Validate 'Wish List' button' removing item</t>
+  </si>
+  <si>
+    <t>Open https://demo.opencart.com
+Added multiple wish list item</t>
+  </si>
+  <si>
+    <t>1. Click hearth symbol which displayed on multiple product
+2. Click on 'Wish List' button
+3. Click remove button on selected item</t>
+  </si>
+  <si>
+    <t>only selected wish list item should be removed from wish list page</t>
+  </si>
+  <si>
+    <t>TC_HD_018</t>
+  </si>
+  <si>
+    <t>Validate 'Wish List' button' empty wish list</t>
+  </si>
+  <si>
+    <t>Open https://demo.opencart.com
+Added an item</t>
+  </si>
+  <si>
+    <t>Correct display should be 'Wish List is empty'</t>
+  </si>
+  <si>
+    <t>TC_HD_019</t>
   </si>
   <si>
     <t>Validate shopping cart button functionality</t>
@@ -657,14 +768,11 @@
     <t>1. Click 'Shopping Cart' button on the header</t>
   </si>
   <si>
-    <t>Should redirect user to shopping cart page</t>
-  </si>
-  <si>
-    <t>TC_HD_013</t>
-  </si>
-  <si>
-    <t>(TS021)
-Validate the working of 'Header' options</t>
+    <t>Should show shopping cart items listed and total price of the order
+,have "View Cart" or "Checkout" displayed</t>
+  </si>
+  <si>
+    <t>TC_HD_020</t>
   </si>
   <si>
     <t>Validate shopping cart (not empty)</t>
@@ -674,115 +782,96 @@
 2. Verify that shopping cart is displayed correctly</t>
   </si>
   <si>
-    <t>Correct display should displayed number of items</t>
-  </si>
-  <si>
-    <t>TC_HD_014</t>
-  </si>
-  <si>
-    <t>(TS022)
-Validate the working of 'Header' options</t>
-  </si>
-  <si>
-    <t>TC_HD_015</t>
-  </si>
-  <si>
-    <t>(TS023)
-Validate the working of 'Header' options</t>
-  </si>
-  <si>
-    <t>TC_HD_016</t>
-  </si>
-  <si>
-    <t>(TS024)
-Validate the working of 'Header' options</t>
-  </si>
-  <si>
-    <t>TC_HD_017</t>
-  </si>
-  <si>
-    <t>(TS025)
-Validate the working of 'Header' options</t>
-  </si>
-  <si>
-    <t>TC_HD_018</t>
-  </si>
-  <si>
-    <t>(TS026)
-Validate the working of 'Header' options</t>
-  </si>
-  <si>
-    <t>TC_HD_019</t>
-  </si>
-  <si>
-    <t>(TS027)
-Validate the working of 'Header' options</t>
-  </si>
-  <si>
-    <t>TC_HD_020</t>
-  </si>
-  <si>
-    <t>(TS028)
-Validate the working of 'Header' options</t>
+    <t>Product : MacBook, iPhone</t>
+  </si>
+  <si>
+    <t>Correct display should displayed each item details and total price of the order</t>
   </si>
   <si>
     <t>TC_HD_021</t>
   </si>
   <si>
-    <t>(TS029)
-Validate the working of 'Header' options</t>
+    <t>Validate shopping cart (empty)</t>
+  </si>
+  <si>
+    <t>Should display 'this cart is  currently empty'</t>
   </si>
   <si>
     <t>TC_HD_022</t>
   </si>
   <si>
-    <t>(TS030)
-Validate the working of 'Header' options</t>
+    <t>Validate shopping cart 'View Cart' button</t>
+  </si>
+  <si>
+    <t>1. Click 'Shopping Cart' button on the header
+2. Click 'View Cart' button</t>
+  </si>
+  <si>
+    <t>Should redirect to cart page</t>
   </si>
   <si>
     <t>TC_HD_023</t>
   </si>
   <si>
-    <t>(TS031)
-Validate the working of 'Header' options</t>
+    <t>Validate shopping cart 'Checkout' button</t>
+  </si>
+  <si>
+    <t>1. Click 'Shopping Cart' button on the header
+2. Click 'Checkout' button</t>
+  </si>
+  <si>
+    <t>Should redirect to checkout page</t>
   </si>
   <si>
     <t>TC_HD_024</t>
   </si>
   <si>
-    <t>(TS032)
-Validate the working of 'Header' options</t>
+    <t>Validate Link 'Wish List'</t>
+  </si>
+  <si>
+    <t>1.Click 'Wish List' button</t>
+  </si>
+  <si>
+    <t>Should redirect to wish list page</t>
   </si>
   <si>
     <t>TC_HD_025</t>
   </si>
   <si>
-    <t>(TS033)
-Validate the working of 'Header' options</t>
+    <t>Validate Link 'My Account'</t>
+  </si>
+  <si>
+    <t>1.Click 'My Account' button</t>
+  </si>
+  <si>
+    <t>Should redirect to my account page</t>
   </si>
   <si>
     <t>TC_HD_026</t>
   </si>
   <si>
-    <t>(TS034)
-Validate the working of 'Header' options</t>
+    <t>Validate Link 'Shopping Cart'</t>
+  </si>
+  <si>
+    <t>1.Click 'Shopping Cart' button</t>
+  </si>
+  <si>
+    <t>Should redirect to shopping cart page</t>
   </si>
   <si>
     <t>TC_HD_027</t>
   </si>
   <si>
-    <t>(TS035)
-Validate the working of 'Header' options</t>
-  </si>
-  <si>
-    <t>TC_HD_028</t>
-  </si>
-  <si>
-    <t>(TS036)
-Validate the working of 'Header' options</t>
+    <t>Validate Link 'Check Out'</t>
+  </si>
+  <si>
+    <t>1.Click 'Check Out' button</t>
   </si>
   <si>
     <t>Validate top menu parent</t>
+  </si>
+  <si>
+    <t>1. Verify that top menu is displayed correctly</t>
   </si>
   <si>
     <t>Only top parent catagories should visible</t>
@@ -1055,7 +1144,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1070,19 +1159,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1267,7 +1350,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1288,6 +1371,83 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1414,7 +1574,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1426,119 +1586,119 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1578,9 +1738,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1591,9 +1748,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1603,28 +1757,67 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1635,34 +1828,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
@@ -1683,7 +1852,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2219,14 +2403,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
     <col min="2" max="2" width="9.875" customWidth="1"/>
     <col min="3" max="3" width="69.75" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
+    <col min="5" max="5" width="21" style="1" customWidth="1"/>
     <col min="8" max="8" width="69.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2239,27 +2423,25 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
     </row>
     <row r="3" ht="18" spans="1:9">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="F3" s="46"/>
     </row>
     <row r="4" spans="1:9">
       <c r="B4" t="s">
@@ -2267,41 +2449,41 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="49" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:9">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="38" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="50" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:9">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="38" t="s">
         <v>14</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="50" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2312,7 +2494,7 @@
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="50" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2323,7 +2505,7 @@
       <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="50" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2334,7 +2516,7 @@
       <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="50" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2345,7 +2527,7 @@
       <c r="B12" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="50" t="s">
         <v>24</v>
       </c>
       <c r="D12" t="s">
@@ -2359,7 +2541,7 @@
       <c r="B13" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="50" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2370,7 +2552,7 @@
       <c r="B14" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="50" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2381,7 +2563,7 @@
       <c r="B15" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="50" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2392,7 +2574,7 @@
       <c r="B16" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="C16" s="50" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2403,23 +2585,23 @@
       <c r="B17" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="C17" s="50" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="18" s="40" customFormat="1" spans="1:5">
-      <c r="A18" s="40" t="s">
+    <row r="18" s="44" customFormat="1" spans="1:5">
+      <c r="A18" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="40">
-        <f>COUNTA(HomePage!A3:A9999)</f>
-        <v>12</v>
+      <c r="E18" s="51">
+        <f>COUNTA(HomePage!A3:A9998)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2429,7 +2611,7 @@
       <c r="B19" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="50" t="s">
         <v>39</v>
       </c>
     </row>
@@ -2440,7 +2622,7 @@
       <c r="B20" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="50" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2451,7 +2633,7 @@
       <c r="B21" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="50" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2462,7 +2644,7 @@
       <c r="B22" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="47" t="s">
+      <c r="C22" s="50" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2473,7 +2655,7 @@
       <c r="B23" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="50" t="s">
         <v>47</v>
       </c>
     </row>
@@ -2484,7 +2666,7 @@
       <c r="B24" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="47" t="s">
+      <c r="C24" s="50" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2495,7 +2677,7 @@
       <c r="B25" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="47" t="s">
+      <c r="C25" s="50" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2506,7 +2688,7 @@
       <c r="B26" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="50" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2517,7 +2699,7 @@
       <c r="B27" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="47" t="s">
+      <c r="C27" s="50" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2528,7 +2710,7 @@
       <c r="B28" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="47" t="s">
+      <c r="C28" s="50" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2539,7 +2721,7 @@
       <c r="B29" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="47" t="s">
+      <c r="C29" s="50" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2550,7 +2732,7 @@
       <c r="B30" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="47" t="s">
+      <c r="C30" s="50" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2561,7 +2743,7 @@
       <c r="B31" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="50" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2572,96 +2754,114 @@
       <c r="B32" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="48" t="s">
+      <c r="C32" s="52" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>66</v>
       </c>
       <c r="B33" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="48" t="s">
+      <c r="C33" s="52" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>68</v>
       </c>
       <c r="B34" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="48" t="s">
+      <c r="C34" s="52" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>70</v>
       </c>
       <c r="B35" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="48" t="s">
+      <c r="C35" s="52" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>72</v>
       </c>
       <c r="B36" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="47" t="s">
+      <c r="C36" s="50" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="37" s="41" customFormat="1" spans="1:3">
-      <c r="A37" s="41" t="s">
+    <row r="37" s="37" customFormat="1" spans="1:6">
+      <c r="A37" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="41" t="s">
+      <c r="B37" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="41" t="s">
+      <c r="C37" s="37" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="E37" s="53">
+        <v>27</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="47" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="C38" s="50" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="47" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="C39" s="50" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="47" t="s">
-        <v>81</v>
+      <c r="C40" s="50" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="54"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="55">
+        <f>SUM(E7:E40)</f>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2683,14 +2883,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
     <col min="2" max="2" width="40.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="44.5" style="8" customWidth="1"/>
     <col min="4" max="4" width="30.875" customWidth="1"/>
-    <col min="5" max="5" width="37.75" style="8" customWidth="1"/>
+    <col min="5" max="5" width="52.375" style="8" customWidth="1"/>
     <col min="6" max="6" width="21.375" customWidth="1"/>
     <col min="7" max="7" width="73.25" style="8" customWidth="1"/>
     <col min="8" max="8" width="35" customWidth="1"/>
@@ -2700,378 +2900,355 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
-      <c r="A1" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="28" t="s">
+      <c r="A1" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="B1" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="C1" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="D1" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="E1" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="F1" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="G1" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="K1" s="27" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" s="24" customFormat="1" ht="18" spans="1:11">
-      <c r="A2" s="29" t="s">
+      <c r="J1" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-    </row>
-    <row r="3" s="26" customFormat="1" ht="114" spans="1:11">
-      <c r="A3" s="32" t="s">
+      <c r="K1" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="33" t="s">
+    </row>
+    <row r="2" s="38" customFormat="1" ht="18" spans="1:11">
+      <c r="A2" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="B2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+    </row>
+    <row r="3" ht="142.5" spans="1:11">
+      <c r="A3" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="B3" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="C3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="D3" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="E3" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-    </row>
-    <row r="4" ht="142.5" spans="1:11">
-      <c r="A4" s="36" t="s">
+      <c r="F3" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="36" t="s">
+      <c r="G3" s="17" t="s">
         <v>101</v>
       </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+    </row>
+    <row r="4" ht="28.5" spans="1:11">
+      <c r="A4" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>103</v>
+      </c>
       <c r="D4" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+    </row>
+    <row r="5" ht="42.75" spans="1:11">
+      <c r="A5" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="38" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="36" t="s">
+      <c r="C5" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G4" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-    </row>
-    <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+    </row>
+    <row r="6" ht="28.5" spans="1:11">
+      <c r="A6" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="F5" s="36" t="s">
+      <c r="C6" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-    </row>
-    <row r="6" ht="57" spans="1:11">
-      <c r="A6" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+    </row>
+    <row r="7" ht="28.5" spans="1:11">
+      <c r="A7" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="F6" s="36" t="s">
+      <c r="C7" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-    </row>
-    <row r="7" ht="28.5" spans="1:11">
-      <c r="A7" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" ht="28.5" spans="1:11">
+      <c r="A8" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="F7" s="36" t="s">
+      <c r="C8" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-    </row>
-    <row r="8" ht="28.5" spans="1:11">
-      <c r="A8" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="11" t="s">
+      <c r="E8" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" ht="28.5" spans="1:11">
+      <c r="A9" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E8" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="F8" s="36" t="s">
+      <c r="C9" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G8" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-    </row>
-    <row r="9" ht="28.5" spans="1:11">
-      <c r="A9" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+    </row>
+    <row r="10" ht="114" spans="1:11">
+      <c r="A10" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E9" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="F9" s="36" t="s">
+      <c r="C10" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-    </row>
-    <row r="10" ht="28.5" spans="1:11">
-      <c r="A10" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+    </row>
+    <row r="11" ht="28.5" spans="1:11">
+      <c r="A11" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="C11" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+    </row>
+    <row r="12" ht="28.5" spans="1:11">
+      <c r="A12" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+    </row>
+    <row r="13" ht="71.25" spans="1:11">
+      <c r="A13" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-    </row>
-    <row r="11" ht="114" spans="1:11">
-      <c r="A11" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="G11" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-    </row>
-    <row r="12" ht="28.5" spans="1:11">
-      <c r="A12" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>132</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="F12" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-    </row>
-    <row r="13" ht="28.5" spans="1:11">
-      <c r="A13" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E13" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="F13" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-    </row>
-    <row r="14" ht="71.25" spans="1:11">
-      <c r="A14" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="B14" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="38" t="s">
+      <c r="E13" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" s="38" t="s">
+      <c r="F13" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="F14" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="36"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="7"/>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:11">
       <c r="B15" s="7"/>
@@ -3079,7 +3256,6 @@
     </row>
     <row r="16" spans="1:11">
       <c r="B16" s="7"/>
-      <c r="D16" s="3"/>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="7"/>
@@ -3113,9 +3289,6 @@
     </row>
     <row r="27" spans="2:2">
       <c r="B27" s="7"/>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3147,88 +3320,88 @@
   <sheetData>
     <row r="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:11">
       <c r="A2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B2" s="24"/>
+        <v>142</v>
+      </c>
+      <c r="B2" s="38"/>
       <c r="C2" s="12"/>
       <c r="E2" s="12"/>
     </row>
     <row r="3" ht="18" spans="1:11">
-      <c r="B3" s="25"/>
+      <c r="B3" s="39"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
     </row>
     <row r="4" ht="18" spans="1:11">
-      <c r="B4" s="25"/>
+      <c r="B4" s="39"/>
       <c r="D4" s="12"/>
     </row>
     <row r="5" ht="18" spans="1:11">
-      <c r="B5" s="25"/>
+      <c r="B5" s="39"/>
     </row>
     <row r="6" ht="18" spans="1:11">
-      <c r="B6" s="25"/>
+      <c r="B6" s="39"/>
     </row>
     <row r="7" ht="18" spans="1:11">
-      <c r="B7" s="25"/>
+      <c r="B7" s="39"/>
     </row>
     <row r="8" ht="18" spans="1:11">
-      <c r="B8" s="24"/>
+      <c r="B8" s="38"/>
     </row>
     <row r="9" ht="18" spans="1:11">
-      <c r="B9" s="25"/>
+      <c r="B9" s="39"/>
     </row>
     <row r="10" ht="18" spans="1:11">
-      <c r="B10" s="25"/>
+      <c r="B10" s="39"/>
     </row>
     <row r="11" ht="18" spans="1:11">
-      <c r="B11" s="25"/>
+      <c r="B11" s="39"/>
     </row>
     <row r="12" ht="18" spans="1:11">
-      <c r="B12" s="25"/>
+      <c r="B12" s="39"/>
     </row>
     <row r="13" ht="18" spans="1:11">
-      <c r="B13" s="25"/>
+      <c r="B13" s="39"/>
     </row>
     <row r="14" ht="18" spans="1:11">
-      <c r="B14" s="24"/>
+      <c r="B14" s="38"/>
     </row>
     <row r="15" ht="18" spans="1:11">
-      <c r="B15" s="24"/>
+      <c r="B15" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3239,452 +3412,870 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="14.125" customWidth="1"/>
-    <col min="3" max="3" width="32.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="30.875" customWidth="1"/>
-    <col min="5" max="5" width="38.925" style="13" customWidth="1"/>
-    <col min="6" max="6" width="17.5" customWidth="1"/>
-    <col min="7" max="7" width="58.75" customWidth="1"/>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="18.75" customWidth="1"/>
+    <col min="3" max="3" width="36.375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="30.25" customWidth="1"/>
+    <col min="5" max="5" width="36.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="69.5" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
     <col min="9" max="9" width="7.75" customWidth="1"/>
     <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
+    <col min="11" max="11" width="41.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:11">
-      <c r="A1" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="G1" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>91</v>
+      <c r="J1" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
+      <c r="A2" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" ht="114" spans="1:11">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="C3" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="D3" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+    </row>
+    <row r="4" ht="42.75" spans="1:11">
+      <c r="A4" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-    </row>
-    <row r="4" ht="57" spans="1:11">
-      <c r="A4" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="G4" s="20" t="s">
+      <c r="F4" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-    </row>
-    <row r="5" ht="57" spans="1:11">
-      <c r="A5" s="16" t="s">
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+    </row>
+    <row r="5" ht="42.75" spans="1:11">
+      <c r="A5" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="B5" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>153</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E5" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+    </row>
+    <row r="6" ht="71.25" spans="1:11">
+      <c r="A6" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-    </row>
-    <row r="6" ht="57" spans="1:11">
-      <c r="A6" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-    </row>
-    <row r="7" ht="57" spans="1:11">
-      <c r="A7" s="16" t="s">
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+    </row>
+    <row r="7" ht="42.75" spans="1:11">
+      <c r="A7" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="F7" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+    </row>
+    <row r="8" ht="42.75" spans="1:11">
+      <c r="A8" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" ht="57" spans="1:11">
-      <c r="A8" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" s="18" t="s">
+      <c r="E8" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="F8" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" s="13" t="s">
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" ht="42.75" spans="1:11">
+      <c r="A9" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="B9" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" ht="57" spans="1:11">
-      <c r="A9" s="16" t="s">
+      <c r="E9" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="F9" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+    </row>
+    <row r="10" ht="71.25" spans="1:11">
+      <c r="A10" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="B10" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" s="13" t="s">
+      <c r="D10" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E10" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F10" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+    </row>
+    <row r="11" ht="42.75" spans="1:11">
+      <c r="A11" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" ht="57" spans="1:11">
-      <c r="A10" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="B10" s="18" t="s">
+      <c r="E11" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="F11" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" ht="57" spans="1:11">
-      <c r="A11" s="16" t="s">
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+    </row>
+    <row r="12" ht="42.75" spans="1:11">
+      <c r="A12" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B12" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="12" ht="57" spans="1:11">
-      <c r="A12" s="16" t="s">
+      <c r="D12" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="F12" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="15" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="13" ht="57" spans="1:11">
-      <c r="A13" s="16" t="s">
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+    </row>
+    <row r="13" ht="42.75" spans="1:11">
+      <c r="A13" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="14" ht="57" spans="1:11">
-      <c r="A14" s="16" t="s">
+      <c r="D13" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="F13" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+    </row>
+    <row r="14" ht="42.75" spans="1:11">
+      <c r="A14" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" s="13" t="s">
+      <c r="B14" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="D14" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+    </row>
+    <row r="15" ht="42.75" spans="1:11">
+      <c r="A15" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+    </row>
+    <row r="16" ht="111" customHeight="1" spans="1:11">
+      <c r="A16" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G14" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="15" ht="57" spans="1:11">
-      <c r="A15" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="F15" t="s">
-        <v>138</v>
-      </c>
-      <c r="G15" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="16" ht="57" spans="1:11">
-      <c r="A16" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="17" ht="57" spans="1:2">
-      <c r="A17" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="B17" s="18" t="s">
+      <c r="E16" s="23" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="18" ht="57" spans="1:2">
-      <c r="A18" s="16" t="s">
+      <c r="F16" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="H16" s="21"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="26" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="19" ht="57" spans="1:2">
-      <c r="A19" s="16" t="s">
+    <row r="17" ht="111" customHeight="1" spans="1:11">
+      <c r="A17" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B17" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="23" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="20" ht="57" spans="1:2">
-      <c r="A20" s="16" t="s">
+      <c r="D17" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="F17" s="21" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="21" ht="57" spans="1:2">
-      <c r="A21" s="16" t="s">
+      <c r="G17" s="56" t="s">
         <v>205</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="H17" s="21"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="26" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="22" ht="57" spans="1:2">
-      <c r="A22" s="16" t="s">
+    <row r="18" ht="85.5" spans="1:11">
+      <c r="A18" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B18" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="23" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="23" ht="57" spans="1:2">
-      <c r="A23" s="16" t="s">
+      <c r="D18" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="F18" s="26" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="24" ht="57" spans="1:2">
-      <c r="A24" s="16" t="s">
+      <c r="G18" s="56" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="H18" s="21"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="19" ht="98" customHeight="1" spans="1:11">
+      <c r="A19" s="21" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="25" ht="57" spans="1:2">
-      <c r="A25" s="16" t="s">
+      <c r="B19" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="D19" s="28" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="26" ht="57" spans="1:2">
-      <c r="A26" s="16" t="s">
+      <c r="E19" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="F19" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="G19" s="21" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="27" ht="57" spans="1:2">
-      <c r="A27" s="16" t="s">
+      <c r="H19" s="21"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="20" ht="100" customHeight="1" spans="1:11">
+      <c r="A20" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B20" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="23" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="28" ht="57" spans="1:2">
-      <c r="A28" s="16" t="s">
+      <c r="D20" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="E20" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="G20" s="21" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="29" ht="57" spans="1:2">
-      <c r="A29" s="16" t="s">
+      <c r="H20" s="21"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="21" ht="104" customHeight="1" spans="1:11">
+      <c r="A21" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B21" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="23" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="30" ht="57" spans="1:2">
-      <c r="A30" s="16" t="s">
+      <c r="D21" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="F21" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="G21" s="26" t="s">
         <v>224</v>
       </c>
+      <c r="H21" s="21"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="22" ht="115" customHeight="1" spans="1:11">
+      <c r="A22" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="H22" s="21"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="23" ht="106" customHeight="1" spans="1:11">
+      <c r="A23" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="H23" s="21"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" ht="95" customHeight="1" spans="1:11">
+      <c r="A24" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="H24" s="21"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="25" s="12" customFormat="1" ht="125" customHeight="1" spans="1:11">
+      <c r="A25" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>239</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="H25" s="26"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="35"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+    </row>
+    <row r="27" ht="119" customHeight="1" spans="1:11">
+      <c r="A27" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="28" ht="102" customHeight="1" spans="1:11">
+      <c r="A28" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="29" ht="119" customHeight="1" spans="1:11">
+      <c r="A29" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" ht="115" customHeight="1" spans="1:11">
+      <c r="A30" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="C31"/>
+      <c r="E31"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="C32"/>
+      <c r="E32"/>
+    </row>
+    <row r="33" spans="3:5">
+      <c r="C33"/>
+      <c r="E33"/>
+    </row>
+    <row r="34" spans="3:5">
+      <c r="C34"/>
+      <c r="E34"/>
+    </row>
+    <row r="35" spans="3:5">
+      <c r="C35"/>
+      <c r="E35"/>
+    </row>
+    <row r="36" spans="3:5">
+      <c r="C36"/>
+      <c r="E36"/>
+    </row>
+    <row r="37" spans="3:5">
+      <c r="C37"/>
+      <c r="E37"/>
+    </row>
+    <row r="38" spans="3:5">
+      <c r="C38"/>
+      <c r="E38"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3713,105 +4304,105 @@
   <sheetData>
     <row r="1" ht="30" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" ht="42.75" spans="1:11">
       <c r="C2" s="8" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>102</v>
+        <v>257</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" ht="71.25" spans="1:11">
       <c r="C3" s="8" t="s">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="F3" t="s">
-        <v>229</v>
+        <v>261</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>230</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" ht="57" spans="1:11">
       <c r="C4" s="8" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="F4" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" ht="71.25" spans="1:11">
       <c r="C5" s="8" t="s">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -3841,37 +4432,37 @@
   <sheetData>
     <row r="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3923,42 +4514,42 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -3967,48 +4558,48 @@
     </row>
     <row r="3" ht="42.75" spans="1:11">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>242</v>
+        <v>274</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="G3" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" ht="42.75" spans="1:11">
       <c r="A4" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>242</v>
+        <v>274</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G4" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/manual test/Open cert/OpenCartFrontend.xlsx
+++ b/manual test/Open cert/OpenCartFrontend.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25380" windowHeight="12180" firstSheet="1"/>
+    <workbookView windowWidth="25650" windowHeight="11580" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario" sheetId="1" r:id="rId1"/>
     <sheet name="HomePage" sheetId="3" r:id="rId2"/>
-    <sheet name="Register" sheetId="5" r:id="rId3"/>
-    <sheet name="Header" sheetId="4" r:id="rId4"/>
+    <sheet name="Header" sheetId="4" r:id="rId3"/>
+    <sheet name="Register" sheetId="5" r:id="rId4"/>
     <sheet name="Top Menu" sheetId="6" r:id="rId5"/>
     <sheet name="S" sheetId="7" r:id="rId6"/>
     <sheet name="Sheet6" sheetId="8" r:id="rId7"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="249">
   <si>
     <t>Open Cart Frontend</t>
   </si>
@@ -112,9 +112,6 @@
     <t>Validate the working of 'Product compare' functionality</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>TS007</t>
   </si>
   <si>
@@ -263,9 +260,6 @@
   </si>
   <si>
     <t>Validate the working of 'Header' options' functionality</t>
-  </si>
-  <si>
-    <t>Need FRS clearification</t>
   </si>
   <si>
     <t>TS032</t>
@@ -491,9 +485,6 @@
 My Account : My Account, Order History, Wish List, Newsletter</t>
   </si>
   <si>
-    <t>Not in FRS</t>
-  </si>
-  <si>
     <t>TC_HD_001</t>
   </si>
   <si>
@@ -501,10 +492,14 @@
 Validate the working of 'Header' options</t>
   </si>
   <si>
-    <t>Validate header on homepage</t>
-  </si>
-  <si>
-    <t>1. Verify that header is displayed correctly</t>
+    <t>Validate header</t>
+  </si>
+  <si>
+    <t>Open https://demo.opencart.com
+Navigate in any page of application</t>
+  </si>
+  <si>
+    <t>1. Verify that header is displayed correctly (Validate ER-1)</t>
   </si>
   <si>
     <t>Header should displayed at top of the page and contain following options
@@ -520,352 +515,248 @@
     <t>TC_HD_002</t>
   </si>
   <si>
-    <t>Validate header on product page</t>
-  </si>
-  <si>
-    <t>1. Click on selected product
-2. Verify that header is displayed correctly</t>
-  </si>
-  <si>
-    <t>Corrected store logo should display at the top-right corner of the page</t>
+    <t xml:space="preserve">Validate store logo funtionality </t>
+  </si>
+  <si>
+    <t>1. Click store logo (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Should navigate to home page</t>
   </si>
   <si>
     <t>TC_HD_003</t>
   </si>
   <si>
-    <t>Validate header on shopping cart page</t>
-  </si>
-  <si>
-    <t>1. Click on 'Shopping Cart' button
-2. Verify that header is displayed correctly</t>
-  </si>
-  <si>
-    <t>Corrected store logo should display at the top-right corner of the shopping cart page</t>
+    <t>Validate currency functionality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click at 'Currency' on the left side of header (Validate ER-1)
+</t>
+  </si>
+  <si>
+    <t>Correct 2 available option should be USD($) and EUR(€)</t>
   </si>
   <si>
     <t>TC_HD_004</t>
   </si>
   <si>
-    <t>Validate header on shopping checkout page</t>
-  </si>
-  <si>
-    <t>1. Click 'ADD TO CART' on selected product
-2. Click 'Checkout' button on homepage header
-3. Verify that header is displayed correctly</t>
-  </si>
-  <si>
-    <t>Product : iPhone</t>
-  </si>
-  <si>
-    <t>Corrected store logo should display at the top-right corner of the checkout page</t>
+    <t>Validate telephone display</t>
+  </si>
+  <si>
+    <t>1. Verify company telephone number (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Company telephone number should be '123456789'</t>
   </si>
   <si>
     <t>TC_HD_005</t>
   </si>
   <si>
-    <t>Validate store logo funtionality when in home page</t>
-  </si>
-  <si>
-    <t>1. Click store logo</t>
-  </si>
-  <si>
-    <t>Should reload the current page (home page)</t>
+    <t>Validate 'My Account' link</t>
+  </si>
+  <si>
+    <t>1. Click 'My Account' link (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Should display dropdown list 'login' and 'register'</t>
   </si>
   <si>
     <t>TC_HD_006</t>
   </si>
   <si>
-    <t>Validate store logo funtionality when in product page</t>
-  </si>
-  <si>
-    <t>1. Click on selected product
-2. Click store logo</t>
-  </si>
-  <si>
-    <t>Should redirect to home page</t>
+    <t>Validate link 'My Account' - 'Register'</t>
+  </si>
+  <si>
+    <t>Should redirect to register page</t>
   </si>
   <si>
     <t>TC_HD_007</t>
   </si>
   <si>
-    <t>Validate store logo funtionality when in shopping cart page</t>
-  </si>
-  <si>
-    <t>1. Click on 'Shopping Cart' button
-2. Click store logo</t>
+    <t>Validate link 'My Account' - 'Login'</t>
+  </si>
+  <si>
+    <t>Should redirect to login page</t>
   </si>
   <si>
     <t>TC_HD_008</t>
   </si>
   <si>
-    <t>Validate store logo funtionality when in checkout page</t>
-  </si>
-  <si>
-    <t>1. Click 'ADD TO CART' on selected product
-2. Click 'Checkout' button on homepage header
-3. Click store logo</t>
+    <t>Validate link 'Wish List'</t>
+  </si>
+  <si>
+    <t>1. Click 'Wish List' link (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Should redirect to wish list page</t>
   </si>
   <si>
     <t>TC_HD_009</t>
   </si>
   <si>
-    <t>Validate currency functionality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click at 'Currency' on the left side of header
-</t>
-  </si>
-  <si>
-    <t>Correct 2 available option should be USD($) and EUR(€)</t>
+    <t>Validate link 'Wish List' if not logged in</t>
+  </si>
+  <si>
+    <t>1. Click hearth symbol which displayed on product
+2. Verify message (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Product : Canon EOS 5D</t>
+  </si>
+  <si>
+    <t>A message "You must login or create an account to save Canon EOS 5D to your wish list!" should appear</t>
   </si>
   <si>
     <t>TC_HD_010</t>
   </si>
   <si>
-    <t>Validate telephone display</t>
-  </si>
-  <si>
-    <t>1. Verify company telephone number</t>
-  </si>
-  <si>
-    <t>Company telephone number should be '123456789'</t>
+    <t>Validate 'Wish List' button after added an item</t>
+  </si>
+  <si>
+    <t>Open https://demo.opencart.com
+and log in</t>
+  </si>
+  <si>
+    <t>1. Click hearth symbol which displayed on product
+2. Reload page
+3. Verify 'Wish List' button (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>A 'Wish List' button should change to Wish List(1)</t>
   </si>
   <si>
     <t>TC_HD_011</t>
   </si>
   <si>
-    <t>Validate 'My Account' button</t>
-  </si>
-  <si>
-    <t>1. Click on 'My Account' button</t>
-  </si>
-  <si>
-    <t>Should display dropdown list 'login' and 'register'</t>
-  </si>
-  <si>
-    <t>TC_HD_012</t>
-  </si>
-  <si>
-    <t>Validate 'My Account' login option</t>
-  </si>
-  <si>
-    <t>Open https://demo.opencart.com
-Click on 'My Account' button</t>
-  </si>
-  <si>
-    <t>1. Click on 'login'</t>
-  </si>
-  <si>
-    <t>Should redirect to login page</t>
-  </si>
-  <si>
-    <t>TC_HD_013</t>
-  </si>
-  <si>
-    <t>Validate 'My Account' register option</t>
-  </si>
-  <si>
-    <t>1. Click on 'register' button</t>
-  </si>
-  <si>
-    <t>Should redirect to register page</t>
-  </si>
-  <si>
-    <t>TC_HD_014</t>
-  </si>
-  <si>
-    <t>Validate 'Wish List' button (default)</t>
-  </si>
-  <si>
-    <t>1.Verify 'Wish List' button</t>
-  </si>
-  <si>
-    <t>Default dispay should have '(0)' added after Wish List which is Wish List(0)</t>
-  </si>
-  <si>
-    <t>Requirment have overlap function that is following:
-1. all these button is the link that click then go to thier own page
-2. all these button have thier own action
-Need Clearify on SRS</t>
-  </si>
-  <si>
-    <t>TC_HD_015</t>
-  </si>
-  <si>
-    <t>Validate 'Wish List' button after added item</t>
-  </si>
-  <si>
-    <t>1 .Click hearth symbol which displayed on product
-2. Verify 'Wish List' button</t>
-  </si>
-  <si>
-    <t>Product : Canon EOS 5D</t>
-  </si>
-  <si>
-    <t>Wish List' button should change to Wish List(1)</t>
-  </si>
-  <si>
-    <t>Requirment have overlap function that is following:
-1. all these button is the link that click then go to thier own page
-2. all these button have thier own action
-Need Clearify on SRS</t>
-  </si>
-  <si>
-    <t>TC_HD_016</t>
-  </si>
-  <si>
-    <t>Validate 'Wish List' button after added item (multiple)</t>
+    <t>Validate 'Wish List' button after added multiple item</t>
   </si>
   <si>
     <t>1. Click hearth symbol which displayed on multiple product
-2. Verify 'Wish List' button</t>
+2. Reload page
+3. Verify 'Wish List' button (Validate ER-1)</t>
   </si>
   <si>
     <t xml:space="preserve">Product : iPhone, MacBook, Apple Cinema 30"
 </t>
   </si>
   <si>
-    <t>Wish List' button should display Wish List(3)</t>
-  </si>
-  <si>
-    <t>TC_HD_017</t>
-  </si>
-  <si>
-    <t>Validate 'Wish List' button' removing item</t>
+    <t>A 'Wish List' button should display Wish List(3)</t>
+  </si>
+  <si>
+    <t>TC_HD_012</t>
+  </si>
+  <si>
+    <t>Validate 'Wish List' button' removing an item</t>
   </si>
   <si>
     <t>Open https://demo.opencart.com
+and log in
 Added multiple wish list item</t>
   </si>
   <si>
     <t>1. Click hearth symbol which displayed on multiple product
 2. Click on 'Wish List' button
-3. Click remove button on selected item</t>
-  </si>
-  <si>
-    <t>only selected wish list item should be removed from wish list page</t>
+3. Click remove button on selected item  (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>A 'Wish List' button should reduce number in bracket by 1</t>
+  </si>
+  <si>
+    <t>TC_HD_013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate link 'Shopping Cart' </t>
+  </si>
+  <si>
+    <t>1.Click 'Shopping Cart' button (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Should redirect to shopping cart page</t>
+  </si>
+  <si>
+    <t>TC_HD_014</t>
+  </si>
+  <si>
+    <t>Validate shopping cart button (empty)</t>
+  </si>
+  <si>
+    <t>1. Click 'Shopping Cart' button on the header (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Should show message "You shoping cart is empty!"</t>
+  </si>
+  <si>
+    <t>TC_HD_015</t>
+  </si>
+  <si>
+    <t>Validate shopping cart button after add item(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open https://demo.opencart.com
+log in and added item(s) </t>
+  </si>
+  <si>
+    <t>Should show item details of every item in cart,total cost and button to check out</t>
+  </si>
+  <si>
+    <t>TC_HD_016</t>
+  </si>
+  <si>
+    <t>Validate shopping cart 'View Cart' button</t>
+  </si>
+  <si>
+    <t>1. Click 'Shopping Cart' button on the header
+2. Click 'View Cart' button (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Should redirect to cart page</t>
+  </si>
+  <si>
+    <t>TC_HD_017</t>
+  </si>
+  <si>
+    <t>Validate link 'Check Out'</t>
+  </si>
+  <si>
+    <t>1. Click 'Check Out' button (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Should redirect to checkout page</t>
   </si>
   <si>
     <t>TC_HD_018</t>
   </si>
   <si>
-    <t>Validate 'Wish List' button' empty wish list</t>
-  </si>
-  <si>
-    <t>Open https://demo.opencart.com
-Added an item</t>
-  </si>
-  <si>
-    <t>Correct display should be 'Wish List is empty'</t>
+    <t>Validate search box</t>
+  </si>
+  <si>
+    <t>1. Input text into search box
+2. Click Search button (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>"Iphone"</t>
+  </si>
+  <si>
+    <t>Should redirect to search result page</t>
   </si>
   <si>
     <t>TC_HD_019</t>
   </si>
   <si>
-    <t>Validate shopping cart button functionality</t>
-  </si>
-  <si>
-    <t>1. Click 'Shopping Cart' button on the header</t>
-  </si>
-  <si>
-    <t>Should show shopping cart items listed and total price of the order
-,have "View Cart" or "Checkout" displayed</t>
-  </si>
-  <si>
-    <t>TC_HD_020</t>
-  </si>
-  <si>
-    <t>Validate shopping cart (not empty)</t>
-  </si>
-  <si>
-    <t>1. Click 'ADD TO CART' on selected product
-2. Verify that shopping cart is displayed correctly</t>
-  </si>
-  <si>
-    <t>Product : MacBook, iPhone</t>
-  </si>
-  <si>
-    <t>Correct display should displayed each item details and total price of the order</t>
-  </si>
-  <si>
-    <t>TC_HD_021</t>
-  </si>
-  <si>
-    <t>Validate shopping cart (empty)</t>
-  </si>
-  <si>
-    <t>Should display 'this cart is  currently empty'</t>
-  </si>
-  <si>
-    <t>TC_HD_022</t>
-  </si>
-  <si>
-    <t>Validate shopping cart 'View Cart' button</t>
-  </si>
-  <si>
-    <t>1. Click 'Shopping Cart' button on the header
-2. Click 'View Cart' button</t>
-  </si>
-  <si>
-    <t>Should redirect to cart page</t>
-  </si>
-  <si>
-    <t>TC_HD_023</t>
-  </si>
-  <si>
-    <t>Validate shopping cart 'Checkout' button</t>
-  </si>
-  <si>
-    <t>1. Click 'Shopping Cart' button on the header
-2. Click 'Checkout' button</t>
-  </si>
-  <si>
-    <t>Should redirect to checkout page</t>
-  </si>
-  <si>
-    <t>TC_HD_024</t>
-  </si>
-  <si>
-    <t>Validate Link 'Wish List'</t>
-  </si>
-  <si>
-    <t>1.Click 'Wish List' button</t>
-  </si>
-  <si>
-    <t>Should redirect to wish list page</t>
-  </si>
-  <si>
-    <t>TC_HD_025</t>
-  </si>
-  <si>
-    <t>Validate Link 'My Account'</t>
-  </si>
-  <si>
-    <t>1.Click 'My Account' button</t>
-  </si>
-  <si>
-    <t>Should redirect to my account page</t>
-  </si>
-  <si>
-    <t>TC_HD_026</t>
-  </si>
-  <si>
-    <t>Validate Link 'Shopping Cart'</t>
-  </si>
-  <si>
-    <t>1.Click 'Shopping Cart' button</t>
-  </si>
-  <si>
-    <t>Should redirect to shopping cart page</t>
-  </si>
-  <si>
-    <t>TC_HD_027</t>
-  </si>
-  <si>
-    <t>Validate Link 'Check Out'</t>
-  </si>
-  <si>
-    <t>1.Click 'Check Out' button</t>
+    <t>Validate search box - too many characters</t>
+  </si>
+  <si>
+    <t>a text that has over a limit characters</t>
+  </si>
+  <si>
+    <t>Should show error message "you exeed the character limit"</t>
+  </si>
+  <si>
+    <t>do not show error message and proceed with data.
+sometimes cause error 522</t>
+  </si>
+  <si>
+    <t>Not in FRS</t>
   </si>
   <si>
     <t>Validate top menu parent</t>
@@ -961,7 +852,7 @@
     <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;฿&quot;* #,##0_-;\-&quot;฿&quot;* #,##0_-;_-&quot;฿&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1019,6 +910,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="TH Sarabun PSK"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="TH Sarabun PSK"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1144,7 +1042,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1154,12 +1052,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1350,7 +1242,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1368,74 +1260,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1574,10 +1398,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1586,119 +1407,122 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1738,6 +1562,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1748,75 +1587,90 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
@@ -1828,12 +1682,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1852,23 +1706,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" quotePrefix="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2423,25 +2280,25 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
     </row>
     <row r="3" ht="18" spans="1:9">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="F3" s="46"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="F3" s="56"/>
     </row>
     <row r="4" spans="1:9">
       <c r="B4" t="s">
@@ -2449,41 +2306,41 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="59" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:9">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="13" t="s">
         <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="60" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:9">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="13" t="s">
         <v>14</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="60" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2494,7 +2351,7 @@
       <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="60" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2505,7 +2362,7 @@
       <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="60" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2516,7 +2373,7 @@
       <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="60" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2527,341 +2384,338 @@
       <c r="B12" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="60" t="s">
         <v>24</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="50" t="s">
-        <v>27</v>
+      <c r="C13" s="60" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="50" t="s">
-        <v>29</v>
+      <c r="C14" s="60" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="50" t="s">
-        <v>31</v>
+      <c r="C15" s="60" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="50" t="s">
-        <v>33</v>
+      <c r="C16" s="60" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="60" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:5">
+      <c r="A18" s="61" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" s="44" customFormat="1" spans="1:5">
-      <c r="A18" s="44" t="s">
+      <c r="B18" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="51">
+      <c r="D18" s="62"/>
+      <c r="E18" s="63">
         <f>COUNTA(HomePage!A3:A9998)</f>
         <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="50" t="s">
-        <v>39</v>
+      <c r="C19" s="60" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="50" t="s">
-        <v>41</v>
+      <c r="C20" s="60" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="50" t="s">
-        <v>43</v>
+      <c r="C21" s="60" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="50" t="s">
-        <v>45</v>
+      <c r="C22" s="60" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="50" t="s">
-        <v>47</v>
+      <c r="C23" s="60" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="50" t="s">
-        <v>49</v>
+      <c r="C24" s="60" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="50" t="s">
-        <v>51</v>
+      <c r="C25" s="60" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="50" t="s">
-        <v>53</v>
+      <c r="C26" s="60" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="50" t="s">
-        <v>55</v>
+      <c r="C27" s="60" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="50" t="s">
-        <v>57</v>
+      <c r="C28" s="60" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="50" t="s">
-        <v>59</v>
+      <c r="C29" s="60" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="50" t="s">
-        <v>61</v>
+      <c r="C30" s="60" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="50" t="s">
-        <v>63</v>
+      <c r="C31" s="60" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="52" t="s">
+      <c r="C32" s="64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
-        <v>66</v>
       </c>
       <c r="B33" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="52" t="s">
+      <c r="C33" s="64" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
-        <v>68</v>
       </c>
       <c r="B34" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="52" t="s">
+      <c r="C34" s="64" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
-        <v>70</v>
       </c>
       <c r="B35" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="52" t="s">
+      <c r="C35" s="64" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
-        <v>72</v>
       </c>
       <c r="B36" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="50" t="s">
+      <c r="C36" s="60" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:5">
+      <c r="A37" s="65" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="37" s="37" customFormat="1" spans="1:6">
-      <c r="A37" s="37" t="s">
+      <c r="B37" s="65" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C37" s="37" t="s">
+      <c r="D37" s="65"/>
+      <c r="E37" s="63">
+        <f>COUNTA(Header!A3:A133)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
         <v>75</v>
-      </c>
-      <c r="E37" s="53">
-        <v>27</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
-        <v>77</v>
       </c>
       <c r="B38" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="50" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C38" s="60" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="50" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="C39" s="60" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="50" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="54"/>
-      <c r="B41" s="54"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54" t="s">
-        <v>83</v>
-      </c>
-      <c r="E41" s="55">
+      <c r="C40" s="60" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="66"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="67">
         <f>SUM(E7:E40)</f>
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2900,351 +2754,351 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="D1" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="E1" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="F1" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="G1" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="H1" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="I1" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="K1" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="I1" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="13" t="s">
+    </row>
+    <row r="2" s="13" customFormat="1" ht="18" spans="1:11">
+      <c r="A2" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+    </row>
+    <row r="3" ht="142.5" spans="1:11">
+      <c r="A3" s="20" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="2" s="38" customFormat="1" ht="18" spans="1:11">
-      <c r="A2" s="40" t="s">
+      <c r="B3" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-    </row>
-    <row r="3" ht="142.5" spans="1:11">
-      <c r="A3" s="15" t="s">
+      <c r="C3" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="D3" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="E3" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="F3" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="G3" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+    </row>
+    <row r="4" ht="28.5" spans="1:11">
+      <c r="A4" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="B4" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-    </row>
-    <row r="4" ht="28.5" spans="1:11">
-      <c r="A4" s="15" t="s">
+      <c r="D4" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="F4" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+    </row>
+    <row r="5" ht="42.75" spans="1:11">
+      <c r="A5" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="E5" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-    </row>
-    <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" s="16" t="s">
+      <c r="G5" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+    </row>
+    <row r="6" ht="28.5" spans="1:11">
+      <c r="A6" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="11" t="s">
+      <c r="E6" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-    </row>
-    <row r="6" ht="28.5" spans="1:11">
-      <c r="A6" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="16" t="s">
+      <c r="G6" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+    </row>
+    <row r="7" ht="28.5" spans="1:11">
+      <c r="A7" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" s="11" t="s">
+      <c r="E7" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-    </row>
-    <row r="7" ht="28.5" spans="1:11">
-      <c r="A7" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" s="16" t="s">
+      <c r="G7" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+    </row>
+    <row r="8" ht="28.5" spans="1:11">
+      <c r="A8" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="E8" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-    </row>
-    <row r="8" ht="28.5" spans="1:11">
-      <c r="A8" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="G8" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+    </row>
+    <row r="9" ht="28.5" spans="1:11">
+      <c r="A9" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="11" t="s">
+      <c r="E9" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-    </row>
-    <row r="9" ht="28.5" spans="1:11">
-      <c r="A9" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B9" s="16" t="s">
+      <c r="G9" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+    </row>
+    <row r="10" ht="114" spans="1:11">
+      <c r="A10" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="E10" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G10" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+    </row>
+    <row r="11" ht="28.5" spans="1:11">
+      <c r="A11" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+    </row>
+    <row r="12" ht="28.5" spans="1:11">
+      <c r="A12" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+    </row>
+    <row r="13" ht="71.25" spans="1:11">
+      <c r="A13" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="F13" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-    </row>
-    <row r="10" ht="114" spans="1:11">
-      <c r="A10" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-    </row>
-    <row r="11" ht="28.5" spans="1:11">
-      <c r="A11" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-    </row>
-    <row r="12" ht="28.5" spans="1:11">
-      <c r="A12" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-    </row>
-    <row r="13" ht="71.25" spans="1:11">
-      <c r="A13" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="17" t="s">
+      <c r="G13" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
     </row>
     <row r="14" spans="1:11">
       <c r="B14" s="7"/>
@@ -3300,6 +3154,708 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="18.75" customWidth="1"/>
+    <col min="3" max="3" width="52.25" style="3" customWidth="1"/>
+    <col min="4" max="4" width="38.3833333333333" customWidth="1"/>
+    <col min="5" max="5" width="53.025" style="3" customWidth="1"/>
+    <col min="6" max="6" width="24.875" style="15" customWidth="1"/>
+    <col min="7" max="7" width="72.85" style="16" customWidth="1"/>
+    <col min="8" max="8" width="19.2916666666667" style="17" customWidth="1"/>
+    <col min="9" max="9" width="7.75" customWidth="1"/>
+    <col min="10" max="10" width="7.125" customWidth="1"/>
+    <col min="11" max="11" width="41.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" spans="1:11">
+      <c r="A1" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+    </row>
+    <row r="3" ht="114" spans="1:11">
+      <c r="A3" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+    </row>
+    <row r="4" ht="42.75" spans="1:11">
+      <c r="A4" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="H4" s="23"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+    </row>
+    <row r="5" ht="42.75" spans="1:11">
+      <c r="A5" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="H5" s="23"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+    </row>
+    <row r="6" ht="42.75" spans="1:11">
+      <c r="A6" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="H6" s="23"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+    </row>
+    <row r="7" ht="42.75" spans="1:11">
+      <c r="A7" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="H7" s="23"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+    </row>
+    <row r="8" ht="42.75" spans="1:11">
+      <c r="A8" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="H8" s="34"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="36"/>
+    </row>
+    <row r="9" ht="42.75" spans="1:11">
+      <c r="A9" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="H9" s="38"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+    </row>
+    <row r="10" ht="42.75" spans="1:11">
+      <c r="A10" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="H10" s="34"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="36"/>
+    </row>
+    <row r="11" ht="42.75" spans="1:11">
+      <c r="A11" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>175</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="H11" s="34"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="36"/>
+    </row>
+    <row r="12" ht="42.75" spans="1:11">
+      <c r="A12" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>175</v>
+      </c>
+      <c r="G12" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="H12" s="34"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="36"/>
+    </row>
+    <row r="13" ht="42.75" spans="1:11">
+      <c r="A13" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="H13" s="34"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="36"/>
+    </row>
+    <row r="14" ht="42.75" spans="1:11">
+      <c r="A14" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="F14" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="H14" s="34"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="36"/>
+    </row>
+    <row r="15" ht="42.75" spans="1:11">
+      <c r="A15" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="H15" s="34"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="36"/>
+    </row>
+    <row r="16" ht="42.75" spans="1:11">
+      <c r="A16" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="H16" s="34"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="36"/>
+    </row>
+    <row r="17" ht="42.75" spans="1:11">
+      <c r="A17" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="H17" s="34"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="36"/>
+    </row>
+    <row r="18" ht="42.75" spans="1:11">
+      <c r="A18" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="F18" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="H18" s="34"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="36"/>
+    </row>
+    <row r="19" s="12" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A19" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="F19" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="H19" s="34"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="36"/>
+    </row>
+    <row r="20" s="12" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A20" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="G20" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="H20" s="36"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="36"/>
+    </row>
+    <row r="21" customFormat="1" ht="71.25" spans="1:11">
+      <c r="A21" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="H21" s="48" t="s">
+        <v>221</v>
+      </c>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+    </row>
+    <row r="33" spans="3:8">
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+    </row>
+    <row r="34" spans="3:8">
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+    </row>
+    <row r="35" spans="3:8">
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K15"/>
@@ -3320,962 +3876,88 @@
   <sheetData>
     <row r="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:11">
       <c r="A2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2" s="38"/>
+        <v>222</v>
+      </c>
+      <c r="B2" s="13"/>
       <c r="C2" s="12"/>
       <c r="E2" s="12"/>
     </row>
     <row r="3" ht="18" spans="1:11">
-      <c r="B3" s="39"/>
+      <c r="B3" s="14"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
     </row>
     <row r="4" ht="18" spans="1:11">
-      <c r="B4" s="39"/>
+      <c r="B4" s="14"/>
       <c r="D4" s="12"/>
     </row>
     <row r="5" ht="18" spans="1:11">
-      <c r="B5" s="39"/>
+      <c r="B5" s="14"/>
     </row>
     <row r="6" ht="18" spans="1:11">
-      <c r="B6" s="39"/>
+      <c r="B6" s="14"/>
     </row>
     <row r="7" ht="18" spans="1:11">
-      <c r="B7" s="39"/>
+      <c r="B7" s="14"/>
     </row>
     <row r="8" ht="18" spans="1:11">
-      <c r="B8" s="38"/>
+      <c r="B8" s="13"/>
     </row>
     <row r="9" ht="18" spans="1:11">
-      <c r="B9" s="39"/>
+      <c r="B9" s="14"/>
     </row>
     <row r="10" ht="18" spans="1:11">
-      <c r="B10" s="39"/>
+      <c r="B10" s="14"/>
     </row>
     <row r="11" ht="18" spans="1:11">
-      <c r="B11" s="39"/>
+      <c r="B11" s="14"/>
     </row>
     <row r="12" ht="18" spans="1:11">
-      <c r="B12" s="39"/>
+      <c r="B12" s="14"/>
     </row>
     <row r="13" ht="18" spans="1:11">
-      <c r="B13" s="39"/>
+      <c r="B13" s="14"/>
     </row>
     <row r="14" ht="18" spans="1:11">
-      <c r="B14" s="38"/>
+      <c r="B14" s="13"/>
     </row>
     <row r="15" ht="18" spans="1:11">
-      <c r="B15" s="38"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="11.625" customWidth="1"/>
-    <col min="2" max="2" width="18.75" customWidth="1"/>
-    <col min="3" max="3" width="36.375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="30.25" customWidth="1"/>
-    <col min="5" max="5" width="36.625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
-    <col min="7" max="7" width="69.5" customWidth="1"/>
-    <col min="8" max="8" width="13.375" customWidth="1"/>
-    <col min="9" max="9" width="7.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="11" width="41.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" spans="1:11">
-      <c r="A1" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-    </row>
-    <row r="3" ht="114" spans="1:11">
-      <c r="A3" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-    </row>
-    <row r="4" ht="42.75" spans="1:11">
-      <c r="A4" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-    </row>
-    <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-    </row>
-    <row r="6" ht="71.25" spans="1:11">
-      <c r="A6" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-    </row>
-    <row r="7" ht="42.75" spans="1:11">
-      <c r="A7" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-    </row>
-    <row r="8" ht="42.75" spans="1:11">
-      <c r="A8" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-    </row>
-    <row r="9" ht="42.75" spans="1:11">
-      <c r="A9" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-    </row>
-    <row r="10" ht="71.25" spans="1:11">
-      <c r="A10" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-    </row>
-    <row r="11" ht="42.75" spans="1:11">
-      <c r="A11" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-    </row>
-    <row r="12" ht="42.75" spans="1:11">
-      <c r="A12" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-    </row>
-    <row r="13" ht="42.75" spans="1:11">
-      <c r="A13" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-    </row>
-    <row r="14" ht="42.75" spans="1:11">
-      <c r="A14" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-    </row>
-    <row r="15" ht="42.75" spans="1:11">
-      <c r="A15" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-    </row>
-    <row r="16" ht="111" customHeight="1" spans="1:11">
-      <c r="A16" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="26" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" ht="111" customHeight="1" spans="1:11">
-      <c r="A17" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="G17" s="56" t="s">
-        <v>205</v>
-      </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="18" ht="85.5" spans="1:11">
-      <c r="A18" s="21" t="s">
-        <v>207</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="G18" s="56" t="s">
-        <v>211</v>
-      </c>
-      <c r="H18" s="21"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" ht="98" customHeight="1" spans="1:11">
-      <c r="A19" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="E19" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="H19" s="21"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="20" ht="100" customHeight="1" spans="1:11">
-      <c r="A20" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="H20" s="21"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="21" ht="104" customHeight="1" spans="1:11">
-      <c r="A21" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="G21" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="H21" s="21"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="22" ht="115" customHeight="1" spans="1:11">
-      <c r="A22" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E22" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="H22" s="21"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="23" ht="106" customHeight="1" spans="1:11">
-      <c r="A23" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="G23" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="H23" s="21"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="24" ht="95" customHeight="1" spans="1:11">
-      <c r="A24" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>235</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>236</v>
-      </c>
-      <c r="H24" s="21"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="25" s="12" customFormat="1" ht="125" customHeight="1" spans="1:11">
-      <c r="A25" s="26" t="s">
-        <v>237</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="D25" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>239</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="G25" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="H25" s="26"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="35"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="37"/>
-    </row>
-    <row r="27" ht="119" customHeight="1" spans="1:11">
-      <c r="A27" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E27" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="F27" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="G27" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="28" ht="102" customHeight="1" spans="1:11">
-      <c r="A28" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="F28" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="G28" s="21" t="s">
-        <v>248</v>
-      </c>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="29" ht="119" customHeight="1" spans="1:11">
-      <c r="A29" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="F29" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="30" ht="115" customHeight="1" spans="1:11">
-      <c r="A30" s="21" t="s">
-        <v>253</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="D30" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="F30" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="G30" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="C31"/>
-      <c r="E31"/>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="C32"/>
-      <c r="E32"/>
-    </row>
-    <row r="33" spans="3:5">
-      <c r="C33"/>
-      <c r="E33"/>
-    </row>
-    <row r="34" spans="3:5">
-      <c r="C34"/>
-      <c r="E34"/>
-    </row>
-    <row r="35" spans="3:5">
-      <c r="C35"/>
-      <c r="E35"/>
-    </row>
-    <row r="36" spans="3:5">
-      <c r="C36"/>
-      <c r="E36"/>
-    </row>
-    <row r="37" spans="3:5">
-      <c r="C37"/>
-      <c r="E37"/>
-    </row>
-    <row r="38" spans="3:5">
-      <c r="C38"/>
-      <c r="E38"/>
+      <c r="B15" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4304,105 +3986,105 @@
   <sheetData>
     <row r="1" ht="30" spans="1:11">
       <c r="A1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" ht="42.75" spans="1:11">
       <c r="C2" s="8" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="D2" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="F2" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="F2" t="s">
-        <v>100</v>
-      </c>
       <c r="G2" s="12" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" ht="71.25" spans="1:11">
       <c r="C3" s="8" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="F3" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" ht="57" spans="1:11">
       <c r="C4" s="8" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F4" t="s">
-        <v>265</v>
+        <v>232</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" ht="71.25" spans="1:11">
       <c r="C5" s="8" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -4432,37 +4114,37 @@
   <sheetData>
     <row r="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -4514,42 +4196,42 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -4558,48 +4240,48 @@
     </row>
     <row r="3" ht="42.75" spans="1:11">
       <c r="A3" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="G3" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" ht="42.75" spans="1:11">
       <c r="A4" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>279</v>
+        <v>246</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>280</v>
+        <v>247</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G4" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/manual test/Open cert/OpenCartFrontend.xlsx
+++ b/manual test/Open cert/OpenCartFrontend.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25650" windowHeight="11580" firstSheet="1"/>
+    <workbookView windowWidth="25275" windowHeight="11580" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario" sheetId="1" r:id="rId1"/>
     <sheet name="HomePage" sheetId="3" r:id="rId2"/>
-    <sheet name="Header" sheetId="4" r:id="rId3"/>
-    <sheet name="Register" sheetId="5" r:id="rId4"/>
-    <sheet name="Top Menu" sheetId="6" r:id="rId5"/>
-    <sheet name="S" sheetId="7" r:id="rId6"/>
+    <sheet name="Top Menu" sheetId="6" r:id="rId3"/>
+    <sheet name="Header" sheetId="4" r:id="rId4"/>
+    <sheet name="Footer" sheetId="7" r:id="rId5"/>
+    <sheet name="Register" sheetId="5" r:id="rId6"/>
     <sheet name="Sheet6" sheetId="8" r:id="rId7"/>
     <sheet name="Sheet7" sheetId="9" r:id="rId8"/>
     <sheet name="Currency" sheetId="2" r:id="rId9"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="313">
   <si>
     <t>Open Cart Frontend</t>
   </si>
@@ -70,6 +70,9 @@
     <t>Number of Test Cases</t>
   </si>
   <si>
+    <t>Note</t>
+  </si>
+  <si>
     <t>TS001</t>
   </si>
   <si>
@@ -79,6 +82,9 @@
     <t>Validate the working of 'Register an account' functionality</t>
   </si>
   <si>
+    <t>Not in FRS will do exploratory test to create test case.</t>
+  </si>
+  <si>
     <t>TS002</t>
   </si>
   <si>
@@ -151,130 +157,136 @@
     <t>TS013</t>
   </si>
   <si>
+    <t>Validate the working of 'Slideshow' functionality</t>
+  </si>
+  <si>
+    <t>TS014</t>
+  </si>
+  <si>
     <t>Validate the working of 'Checkout' functionality</t>
   </si>
   <si>
-    <t>TS014</t>
+    <t>TS015</t>
   </si>
   <si>
     <t>Validate the working of 'My Account' functionality</t>
   </si>
   <si>
-    <t>TS015</t>
+    <t>TS016</t>
   </si>
   <si>
     <t>Validate the working of 'My Account &gt; Account Information' functionality</t>
   </si>
   <si>
-    <t>TS016</t>
+    <t>TS017</t>
   </si>
   <si>
     <t>Validate the working of 'My Account &gt; Change Password' functionality</t>
   </si>
   <si>
-    <t>TS017</t>
+    <t>TS018</t>
   </si>
   <si>
     <t>Validate the working of 'My Account Address Book' functionality</t>
   </si>
   <si>
-    <t>TS018</t>
+    <t>TS019</t>
   </si>
   <si>
     <t>Validate the working of 'My Order &gt; Order History' functionality</t>
   </si>
   <si>
-    <t>TS019</t>
+    <t>TS020</t>
   </si>
   <si>
     <t>Validate the working of 'My Orders &gt; Order Information' functionality</t>
   </si>
   <si>
-    <t>TS020</t>
+    <t>TS021</t>
   </si>
   <si>
     <t>Validate the working of 'My Orders &gt; Product Returns' functionality</t>
   </si>
   <si>
-    <t>TS021</t>
+    <t>TS022</t>
   </si>
   <si>
     <t>Validate the working of 'My Order &gt; Downloads' functionality</t>
   </si>
   <si>
-    <t>TS022</t>
+    <t>TS023</t>
   </si>
   <si>
     <t>Validate the working of 'My Orders &gt; Reward Points' functionality</t>
   </si>
   <si>
-    <t>TS023</t>
+    <t>TS024</t>
   </si>
   <si>
     <t>Validate the working of 'My Orders &gt; Returned Request' functionality</t>
   </si>
   <si>
-    <t>TS024</t>
+    <t>TS025</t>
   </si>
   <si>
     <t>Validate the working of 'My Order &gt; Your Transactions' functionality</t>
   </si>
   <si>
-    <t>TS025</t>
+    <t>TS026</t>
   </si>
   <si>
     <t>Validate the working of 'My Order &gt; Recurring Payments' functionality</t>
   </si>
   <si>
-    <t>TS026</t>
+    <t>TS027</t>
   </si>
   <si>
     <t>Validate the working of 'Affiliate' functionality</t>
   </si>
   <si>
-    <t>TS027</t>
+    <t>TS028</t>
   </si>
   <si>
     <t>Validate the working of 'Newsletter' functionality</t>
   </si>
   <si>
-    <t>TS028</t>
+    <t>TS029</t>
   </si>
   <si>
     <t>Validate the working of 'Contact Us' functionality</t>
   </si>
   <si>
-    <t>TS029</t>
+    <t>TS030</t>
   </si>
   <si>
     <t>Validate the working of 'Gift' functionality</t>
   </si>
   <si>
-    <t>TS030</t>
+    <t>TS031</t>
   </si>
   <si>
     <t>Validate the working of 'Special Offer' functionality</t>
   </si>
   <si>
-    <t>TS031</t>
+    <t>TS032</t>
   </si>
   <si>
     <t>Validate the working of 'Header' options' functionality</t>
   </si>
   <si>
-    <t>TS032</t>
-  </si>
-  <si>
-    <t>Validate the working of 'Menu' options' functionality</t>
-  </si>
-  <si>
     <t>TS033</t>
   </si>
   <si>
+    <t>Validate the working of 'Top Menu' options' functionality</t>
+  </si>
+  <si>
+    <t>TS034</t>
+  </si>
+  <si>
     <t>Validate the working of 'Footer' options' functionality</t>
   </si>
   <si>
-    <t>TS034</t>
+    <t>TS035</t>
   </si>
   <si>
     <t>Validate the Application functionality for different currency' functionality</t>
@@ -329,7 +341,7 @@
     <t>Open https://demo.opencart.com</t>
   </si>
   <si>
-    <t>1. Verify that top menu is displayed correctly (Validate ER-1)</t>
+    <t>1. Validate that top menu is displayed correctly (Validate ER-1)</t>
   </si>
   <si>
     <t>No Applicable</t>
@@ -352,8 +364,12 @@
     <t>Validate 'Direct back to home page' from product page</t>
   </si>
   <si>
-    <t>1. Select product from 'Featured products(Validate ER-1)
-2. Click store logo at top right corner on header (Validate ER-2)</t>
+    <t>1. Click on product from 'Featured products - &lt;Refer Test Data&gt;
+2. Wait for application to redirect user to product page (Validate ER-1)
+3. Click store logo at top right corner on header (Validate ER-2)</t>
+  </si>
+  <si>
+    <t>MacBook</t>
   </si>
   <si>
     <t>1) User should redirect to product page
@@ -381,7 +397,7 @@
     <t>Slideshow display image</t>
   </si>
   <si>
-    <t>1. Verify display image (Validate ER-1)</t>
+    <t>1. Validate display image (Validate ER-1)</t>
   </si>
   <si>
     <t>1) All Selected images will appear in slideshow</t>
@@ -393,11 +409,10 @@
     <t>Slideshow automatically change image</t>
   </si>
   <si>
-    <t>1. Verify display image
-2. Wait a certain amount of time (Validate ER-1)</t>
-  </si>
-  <si>
-    <t>1) image should shift to the next one</t>
+    <t>1. Wait a certain amount of time (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>1) image in slidesohw should shift to the next one</t>
   </si>
   <si>
     <t>TC_HP_006</t>
@@ -406,7 +421,7 @@
     <t>Slideshow manually change image</t>
   </si>
   <si>
-    <t>1. Verify display image (Validate ER-1)
+    <t>1. Validate display image (Validate ER-1)
 2. Select another dot under image (Validate ER-2)</t>
   </si>
   <si>
@@ -420,7 +435,11 @@
     <t>Slideshow select product</t>
   </si>
   <si>
-    <t>1. Click display image (Validate ER-1)</t>
+    <t>1. Click display image - &lt;Refer Test Data&gt;
+2. Validate navigation result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Slideshow image : 'MacBook'</t>
   </si>
   <si>
     <t>1) User should redirect to product page of selected product</t>
@@ -432,7 +451,7 @@
     <t>Validate 'Featured products' details</t>
   </si>
   <si>
-    <t>1. Verify featured product display correctly (Validate ER-1)</t>
+    <t>1. Validate featured product display correctly (Validate ER-1)</t>
   </si>
   <si>
     <t>1) Featured product should display under slideshow contain following elements:
@@ -448,7 +467,7 @@
     <t>TC_HP_009</t>
   </si>
   <si>
-    <t>Validate 'Featured products' switch list of product</t>
+    <t>Validate 'Featured products' swish list of product</t>
   </si>
   <si>
     <t>1. Click another dot under displayed featured (Validate ER-1)</t>
@@ -463,7 +482,8 @@
     <t>Select product from 'Featured products'</t>
   </si>
   <si>
-    <t>1. Select product from 'Featured' (Validate ER-1)</t>
+    <t>1. Click on product image from 'Featured' - &lt;Refer Test Data&gt;
+2. Validate nagivation result (Validate ER-1)</t>
   </si>
   <si>
     <t>Product : MacBook</t>
@@ -475,7 +495,7 @@
     <t>Validate footer</t>
   </si>
   <si>
-    <t>1. Verify that footer is displayed correctly (Validate ER-1)</t>
+    <t>1. Validate that footer is displayed correctly (Validate ER-1)</t>
   </si>
   <si>
     <t>1) Footer should displayed at bottom of the page and divided into following section :
@@ -485,6 +505,99 @@
 My Account : My Account, Order History, Wish List, Newsletter</t>
   </si>
   <si>
+    <t>TC_TM_01</t>
+  </si>
+  <si>
+    <t>(TS_032)
+Validate the working of 'Top Menu' options' functionality</t>
+  </si>
+  <si>
+    <t>Validate top menu visibility on any page</t>
+  </si>
+  <si>
+    <t>Open https://demo.opencart.com or currently in any page on application</t>
+  </si>
+  <si>
+    <t>1. Validate that top menu is displayed correctly ( Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Top menu should be displayed at top of the page on every page of the store</t>
+  </si>
+  <si>
+    <t>TC_TM_02</t>
+  </si>
+  <si>
+    <t>Validate top menu content</t>
+  </si>
+  <si>
+    <t>1. Validate top menu contents display correctly (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Top menu should contain parent categories as following : 
+- Desktops
+- Laptops &amp; Notebooks
+- Components
+- Tablets
+- Software
+- Phones &amp; PDAs
+- Cameras
+- MP3 Players</t>
+  </si>
+  <si>
+    <t>TC_TM_03</t>
+  </si>
+  <si>
+    <t>Validate top menu action 'click' on parent category</t>
+  </si>
+  <si>
+    <t>1. Click on any of 'top menu' content - &lt;Refer Test Data&gt;
+2. Validate result ( Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Desktops</t>
+  </si>
+  <si>
+    <t>Should navigate user to selected category page</t>
+  </si>
+  <si>
+    <t>TC_TM_04</t>
+  </si>
+  <si>
+    <t>Validate top menu action 'hover'</t>
+  </si>
+  <si>
+    <t>1. Hover on any of 'top menu' content - &lt;Refer Test Data&gt;
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Laptops &amp; Notebooks</t>
+  </si>
+  <si>
+    <t>A drop-down menu will display the sub-categories for that parent category</t>
+  </si>
+  <si>
+    <t>TC_TM_05</t>
+  </si>
+  <si>
+    <t>Validate top menu action 'click' on sub-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open https://demo.opencart.com
+</t>
+  </si>
+  <si>
+    <t>1. Hover on 'top menu' content - &lt;Refer Test Data - Parent Category&gt;
+2. Click on 'sub category' - &lt;Refer Test Data - Subcategory&gt;
+3. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Parent Category : Desktops
+Subcategory : CPU</t>
+  </si>
+  <si>
+    <t>Should navigate user to product page which display only selected subcategory</t>
+  </si>
+  <si>
     <t>TC_HD_001</t>
   </si>
   <si>
@@ -499,7 +612,7 @@
 Navigate in any page of application</t>
   </si>
   <si>
-    <t>1. Verify that header is displayed correctly (Validate ER-1)</t>
+    <t>1. Validate that header is displayed correctly (Validate ER-1)</t>
   </si>
   <si>
     <t>Header should displayed at top of the page and contain following options
@@ -543,7 +656,7 @@
     <t>Validate telephone display</t>
   </si>
   <si>
-    <t>1. Verify company telephone number (Validate ER-1)</t>
+    <t>1. Validate company telephone number (Validate ER-1)</t>
   </si>
   <si>
     <t>Company telephone number should be '123456789'</t>
@@ -597,8 +710,8 @@
     <t>Validate link 'Wish List' if not logged in</t>
   </si>
   <si>
-    <t>1. Click hearth symbol which displayed on product
-2. Verify message (Validate ER-1)</t>
+    <t>1. Click hearth symbol which displayed on product - &lt;Refer Test Data&gt;
+2. Validate message (Validate ER-1)</t>
   </si>
   <si>
     <t>Product : Canon EOS 5D</t>
@@ -617,9 +730,9 @@
 and log in</t>
   </si>
   <si>
-    <t>1. Click hearth symbol which displayed on product
+    <t>1. Click hearth symbol which displayed on product - &lt;Refer Test Data&gt;
 2. Reload page
-3. Verify 'Wish List' button (Validate ER-1)</t>
+3. Validate 'Wish List' button (Validate ER-1)</t>
   </si>
   <si>
     <t>A 'Wish List' button should change to Wish List(1)</t>
@@ -631,9 +744,9 @@
     <t>Validate 'Wish List' button after added multiple item</t>
   </si>
   <si>
-    <t>1. Click hearth symbol which displayed on multiple product
+    <t>1. Click hearth symbol which displayed on multiple product - &lt;Refer Test Data&gt;
 2. Reload page
-3. Verify 'Wish List' button (Validate ER-1)</t>
+3. Validate 'Wish List' button (Validate ER-1)</t>
   </si>
   <si>
     <t xml:space="preserve">Product : iPhone, MacBook, Apple Cinema 30"
@@ -654,7 +767,7 @@
 Added multiple wish list item</t>
   </si>
   <si>
-    <t>1. Click hearth symbol which displayed on multiple product
+    <t>1. Click hearth symbol which displayed on product - &lt;Refer Test Data&gt;
 2. Click on 'Wish List' button
 3. Click remove button on selected item  (Validate ER-1)</t>
   </si>
@@ -730,7 +843,7 @@
     <t>Validate search box</t>
   </si>
   <si>
-    <t>1. Input text into search box
+    <t>1. Input text into search box  - &lt;Refer Test Data&gt;
 2. Click Search button (Validate ER-1)</t>
   </si>
   <si>
@@ -746,7 +859,7 @@
     <t>Validate search box - too many characters</t>
   </si>
   <si>
-    <t>a text that has over a limit characters</t>
+    <t>a text that has over a 500 characters</t>
   </si>
   <si>
     <t>Should show error message "you exeed the character limit"</t>
@@ -756,54 +869,168 @@
 sometimes cause error 522</t>
   </si>
   <si>
+    <t>TC_FT_001</t>
+  </si>
+  <si>
+    <t>(TS-034)
+Validate the working of 'Footer' options' functionality</t>
+  </si>
+  <si>
+    <t>Validate footer contents</t>
+  </si>
+  <si>
+    <t>Open Application</t>
+  </si>
+  <si>
+    <t>1. Validate content of footer (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Footer should located at bottom of every page and contain following contents :
+Information which have :
+ About Us, Delivery Information, Privacy Policy, Terms &amp; Conditions
+Customer Service which have:
+ Contact Us, Returns, Site Map
+Extras which have:
+ Brands, Gift Vouchers, Affiliates, Specials
+My Account which have:
+ My Account, Order History, Wish List, Newsletter</t>
+  </si>
+  <si>
+    <t>TC_FT_002</t>
+  </si>
+  <si>
+    <t>Validate footer link 'About Us'</t>
+  </si>
+  <si>
+    <t>1. Click on footer content - &lt;Refer Test Data&gt;
+2. Validate navigation result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>TC_FT_003</t>
+  </si>
+  <si>
+    <t>Validate footer link 'Delivery Information'</t>
+  </si>
+  <si>
+    <t>TC_FT_004</t>
+  </si>
+  <si>
+    <t>Validate fotter link 'Privacy Policy'</t>
+  </si>
+  <si>
+    <t>TC_FT_005</t>
+  </si>
+  <si>
+    <t>Validate footer link 'Term &amp; Conditions'</t>
+  </si>
+  <si>
+    <t>TC_FT_006</t>
+  </si>
+  <si>
+    <t>Validate footer link 'Contact Us'</t>
+  </si>
+  <si>
+    <t>TC_FT_007</t>
+  </si>
+  <si>
+    <t>(TS-035)
+Validate the working of 'Footer' options' functionality</t>
+  </si>
+  <si>
+    <t>Validate footer link ' Returns'</t>
+  </si>
+  <si>
+    <t>TC_FT_008</t>
+  </si>
+  <si>
+    <t>(TS-036)
+Validate the working of 'Footer' options' functionality</t>
+  </si>
+  <si>
+    <t>Validate footer link 'Site Map'</t>
+  </si>
+  <si>
+    <t>TC_FT_009</t>
+  </si>
+  <si>
+    <t>(TS-037)
+Validate the working of 'Footer' options' functionality</t>
+  </si>
+  <si>
+    <t>Validate footer link 'Brands'</t>
+  </si>
+  <si>
+    <t>TC_FT_010</t>
+  </si>
+  <si>
+    <t>(TS-038)
+Validate the working of 'Footer' options' functionality</t>
+  </si>
+  <si>
+    <t>Validate footer link 'Gift Voucher'</t>
+  </si>
+  <si>
+    <t>TC_FT_011</t>
+  </si>
+  <si>
+    <t>(TS-039)
+Validate the working of 'Footer' options' functionality</t>
+  </si>
+  <si>
+    <t>Validate footer link 'Affiliates'</t>
+  </si>
+  <si>
+    <t>TC_FT_012</t>
+  </si>
+  <si>
+    <t>(TS-040)
+Validate the working of 'Footer' options' functionality</t>
+  </si>
+  <si>
+    <t>Validate footer link 'Specials'</t>
+  </si>
+  <si>
+    <t>TC_FT_013</t>
+  </si>
+  <si>
+    <t>(TS-041)
+Validate the working of 'Footer' options' functionality</t>
+  </si>
+  <si>
+    <t>Validate footer link 'My Account'</t>
+  </si>
+  <si>
+    <t>TC_FT_014</t>
+  </si>
+  <si>
+    <t>(TS-042)
+Validate the working of 'Footer' options' functionality</t>
+  </si>
+  <si>
+    <t>Validate footer link 'Order History'</t>
+  </si>
+  <si>
+    <t>TC_FT_015</t>
+  </si>
+  <si>
+    <t>(TS-043)
+Validate the working of 'Footer' options' functionality</t>
+  </si>
+  <si>
+    <t>Validate footer link 'Wish List'</t>
+  </si>
+  <si>
+    <t>TC_FT_016</t>
+  </si>
+  <si>
+    <t>(TS-044)
+Validate the working of 'Footer' options' functionality</t>
+  </si>
+  <si>
+    <t>Validate footer link 'Newletter'</t>
+  </si>
+  <si>
     <t>Not in FRS</t>
-  </si>
-  <si>
-    <t>Validate top menu parent</t>
-  </si>
-  <si>
-    <t>1. Verify that top menu is displayed correctly</t>
-  </si>
-  <si>
-    <t>Only top parent catagories should visible</t>
-  </si>
-  <si>
-    <t>Validate top menu sub catagories (hover)</t>
-  </si>
-  <si>
-    <t>1. Drag mouse over catagories</t>
-  </si>
-  <si>
-    <t>Desktops</t>
-  </si>
-  <si>
-    <t>Drop down sub-catagories of Desktops appear under Desktops catagories</t>
-  </si>
-  <si>
-    <t>Validate redirect to selected catagory</t>
-  </si>
-  <si>
-    <t>1. Click Catagories</t>
-  </si>
-  <si>
-    <t>Cameras</t>
-  </si>
-  <si>
-    <t>Should navigate user to catagory page which displayed only the selected catagory</t>
-  </si>
-  <si>
-    <t>Validate redirect to selected sub-catagory</t>
-  </si>
-  <si>
-    <t>1. Drag mouse over preferr catagories
-2. Select sub-catagory</t>
-  </si>
-  <si>
-    <t>Catagory : 'Software'
-Sub-catagory : '_____'</t>
-  </si>
-  <si>
-    <t>Should navigate user to catagory page which displayed only the selected sub-catagory</t>
   </si>
   <si>
     <t>TC_CF_001</t>
@@ -1522,7 +1749,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1556,36 +1783,57 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1604,96 +1852,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1706,20 +1906,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -2260,14 +2469,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
     <col min="2" max="2" width="9.875" customWidth="1"/>
     <col min="3" max="3" width="69.75" customWidth="1"/>
-    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
     <col min="5" max="5" width="21" style="1" customWidth="1"/>
+    <col min="6" max="6" width="48.625" customWidth="1"/>
     <col min="8" max="8" width="69.75" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2280,25 +2490,25 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
     </row>
     <row r="3" ht="18" spans="1:9">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="F3" s="56"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="F3" s="22"/>
     </row>
     <row r="4" spans="1:9">
       <c r="B4" t="s">
@@ -2306,416 +2516,444 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="50" t="s">
         <v>10</v>
       </c>
+      <c r="F6" s="50" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" ht="18" spans="1:9">
-      <c r="A7" s="13" t="s">
-        <v>11</v>
+      <c r="A7" s="11" t="s">
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="60" t="s">
         <v>13</v>
       </c>
+      <c r="C7" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" ht="18" spans="1:9">
-      <c r="A8" s="13" t="s">
-        <v>14</v>
+      <c r="A8" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="60" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="60" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="60" t="s">
-        <v>19</v>
+        <v>13</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="60" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="60" t="s">
-        <v>24</v>
+      <c r="C12" s="51" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="60" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="60" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="60" t="s">
-        <v>30</v>
+        <v>23</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>32</v>
+        <v>23</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="60" t="s">
-        <v>34</v>
+        <v>23</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:5">
-      <c r="A18" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="62"/>
-      <c r="E18" s="63">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="54"/>
+      <c r="E18" s="55">
         <f>COUNTA(HomePage!A3:A9998)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" customFormat="1" spans="1:5">
       <c r="A19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="60" t="s">
-        <v>38</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="B19" s="52" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="60" t="s">
-        <v>40</v>
+        <v>23</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="60" t="s">
-        <v>42</v>
+        <v>23</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="60" t="s">
-        <v>44</v>
+        <v>23</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="60" t="s">
-        <v>46</v>
+        <v>23</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="60" t="s">
-        <v>48</v>
+        <v>23</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="60" t="s">
-        <v>50</v>
+        <v>23</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="60" t="s">
-        <v>52</v>
+        <v>23</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="60" t="s">
-        <v>54</v>
+        <v>23</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="60" t="s">
-        <v>56</v>
+        <v>23</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" s="60" t="s">
-        <v>58</v>
+        <v>23</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" s="60" t="s">
-        <v>60</v>
+        <v>23</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" s="60" t="s">
-        <v>62</v>
+        <v>23</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" s="64" t="s">
-        <v>64</v>
+        <v>23</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" s="64" t="s">
-        <v>66</v>
+        <v>23</v>
+      </c>
+      <c r="C33" s="56" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="64" t="s">
-        <v>68</v>
+        <v>23</v>
+      </c>
+      <c r="C34" s="56" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
-      </c>
-      <c r="C35" s="64" t="s">
-        <v>70</v>
+        <v>23</v>
+      </c>
+      <c r="C35" s="56" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="60" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" spans="1:5">
-      <c r="A37" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="65" t="s">
-        <v>21</v>
-      </c>
-      <c r="C37" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="D37" s="65"/>
-      <c r="E37" s="63">
-        <f>COUNTA(Header!A3:A133)</f>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:5">
+      <c r="A38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D38" s="58"/>
+      <c r="E38" s="55">
+        <f>COUNTA(Header!A3:A200)</f>
         <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B38" t="s">
-        <v>21</v>
-      </c>
-      <c r="C38" s="60" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" s="60" t="s">
-        <v>78</v>
+        <v>23</v>
+      </c>
+      <c r="C39" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="58"/>
+      <c r="E39" s="59">
+        <f>COUNTA('Top Menu'!A2:A200)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" s="60" t="s">
-        <v>80</v>
+        <v>23</v>
+      </c>
+      <c r="C40" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="58"/>
+      <c r="E40" s="59">
+        <f>COUNTA(Footer!A3:A200)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="66"/>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66" t="s">
-        <v>81</v>
-      </c>
-      <c r="E41" s="67">
-        <f>SUM(E7:E40)</f>
-        <v>30</v>
+      <c r="A41" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="60"/>
+      <c r="B42" s="60"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="E42" s="61">
+        <f>SUM(E7:E41)</f>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -2728,6 +2966,9 @@
     <hyperlink ref="B2" r:id="rId1" display="https://demo.opencart.com/" tooltip="https://demo.opencart.com/"/>
     <hyperlink ref="A8" location="TS002!A1" display="TS002"/>
     <hyperlink ref="B3" r:id="rId2" display="https://drive.google.com/drive/folders/1nBs25k9jTb06qrV-5fTC75gtPOR6uW4V"/>
+    <hyperlink ref="A18" location="HomePage!A1" display="TS012"/>
+    <hyperlink ref="A38" location="Header!A1" display="TS032"/>
+    <hyperlink ref="A39" location="'Top Menu'!A1" display="TS033"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2745,7 +2986,7 @@
     <col min="3" max="3" width="44.5" style="8" customWidth="1"/>
     <col min="4" max="4" width="30.875" customWidth="1"/>
     <col min="5" max="5" width="52.375" style="8" customWidth="1"/>
-    <col min="6" max="6" width="21.375" customWidth="1"/>
+    <col min="6" max="6" width="30.4333333333333" customWidth="1"/>
     <col min="7" max="7" width="73.25" style="8" customWidth="1"/>
     <col min="8" max="8" width="35" customWidth="1"/>
     <col min="9" max="9" width="7.75" customWidth="1"/>
@@ -2754,351 +2995,351 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
-      <c r="A1" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="E1" s="19" t="s">
+      <c r="A1" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="B1" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="C1" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="D1" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="E1" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="K1" s="18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" s="13" customFormat="1" ht="18" spans="1:11">
-      <c r="A2" s="50" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="J1" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" s="11" customFormat="1" ht="18" spans="1:11">
+      <c r="A2" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="3" ht="142.5" spans="1:11">
-      <c r="A3" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3" s="25" t="s">
+      <c r="A3" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="B3" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="C3" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-    </row>
-    <row r="4" ht="28.5" spans="1:11">
-      <c r="A4" s="20" t="s">
+      <c r="D3" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="20" t="s">
+      <c r="E3" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="53" t="s">
+      <c r="F3" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="G3" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+    </row>
+    <row r="4" ht="71.25" spans="1:11">
+      <c r="A4" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="G4" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
+      <c r="C4" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
     </row>
     <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E5" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="F5" s="20" t="s">
+      <c r="A5" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
+      <c r="C5" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
     </row>
     <row r="6" ht="28.5" spans="1:11">
-      <c r="A6" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="F6" s="20" t="s">
+      <c r="A6" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
+      <c r="C6" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
     </row>
     <row r="7" ht="28.5" spans="1:11">
-      <c r="A7" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="F7" s="20" t="s">
+      <c r="A7" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
+      <c r="C7" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
     </row>
     <row r="8" ht="28.5" spans="1:11">
-      <c r="A8" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="F8" s="20" t="s">
+      <c r="A8" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="G8" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
+      <c r="C8" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
     </row>
     <row r="9" ht="28.5" spans="1:11">
-      <c r="A9" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="F9" s="20" t="s">
+      <c r="A9" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
+      <c r="C9" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
     </row>
     <row r="10" ht="114" spans="1:11">
-      <c r="A10" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="F10" s="20" t="s">
+      <c r="A10" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
+      <c r="C10" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
     </row>
     <row r="11" ht="28.5" spans="1:11">
-      <c r="A11" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="20" t="s">
+      <c r="A11" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+    </row>
+    <row r="12" ht="28.5" spans="1:11">
+      <c r="A12" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="G12" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="F11" s="20" t="s">
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+    </row>
+    <row r="13" ht="71.25" spans="1:11">
+      <c r="A13" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="G11" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12" ht="28.5" spans="1:11">
-      <c r="A12" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13" ht="71.25" spans="1:11">
-      <c r="A13" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
+      <c r="C13" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
     </row>
     <row r="14" spans="1:11">
       <c r="B14" s="7"/>
@@ -3147,6 +3388,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2:XFD2" location="Scenario!A8" display="&lt;&lt;Test Scenario"/>
+    <hyperlink ref="A2" location="Scenario!A18" display="&lt;&lt;Test Scenario"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3154,6 +3396,234 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="30.8833333333333" style="15" customWidth="1"/>
+    <col min="3" max="3" width="45.25" customWidth="1"/>
+    <col min="4" max="4" width="30.875" customWidth="1"/>
+    <col min="5" max="5" width="59.9916666666667" customWidth="1"/>
+    <col min="6" max="6" width="18.75" customWidth="1"/>
+    <col min="7" max="7" width="66.375" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="7.75" customWidth="1"/>
+    <col min="10" max="10" width="7.125" customWidth="1"/>
+    <col min="11" max="11" width="10.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" spans="1:11">
+      <c r="A1" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" ht="69" customHeight="1" spans="1:11">
+      <c r="A2" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+    </row>
+    <row r="3" ht="142.5" spans="1:11">
+      <c r="A3" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+    </row>
+    <row r="4" ht="42.75" spans="1:11">
+      <c r="A4" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+    </row>
+    <row r="5" ht="42.75" spans="1:11">
+      <c r="A5" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+    </row>
+    <row r="6" ht="42.75" spans="1:11">
+      <c r="A6" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16"/>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K35"/>
@@ -3164,247 +3634,247 @@
     <col min="3" max="3" width="52.25" style="3" customWidth="1"/>
     <col min="4" max="4" width="38.3833333333333" customWidth="1"/>
     <col min="5" max="5" width="53.025" style="3" customWidth="1"/>
-    <col min="6" max="6" width="24.875" style="15" customWidth="1"/>
-    <col min="7" max="7" width="72.85" style="16" customWidth="1"/>
-    <col min="8" max="8" width="19.2916666666667" style="17" customWidth="1"/>
+    <col min="6" max="6" width="24.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="72.85" style="22" customWidth="1"/>
+    <col min="8" max="8" width="19.2916666666667" style="12" customWidth="1"/>
     <col min="9" max="9" width="7.75" customWidth="1"/>
     <col min="10" max="10" width="7.125" customWidth="1"/>
     <col min="11" max="11" width="41.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:11">
-      <c r="A1" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="E1" s="19" t="s">
+      <c r="A1" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="B1" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="C1" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="D1" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="E1" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="K1" s="18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
+      <c r="J1" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" ht="18" spans="1:11">
+      <c r="A2" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
     </row>
     <row r="3" ht="114" spans="1:11">
-      <c r="A3" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
+      <c r="A3" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
     </row>
     <row r="4" ht="42.75" spans="1:11">
-      <c r="A4" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>141</v>
+      <c r="A4" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>173</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="H4" s="23"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
+        <v>179</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="H4" s="30"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
     </row>
     <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>141</v>
+      <c r="A5" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>173</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
+        <v>183</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="H5" s="30"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
     </row>
     <row r="6" ht="42.75" spans="1:11">
-      <c r="A6" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>141</v>
+      <c r="A6" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>173</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>96</v>
+        <v>187</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>100</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="H6" s="23"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
+        <v>188</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="H6" s="30"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
     </row>
     <row r="7" ht="42.75" spans="1:11">
-      <c r="A7" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>141</v>
+      <c r="A7" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>173</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
+        <v>191</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="H7" s="30"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
     </row>
     <row r="8" ht="42.75" spans="1:11">
-      <c r="A8" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="G8" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="H8" s="34"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="36"/>
+      <c r="A8" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="H8" s="38"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="38"/>
     </row>
     <row r="9" ht="42.75" spans="1:11">
-      <c r="A9" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="F9" s="31" t="s">
-        <v>98</v>
+      <c r="A9" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>102</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="39"/>
@@ -3412,334 +3882,333 @@
       <c r="K9" s="39"/>
     </row>
     <row r="10" ht="42.75" spans="1:11">
-      <c r="A10" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="G10" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="H10" s="34"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="36"/>
+      <c r="A10" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="H10" s="38"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="38"/>
     </row>
     <row r="11" ht="42.75" spans="1:11">
-      <c r="A11" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C11" s="30" t="s">
+      <c r="A11" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="B11" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>175</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="H11" s="34"/>
+      <c r="C11" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="H11" s="38"/>
       <c r="I11" s="39"/>
       <c r="J11" s="39"/>
-      <c r="K11" s="36"/>
-    </row>
-    <row r="12" ht="42.75" spans="1:11">
-      <c r="A12" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="E12" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="F12" s="41" t="s">
-        <v>175</v>
-      </c>
-      <c r="G12" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="H12" s="34"/>
+      <c r="K11" s="38"/>
+    </row>
+    <row r="12" ht="57" spans="1:11">
+      <c r="A12" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>210</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="H12" s="38"/>
       <c r="I12" s="39"/>
       <c r="J12" s="39"/>
-      <c r="K12" s="36"/>
-    </row>
-    <row r="13" ht="42.75" spans="1:11">
-      <c r="A13" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>183</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="G13" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="H13" s="34"/>
+      <c r="K12" s="38"/>
+    </row>
+    <row r="13" ht="57" spans="1:11">
+      <c r="A13" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="G13" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="H13" s="38"/>
       <c r="I13" s="39"/>
       <c r="J13" s="39"/>
-      <c r="K13" s="36"/>
-    </row>
-    <row r="14" ht="42.75" spans="1:11">
-      <c r="A14" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="B14" s="31" t="s">
+      <c r="K13" s="38"/>
+    </row>
+    <row r="14" ht="57" spans="1:11">
+      <c r="A14" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="F14" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="D14" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="E14" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="F14" s="41" t="s">
-        <v>135</v>
-      </c>
-      <c r="G14" s="33" t="s">
-        <v>191</v>
-      </c>
-      <c r="H14" s="34"/>
+      <c r="G14" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="H14" s="38"/>
       <c r="I14" s="39"/>
       <c r="J14" s="39"/>
-      <c r="K14" s="36"/>
+      <c r="K14" s="38"/>
     </row>
     <row r="15" ht="42.75" spans="1:11">
-      <c r="A15" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="F15" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="H15" s="34"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="36"/>
+      <c r="A15" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="H15" s="38"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="38"/>
     </row>
     <row r="16" ht="42.75" spans="1:11">
-      <c r="A16" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="F16" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="G16" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="36"/>
+      <c r="A16" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="H16" s="38"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="38"/>
     </row>
     <row r="17" ht="42.75" spans="1:11">
-      <c r="A17" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="E17" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="F17" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="H17" s="34"/>
+      <c r="A17" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="F17" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="H17" s="38"/>
       <c r="I17" s="39"/>
       <c r="J17" s="39"/>
-      <c r="K17" s="36"/>
+      <c r="K17" s="38"/>
     </row>
     <row r="18" ht="42.75" spans="1:11">
-      <c r="A18" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>205</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="F18" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="G18" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="H18" s="34"/>
+      <c r="A18" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="F18" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>239</v>
+      </c>
+      <c r="H18" s="38"/>
       <c r="I18" s="39"/>
       <c r="J18" s="39"/>
-      <c r="K18" s="36"/>
+      <c r="K18" s="38"/>
     </row>
     <row r="19" s="12" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A19" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="F19" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="H19" s="34"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="36"/>
+      <c r="A19" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>242</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="H19" s="38"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="38"/>
     </row>
     <row r="20" s="12" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A20" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="B20" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="E20" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="G20" s="45" t="s">
-        <v>216</v>
-      </c>
-      <c r="H20" s="36"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="36"/>
+      <c r="A20" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="G20" s="41" t="s">
+        <v>248</v>
+      </c>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
     </row>
     <row r="21" customFormat="1" ht="71.25" spans="1:11">
-      <c r="A21" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="G21" s="47" t="s">
-        <v>220</v>
-      </c>
-      <c r="H21" s="48" t="s">
-        <v>221</v>
-      </c>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
-      <c r="K21" s="49"/>
+      <c r="A21" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="H21" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
     </row>
     <row r="22" spans="1:11">
       <c r="C22"/>
-      <c r="D22"/>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
@@ -3747,7 +4216,6 @@
     </row>
     <row r="23" spans="1:11">
       <c r="C23"/>
-      <c r="D23"/>
       <c r="E23"/>
       <c r="F23"/>
       <c r="G23"/>
@@ -3755,7 +4223,6 @@
     </row>
     <row r="24" spans="1:11">
       <c r="C24"/>
-      <c r="D24"/>
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24"/>
@@ -3763,7 +4230,6 @@
     </row>
     <row r="25" spans="1:11">
       <c r="C25"/>
-      <c r="D25"/>
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25"/>
@@ -3771,7 +4237,6 @@
     </row>
     <row r="26" spans="1:11">
       <c r="C26"/>
-      <c r="D26"/>
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26"/>
@@ -3779,7 +4244,6 @@
     </row>
     <row r="27" spans="1:11">
       <c r="C27"/>
-      <c r="D27"/>
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27"/>
@@ -3787,7 +4251,6 @@
     </row>
     <row r="28" spans="1:11">
       <c r="C28"/>
-      <c r="D28"/>
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28"/>
@@ -3795,7 +4258,6 @@
     </row>
     <row r="29" spans="1:11">
       <c r="C29"/>
-      <c r="D29"/>
       <c r="E29"/>
       <c r="F29"/>
       <c r="G29"/>
@@ -3803,7 +4265,6 @@
     </row>
     <row r="30" spans="1:11">
       <c r="C30"/>
-      <c r="D30"/>
       <c r="E30"/>
       <c r="F30"/>
       <c r="G30"/>
@@ -3811,7 +4272,6 @@
     </row>
     <row r="31" spans="1:11">
       <c r="C31"/>
-      <c r="D31"/>
       <c r="E31"/>
       <c r="F31"/>
       <c r="G31"/>
@@ -3819,7 +4279,6 @@
     </row>
     <row r="32" spans="1:11">
       <c r="C32"/>
-      <c r="D32"/>
       <c r="E32"/>
       <c r="F32"/>
       <c r="G32"/>
@@ -3827,7 +4286,6 @@
     </row>
     <row r="33" spans="3:8">
       <c r="C33"/>
-      <c r="D33"/>
       <c r="E33"/>
       <c r="F33"/>
       <c r="G33"/>
@@ -3835,7 +4293,6 @@
     </row>
     <row r="34" spans="3:8">
       <c r="C34"/>
-      <c r="D34"/>
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34"/>
@@ -3843,19 +4300,542 @@
     </row>
     <row r="35" spans="3:8">
       <c r="C35"/>
-      <c r="D35"/>
       <c r="E35"/>
       <c r="F35"/>
       <c r="G35"/>
       <c r="H35"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" location="Scenario!A37" display="Test Scenario"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:XFD36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="25.875" style="15" customWidth="1"/>
+    <col min="3" max="3" width="32.625" customWidth="1"/>
+    <col min="4" max="4" width="30.875" customWidth="1"/>
+    <col min="5" max="5" width="42.35" customWidth="1"/>
+    <col min="6" max="6" width="15.2916666666667" customWidth="1"/>
+    <col min="7" max="7" width="86.6" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="7.75" customWidth="1"/>
+    <col min="10" max="10" width="7.125" customWidth="1"/>
+    <col min="11" max="11" width="10.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="14" customFormat="1" ht="15" spans="1:11">
+      <c r="A1" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" s="14" customFormat="1" spans="1:11">
+      <c r="A2" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="18"/>
+    </row>
+    <row r="3" s="14" customFormat="1" ht="128.25" spans="1:11">
+      <c r="A3" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" s="14" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A4" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F4" s="14" t="str">
+        <f>SUBSTITUTE(MID(C4,22,30),"'","")</f>
+        <v>About Us</v>
+      </c>
+      <c r="G4" s="14" t="str">
+        <f>"Should navigate user to "&amp;MID(C4,22,30)&amp;". A proper text/information should display on this page"</f>
+        <v>Should navigate user to 'About Us'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="5" s="14" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A5" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F5" s="14" t="str">
+        <f t="shared" ref="F5:F18" si="0">SUBSTITUTE(MID(C5,22,30),"'","")</f>
+        <v>Delivery Information</v>
+      </c>
+      <c r="G5" s="14" t="str">
+        <f>"Should navigate user to "&amp;MID(C5,22,30)&amp;". A proper text/information should display on this page"</f>
+        <v>Should navigate user to 'Delivery Information'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="6" s="14" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A6" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F6" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Privacy Policy</v>
+      </c>
+      <c r="G6" s="14" t="str">
+        <f>"Should navigate user to "&amp;MID(C6,22,30)&amp;". A proper text/information should display on this page"</f>
+        <v>Should navigate user to 'Privacy Policy'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="7" s="14" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A7" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F7" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Term &amp; Conditions</v>
+      </c>
+      <c r="G7" s="14" t="str">
+        <f t="shared" ref="G7:G18" si="1">"Should navigate user to "&amp;MID(C7,22,30)&amp;". A proper text/information should display on this page"</f>
+        <v>Should navigate user to 'Term &amp; Conditions'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="8" s="14" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A8" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F8" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Contact Us</v>
+      </c>
+      <c r="G8" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Contact Us'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="9" s="14" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A9" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F9" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v> Returns</v>
+      </c>
+      <c r="G9" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to ' Returns'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="10" s="14" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A10" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F10" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Site Map</v>
+      </c>
+      <c r="G10" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Site Map'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="11" s="14" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A11" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F11" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Brands</v>
+      </c>
+      <c r="G11" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Brands'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="12" s="14" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A12" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F12" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Gift Voucher</v>
+      </c>
+      <c r="G12" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Gift Voucher'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="13" s="14" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A13" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F13" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Affiliates</v>
+      </c>
+      <c r="G13" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Affiliates'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="14" s="14" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A14" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F14" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Specials</v>
+      </c>
+      <c r="G14" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Specials'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="15" s="14" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A15" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F15" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>My Account</v>
+      </c>
+      <c r="G15" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'My Account'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="16" s="14" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A16" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F16" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Order History</v>
+      </c>
+      <c r="G16" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Order History'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="17" s="14" customFormat="1" ht="42.75" spans="1:7">
+      <c r="A17" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F17" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Wish List</v>
+      </c>
+      <c r="G17" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Wish List'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="18" s="14" customFormat="1" ht="42.75" spans="1:7">
+      <c r="A18" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>300</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="F18" s="14" t="str">
+        <f t="shared" si="0"/>
+        <v>Newletter</v>
+      </c>
+      <c r="G18" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Newletter'. A proper text/information should display on this page</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="B19" s="21"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="B20" s="21"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="B21" s="21"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="B22" s="21"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="B23" s="21"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="B24" s="21"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="B25" s="21"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="B26" s="21"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="B27" s="21"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="B28" s="21"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="B29" s="21"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="21"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="B31" s="21"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="B32" s="21"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="21"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="21"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="21"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:XFD2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K15"/>
@@ -3876,276 +4856,88 @@
   <sheetData>
     <row r="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:11">
       <c r="A2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B2" s="13"/>
+        <v>301</v>
+      </c>
+      <c r="B2" s="11"/>
       <c r="C2" s="12"/>
       <c r="E2" s="12"/>
     </row>
     <row r="3" ht="18" spans="1:11">
-      <c r="B3" s="14"/>
+      <c r="B3" s="13"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
     </row>
     <row r="4" ht="18" spans="1:11">
-      <c r="B4" s="14"/>
+      <c r="B4" s="13"/>
       <c r="D4" s="12"/>
     </row>
     <row r="5" ht="18" spans="1:11">
-      <c r="B5" s="14"/>
+      <c r="B5" s="13"/>
     </row>
     <row r="6" ht="18" spans="1:11">
-      <c r="B6" s="14"/>
+      <c r="B6" s="13"/>
     </row>
     <row r="7" ht="18" spans="1:11">
-      <c r="B7" s="14"/>
+      <c r="B7" s="13"/>
     </row>
     <row r="8" ht="18" spans="1:11">
-      <c r="B8" s="13"/>
+      <c r="B8" s="11"/>
     </row>
     <row r="9" ht="18" spans="1:11">
-      <c r="B9" s="14"/>
+      <c r="B9" s="13"/>
     </row>
     <row r="10" ht="18" spans="1:11">
-      <c r="B10" s="14"/>
+      <c r="B10" s="13"/>
     </row>
     <row r="11" ht="18" spans="1:11">
-      <c r="B11" s="14"/>
+      <c r="B11" s="13"/>
     </row>
     <row r="12" ht="18" spans="1:11">
-      <c r="B12" s="14"/>
+      <c r="B12" s="13"/>
     </row>
     <row r="13" ht="18" spans="1:11">
-      <c r="B13" s="14"/>
+      <c r="B13" s="13"/>
     </row>
     <row r="14" ht="18" spans="1:11">
-      <c r="B14" s="13"/>
+      <c r="B14" s="11"/>
     </row>
     <row r="15" ht="18" spans="1:11">
-      <c r="B15" s="13"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
-  <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="14.125" customWidth="1"/>
-    <col min="3" max="3" width="18.625" customWidth="1"/>
-    <col min="4" max="4" width="30.875" customWidth="1"/>
-    <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="18.75" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="13.375" customWidth="1"/>
-    <col min="9" max="9" width="7.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" spans="1:11">
-      <c r="A1" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" ht="42.75" spans="1:11">
-      <c r="C2" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="F2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="3" ht="71.25" spans="1:11">
-      <c r="C3" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="F3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="4" ht="57" spans="1:11">
-      <c r="C4" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="F4" t="s">
-        <v>232</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="5" ht="71.25" spans="1:11">
-      <c r="C5" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>237</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="14.125" customWidth="1"/>
-    <col min="3" max="3" width="32.625" customWidth="1"/>
-    <col min="4" max="4" width="30.875" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
-    <col min="7" max="7" width="51" customWidth="1"/>
-    <col min="8" max="8" width="13.375" customWidth="1"/>
-    <col min="9" max="9" width="7.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" spans="1:11">
-      <c r="A1" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>91</v>
-      </c>
+      <c r="B15" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4196,42 +4988,42 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -4240,48 +5032,48 @@
     </row>
     <row r="3" ht="42.75" spans="1:11">
       <c r="A3" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>241</v>
+        <v>305</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>242</v>
+        <v>306</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>243</v>
+        <v>307</v>
       </c>
       <c r="G3" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" ht="42.75" spans="1:11">
       <c r="A4" t="s">
-        <v>245</v>
+        <v>309</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>246</v>
+        <v>310</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>241</v>
+        <v>305</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>247</v>
+        <v>311</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>248</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/manual test/Open cert/OpenCartFrontend.xlsx
+++ b/manual test/Open cert/OpenCartFrontend.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25275" windowHeight="11580" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="26580" windowHeight="11580" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenario" sheetId="1" r:id="rId1"/>
-    <sheet name="HomePage" sheetId="3" r:id="rId2"/>
-    <sheet name="Top Menu" sheetId="6" r:id="rId3"/>
-    <sheet name="Header" sheetId="4" r:id="rId4"/>
-    <sheet name="Footer" sheetId="7" r:id="rId5"/>
-    <sheet name="Register" sheetId="5" r:id="rId6"/>
-    <sheet name="Sheet6" sheetId="8" r:id="rId7"/>
-    <sheet name="Sheet7" sheetId="9" r:id="rId8"/>
-    <sheet name="Currency" sheetId="2" r:id="rId9"/>
+    <sheet name="Version" sheetId="10" r:id="rId1"/>
+    <sheet name="Scenario" sheetId="1" r:id="rId2"/>
+    <sheet name="HomePage" sheetId="3" r:id="rId3"/>
+    <sheet name="Top Menu" sheetId="6" r:id="rId4"/>
+    <sheet name="Header" sheetId="4" r:id="rId5"/>
+    <sheet name="Footer" sheetId="7" r:id="rId6"/>
+    <sheet name="Product Pages" sheetId="8" r:id="rId7"/>
+    <sheet name="Product Listings" sheetId="9" r:id="rId8"/>
+    <sheet name="Register" sheetId="5" r:id="rId9"/>
+    <sheet name="Currency" sheetId="2" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="381">
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>Detail</t>
+  </si>
+  <si>
+    <t>Create test scenario &amp; test case from FRS only.</t>
+  </si>
   <si>
     <t>Open Cart Frontend</t>
   </si>
@@ -52,7 +62,7 @@
     <t>https://drive.google.com/drive/folders/1nBs25k9jTb06qrV-5fTC75gtPOR6uW4V</t>
   </si>
   <si>
-    <t>*create test scenario/test case only from FRS only</t>
+    <t>* 1.0 create test scenario/test case only from FRS only</t>
   </si>
   <si>
     <t>Test Scenario ID</t>
@@ -82,7 +92,7 @@
     <t>Validate the working of 'Register an account' functionality</t>
   </si>
   <si>
-    <t>Not in FRS will do exploratory test to create test case.</t>
+    <t>Not in FRS</t>
   </si>
   <si>
     <t>TS002</t>
@@ -121,7 +131,7 @@
     <t>TS007</t>
   </si>
   <si>
-    <t>Validate the working of 'Product page' functionality for different type of product</t>
+    <t>Validate the working of 'Product page' functionality</t>
   </si>
   <si>
     <t>TS008</t>
@@ -1030,7 +1040,225 @@
     <t>Validate footer link 'Newletter'</t>
   </si>
   <si>
-    <t>Not in FRS</t>
+    <t>TC_PP_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(TS_007)
+Validate the working of 'Product page' functionality
+</t>
+  </si>
+  <si>
+    <t>Validate product page contain a complete elements</t>
+  </si>
+  <si>
+    <t>Open application,
+Open product page</t>
+  </si>
+  <si>
+    <t>1. Validate product page element (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product page should contain following sections :
+Product image, Product details, Cart, Rating/Sharing, Description tab, Review tab
+</t>
+  </si>
+  <si>
+    <t>TC_PP_002</t>
+  </si>
+  <si>
+    <t>Validate product images displayed correctly</t>
+  </si>
+  <si>
+    <t>1. Validate product page image (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Product image can be displayed under title on the left-side, along with alternate views of the product underneath it in smaller box</t>
+  </si>
+  <si>
+    <t>TC_PP_003</t>
+  </si>
+  <si>
+    <t>Validate product images expand functionality</t>
+  </si>
+  <si>
+    <t>1. Click on main image
+2. Validate expand function (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Product image should expand within the window</t>
+  </si>
+  <si>
+    <t>TC_PP_004</t>
+  </si>
+  <si>
+    <t>Validate product details information</t>
+  </si>
+  <si>
+    <t>1. Validate product details ( Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Product details should contain :
+The product code, availability, price
+and displayed correctly</t>
+  </si>
+  <si>
+    <t>TC_PP_005</t>
+  </si>
+  <si>
+    <t>Validate accpet product quantity</t>
+  </si>
+  <si>
+    <t>1. Input test data into quantity box - &lt;Refer test data&gt;
+2. Click 'Add to Cart' button
+3. Validate product details (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Quantity : 5</t>
+  </si>
+  <si>
+    <t>Product added to cart successfully</t>
+  </si>
+  <si>
+    <t>TC_PP_006</t>
+  </si>
+  <si>
+    <t>Validate reject product quantity</t>
+  </si>
+  <si>
+    <t>Quantity : -5
+Quantity : two</t>
+  </si>
+  <si>
+    <t>Error message should appear "Please input quantity correctly"</t>
+  </si>
+  <si>
+    <t>TC_PP_007</t>
+  </si>
+  <si>
+    <t>Validate availability of product</t>
+  </si>
+  <si>
+    <t>Open application,
+Open product page,
+Product is available</t>
+  </si>
+  <si>
+    <t>1. Validate product availability (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Product detail availability should be : 'In Stock' and 'Add to Cart' button should be enabled</t>
+  </si>
+  <si>
+    <t>TC_PP_008</t>
+  </si>
+  <si>
+    <t>Validate unavailability of product</t>
+  </si>
+  <si>
+    <t>Open application,
+Open product page,
+Product is out of stock</t>
+  </si>
+  <si>
+    <t>Product detail availability should be : 'Out of Stock' and 'Add to Cart' button should be disabled</t>
+  </si>
+  <si>
+    <t>TC_PP_009</t>
+  </si>
+  <si>
+    <t>Validate wish list funtionality</t>
+  </si>
+  <si>
+    <t>1. Click on 'wish list' button above the product name(Hearth Symbol)
+2. Validate the result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Page should display "Wish list added successfully"</t>
+  </si>
+  <si>
+    <t>TC_PP_010</t>
+  </si>
+  <si>
+    <t>Validate compare funtionality</t>
+  </si>
+  <si>
+    <t>1. Click on 'compare' button above the product name(next to 'wish list' button)
+2. Validate the result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Product should added to compare list</t>
+  </si>
+  <si>
+    <t>TC_PP_011</t>
+  </si>
+  <si>
+    <t>Validate rating functionality</t>
+  </si>
+  <si>
+    <t>1. Click on the star underneath 'Add to Cart' button
+2. Validate the result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>The star should change based on average of total star</t>
+  </si>
+  <si>
+    <t>TC_PP_012</t>
+  </si>
+  <si>
+    <t>Validate sharing funtionality</t>
+  </si>
+  <si>
+    <t>1. Click on social media button
+2. Validate the result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Should open new window that connect to selected platform</t>
+  </si>
+  <si>
+    <t>TC_PP_013</t>
+  </si>
+  <si>
+    <t>Validate description tab display correctly</t>
+  </si>
+  <si>
+    <t>1. Validate product description ( Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Detailed description of the product should display correctly</t>
+  </si>
+  <si>
+    <t>TC_PP_014</t>
+  </si>
+  <si>
+    <t>Validate review functionality</t>
+  </si>
+  <si>
+    <t>1. Click on 'write a review' link underneath 'Add to Cart' button
+2. Write review(s) - &lt;Refer test data&gt;
+3. Click send (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>This product is over heat easily'</t>
+  </si>
+  <si>
+    <t>Should display message 'Review succesful thank you for your review'</t>
+  </si>
+  <si>
+    <t>TC_PP_015</t>
+  </si>
+  <si>
+    <t>Validate review functionality - error</t>
+  </si>
+  <si>
+    <t>1. Click on 'write a review' link underneath 'Add to Cart' button
+2. Do not input any text in review
+3. Click send (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Should display a required fied or 'please write a review' message</t>
   </si>
   <si>
     <t>TC_CF_001</t>
@@ -1269,7 +1497,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1285,6 +1513,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1469,7 +1703,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1481,6 +1715,43 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -1625,7 +1896,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1637,119 +1908,119 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1792,102 +2063,165 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1897,15 +2231,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1924,17 +2261,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2469,6 +2809,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="B3:C10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="46.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" ht="15" spans="2:3">
+      <c r="B3" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="82" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="2:3">
+      <c r="B4" s="83">
+        <v>1</v>
+      </c>
+      <c r="C4" s="82" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="2:3">
+      <c r="B5" s="83">
+        <v>2</v>
+      </c>
+      <c r="C5" s="83"/>
+    </row>
+    <row r="6" ht="15" spans="2:3">
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+    </row>
+    <row r="7" ht="15" spans="2:3">
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+    </row>
+    <row r="8" ht="15" spans="2:3">
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+    </row>
+    <row r="9" ht="15" spans="2:3">
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+    </row>
+    <row r="10" ht="15" spans="2:3">
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:XFD4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="31.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="30.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="34.75" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="64.875" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="7.75" customWidth="1"/>
+    <col min="10" max="10" width="7.125" customWidth="1"/>
+    <col min="11" max="11" width="10.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
+      <c r="A1" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:11">
+      <c r="A2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" ht="42.75" spans="1:11">
+      <c r="A3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="G3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="4" ht="42.75" spans="1:11">
+      <c r="A4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:XFD2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A2:XFD2" location="Scenario!A7" display="&lt;&lt;Test Scenario"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
@@ -2483,477 +3002,503 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:9">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="47" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
+        <v>4</v>
+      </c>
+      <c r="B2" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
     </row>
     <row r="3" ht="18" spans="1:9">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="F3" s="22"/>
+        <v>6</v>
+      </c>
+      <c r="B3" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="F3" s="41"/>
     </row>
     <row r="4" spans="1:9">
       <c r="B4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="50" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="50" t="s">
+      <c r="A6" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="B6" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="C6" s="70" t="s">
         <v>11</v>
+      </c>
+      <c r="D6" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="70" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:9">
       <c r="A7" s="11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="C7" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:9">
       <c r="A8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>17</v>
+      <c r="C8" s="71" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
         <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>21</v>
+        <v>16</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="C11" s="71" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="51" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>27</v>
+      <c r="C12" s="71" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" ht="18" spans="1:9">
+      <c r="A13" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="C13" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="72"/>
+      <c r="E13" s="73">
+        <f>COUNTA('Product Pages'!A3:A200)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="C14" s="71" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>32</v>
+        <v>26</v>
+      </c>
+      <c r="C15" s="71" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="C16" s="71" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>36</v>
+        <v>26</v>
+      </c>
+      <c r="C17" s="71" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:5">
       <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="52" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="54"/>
-      <c r="E18" s="55">
+        <v>40</v>
+      </c>
+      <c r="B18" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="76"/>
+      <c r="E18" s="77">
         <f>COUNTA(HomePage!A3:A9998)</f>
         <v>11</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:5">
       <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="52" t="s">
-        <v>23</v>
+        <v>42</v>
+      </c>
+      <c r="B19" s="74" t="s">
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>42</v>
+        <v>26</v>
+      </c>
+      <c r="C20" s="71" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>44</v>
+        <v>26</v>
+      </c>
+      <c r="C21" s="71" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>46</v>
+        <v>26</v>
+      </c>
+      <c r="C22" s="71" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>48</v>
+        <v>26</v>
+      </c>
+      <c r="C23" s="71" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="51" t="s">
-        <v>50</v>
+        <v>26</v>
+      </c>
+      <c r="C24" s="71" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="51" t="s">
-        <v>52</v>
+        <v>26</v>
+      </c>
+      <c r="C25" s="71" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="51" t="s">
-        <v>54</v>
+        <v>26</v>
+      </c>
+      <c r="C26" s="71" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="51" t="s">
-        <v>56</v>
+        <v>26</v>
+      </c>
+      <c r="C27" s="71" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>58</v>
+        <v>26</v>
+      </c>
+      <c r="C28" s="71" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="51" t="s">
-        <v>60</v>
+        <v>26</v>
+      </c>
+      <c r="C29" s="71" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="51" t="s">
-        <v>62</v>
+        <v>26</v>
+      </c>
+      <c r="C30" s="71" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="51" t="s">
-        <v>64</v>
+        <v>26</v>
+      </c>
+      <c r="C31" s="71" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" s="51" t="s">
-        <v>66</v>
+        <v>26</v>
+      </c>
+      <c r="C32" s="71" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="56" t="s">
-        <v>68</v>
+        <v>26</v>
+      </c>
+      <c r="C33" s="78" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" s="56" t="s">
-        <v>70</v>
+        <v>26</v>
+      </c>
+      <c r="C34" s="78" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="56" t="s">
-        <v>72</v>
+        <v>26</v>
+      </c>
+      <c r="C35" s="78" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
-      </c>
-      <c r="C36" s="56" t="s">
-        <v>74</v>
+        <v>26</v>
+      </c>
+      <c r="C36" s="78" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="51" t="s">
-        <v>76</v>
+        <v>26</v>
+      </c>
+      <c r="C37" s="71" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:5">
       <c r="A38" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" s="57" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" s="58" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" s="58"/>
-      <c r="E38" s="55">
+        <v>80</v>
+      </c>
+      <c r="B38" s="79" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="72" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="72"/>
+      <c r="E38" s="77">
         <f>COUNTA(Header!A3:A200)</f>
         <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" s="58" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" s="58"/>
-      <c r="E39" s="59">
+        <v>26</v>
+      </c>
+      <c r="C39" s="72" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" s="72"/>
+      <c r="E39" s="73">
         <f>COUNTA('Top Menu'!A2:A200)</f>
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="58" t="s">
-        <v>82</v>
-      </c>
-      <c r="D40" s="58"/>
-      <c r="E40" s="59">
+        <v>26</v>
+      </c>
+      <c r="C40" s="72" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="72"/>
+      <c r="E40" s="73">
         <f>COUNTA(Footer!A3:A200)</f>
         <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" s="51" t="s">
-        <v>84</v>
+        <v>26</v>
+      </c>
+      <c r="C41" s="71" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="60"/>
-      <c r="B42" s="60"/>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="E42" s="61">
+      <c r="A42" s="80"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" s="81">
         <f>SUM(E7:E41)</f>
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2969,13 +3514,14 @@
     <hyperlink ref="A18" location="HomePage!A1" display="TS012"/>
     <hyperlink ref="A38" location="Header!A1" display="TS032"/>
     <hyperlink ref="A39" location="'Top Menu'!A1" display="TS033"/>
+    <hyperlink ref="A13" location="'Product Pages'!A1" display="TS007"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K27"/>
@@ -2995,351 +3541,351 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
-      <c r="A1" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" s="23" t="s">
+      <c r="A1" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="B1" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="C1" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="D1" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="E1" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="23" t="s">
+      <c r="F1" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="G1" s="43" t="s">
         <v>95</v>
       </c>
+      <c r="H1" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="42" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="2" s="11" customFormat="1" ht="18" spans="1:11">
-      <c r="A2" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
+      <c r="A2" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
     </row>
     <row r="3" ht="142.5" spans="1:11">
-      <c r="A3" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" s="27" t="s">
+      <c r="A3" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="B3" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="C3" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="D3" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
+      <c r="E3" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
     </row>
     <row r="4" ht="71.25" spans="1:11">
-      <c r="A4" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="26" t="s">
+      <c r="A4" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="49" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+    </row>
+    <row r="5" ht="42.75" spans="1:11">
+      <c r="A5" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-    </row>
-    <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
+      <c r="G5" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
     </row>
     <row r="6" ht="28.5" spans="1:11">
-      <c r="A6" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="G6" s="27" t="s">
+      <c r="A6" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
+      <c r="B6" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
     </row>
     <row r="7" ht="28.5" spans="1:11">
-      <c r="A7" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="27" t="s">
+      <c r="A7" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
+      <c r="B7" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>123</v>
+      </c>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
     </row>
     <row r="8" ht="28.5" spans="1:11">
-      <c r="A8" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="G8" s="32" t="s">
+      <c r="A8" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
+      <c r="B8" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
     </row>
     <row r="9" ht="28.5" spans="1:11">
-      <c r="A9" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" s="45" t="s">
-        <v>127</v>
-      </c>
-      <c r="F9" s="26" t="s">
+      <c r="A9" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="B9" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
+      <c r="D9" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="66" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
     </row>
     <row r="10" ht="114" spans="1:11">
-      <c r="A10" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="26" t="s">
+      <c r="A10" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="45"/>
+    </row>
+    <row r="11" ht="28.5" spans="1:11">
+      <c r="A11" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="45"/>
+    </row>
+    <row r="12" ht="28.5" spans="1:11">
+      <c r="A12" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="F10" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="G10" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-    </row>
-    <row r="11" ht="28.5" spans="1:11">
-      <c r="A11" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="G11" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-    </row>
-    <row r="12" ht="28.5" spans="1:11">
-      <c r="A12" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
     </row>
     <row r="13" ht="71.25" spans="1:11">
-      <c r="A13" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>144</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="G13" s="32" t="s">
+      <c r="A13" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
+      <c r="B13" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
     </row>
     <row r="14" spans="1:11">
       <c r="B14" s="7"/>
@@ -3395,14 +3941,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="30.8833333333333" style="15" customWidth="1"/>
+    <col min="2" max="2" width="30.8833333333333" style="61" customWidth="1"/>
     <col min="3" max="3" width="45.25" customWidth="1"/>
     <col min="4" max="4" width="30.875" customWidth="1"/>
     <col min="5" max="5" width="59.9916666666667" customWidth="1"/>
@@ -3415,174 +3961,174 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" spans="1:11">
-      <c r="A1" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="B1" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="C1" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="D1" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="E1" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="16" t="s">
+      <c r="F1" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="G1" s="18" t="s">
         <v>95</v>
       </c>
+      <c r="H1" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="2" ht="69" customHeight="1" spans="1:11">
-      <c r="A2" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="D2" s="32" t="s">
+      <c r="A2" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="B2" s="62" t="s">
         <v>150</v>
       </c>
-      <c r="F2" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="G2" s="20" t="s">
+      <c r="C2" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
+      <c r="D2" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="63" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="3" ht="142.5" spans="1:11">
-      <c r="A3" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="G3" s="20" t="s">
+      <c r="A3" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
+      <c r="B3" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
     </row>
     <row r="4" ht="42.75" spans="1:11">
-      <c r="A4" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="F4" s="14" t="s">
+      <c r="A4" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="B4" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
+      <c r="D4" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
     </row>
     <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="F5" s="14" t="s">
+      <c r="A5" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="B5" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
+      <c r="D5" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
     </row>
     <row r="6" ht="42.75" spans="1:11">
-      <c r="A6" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="E6" s="20" t="s">
+      <c r="A6" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="B6" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="D6" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
+      <c r="E6" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
     </row>
     <row r="7" spans="1:11">
       <c r="B7"/>
@@ -3623,7 +4169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K35"/>
@@ -3635,7 +4181,7 @@
     <col min="4" max="4" width="38.3833333333333" customWidth="1"/>
     <col min="5" max="5" width="53.025" style="3" customWidth="1"/>
     <col min="6" max="6" width="24.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="72.85" style="22" customWidth="1"/>
+    <col min="7" max="7" width="72.85" style="41" customWidth="1"/>
     <col min="8" max="8" width="19.2916666666667" style="12" customWidth="1"/>
     <col min="9" max="9" width="7.75" customWidth="1"/>
     <col min="10" max="10" width="7.125" customWidth="1"/>
@@ -3643,569 +4189,569 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:11">
-      <c r="A1" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" s="23" t="s">
+      <c r="A1" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="B1" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="C1" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="D1" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="E1" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="23" t="s">
+      <c r="F1" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="G1" s="43" t="s">
         <v>95</v>
       </c>
+      <c r="H1" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="42" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="2" ht="18" spans="1:11">
-      <c r="A2" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
+      <c r="A2" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
     </row>
     <row r="3" ht="114" spans="1:11">
-      <c r="A3" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="B3" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="D3" s="32" t="s">
+      <c r="A3" s="45" t="s">
         <v>175</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="B3" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="F3" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="G3" s="33" t="s">
+      <c r="C3" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
+      <c r="D3" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="E3" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="F3" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="H3" s="49"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
     </row>
     <row r="4" ht="42.75" spans="1:11">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="B4" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
+      <c r="E4" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="H4" s="49"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
     </row>
     <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="29" t="s">
+      <c r="A5" s="45" t="s">
         <v>185</v>
       </c>
-      <c r="H5" s="30"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
+      <c r="B5" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="F5" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="H5" s="49"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
     </row>
     <row r="6" ht="42.75" spans="1:11">
-      <c r="A6" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="G6" s="29" t="s">
+      <c r="A6" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="H6" s="30"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
+      <c r="B6" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="H6" s="49"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
     </row>
     <row r="7" ht="42.75" spans="1:11">
-      <c r="A7" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>191</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="29" t="s">
+      <c r="A7" s="45" t="s">
         <v>193</v>
       </c>
-      <c r="H7" s="30"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
+      <c r="B7" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="H7" s="49"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
     </row>
     <row r="8" ht="42.75" spans="1:11">
-      <c r="A8" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="34" t="s">
+      <c r="A8" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="53" t="s">
         <v>195</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="F8" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="G8" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="H8" s="38"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="38"/>
+      <c r="F8" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="H8" s="57"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="57"/>
     </row>
     <row r="9" ht="42.75" spans="1:11">
-      <c r="A9" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="H9" s="38"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
+      <c r="A9" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="F9" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G9" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" ht="42.75" spans="1:11">
-      <c r="A10" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>201</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>202</v>
-      </c>
-      <c r="F10" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="G10" s="37" t="s">
+      <c r="A10" s="45" t="s">
         <v>203</v>
       </c>
-      <c r="H10" s="38"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="38"/>
+      <c r="B10" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>205</v>
+      </c>
+      <c r="F10" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="H10" s="57"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="58"/>
+      <c r="K10" s="57"/>
     </row>
     <row r="11" ht="42.75" spans="1:11">
-      <c r="A11" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>205</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="F11" s="40" t="s">
+      <c r="A11" s="45" t="s">
         <v>207</v>
       </c>
-      <c r="G11" s="41" t="s">
+      <c r="B11" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="53" t="s">
         <v>208</v>
       </c>
-      <c r="H11" s="38"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="38"/>
+      <c r="D11" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="F11" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="G11" s="60" t="s">
+        <v>211</v>
+      </c>
+      <c r="H11" s="57"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
+      <c r="K11" s="57"/>
     </row>
     <row r="12" ht="57" spans="1:11">
-      <c r="A12" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C12" s="34" t="s">
+      <c r="A12" s="45" t="s">
+        <v>212</v>
+      </c>
+      <c r="B12" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="D12" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="E12" s="55" t="s">
+        <v>215</v>
+      </c>
+      <c r="F12" s="59" t="s">
         <v>210</v>
       </c>
-      <c r="D12" s="36" t="s">
-        <v>211</v>
-      </c>
-      <c r="E12" s="36" t="s">
-        <v>212</v>
-      </c>
-      <c r="F12" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="H12" s="38"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="38"/>
+      <c r="G12" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="H12" s="57"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="58"/>
+      <c r="K12" s="57"/>
     </row>
     <row r="13" ht="57" spans="1:11">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>218</v>
+      </c>
+      <c r="D13" s="55" t="s">
         <v>214</v>
       </c>
-      <c r="B13" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="D13" s="36" t="s">
-        <v>211</v>
-      </c>
-      <c r="E13" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="F13" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="G13" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="H13" s="38"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="38"/>
+      <c r="E13" s="55" t="s">
+        <v>219</v>
+      </c>
+      <c r="F13" s="54" t="s">
+        <v>220</v>
+      </c>
+      <c r="G13" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="H13" s="57"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="57"/>
     </row>
     <row r="14" ht="57" spans="1:11">
-      <c r="A14" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="E14" s="36" t="s">
+      <c r="A14" s="45" t="s">
         <v>222</v>
       </c>
-      <c r="F14" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="G14" s="37" t="s">
+      <c r="B14" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="H14" s="38"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="38"/>
+      <c r="D14" s="55" t="s">
+        <v>224</v>
+      </c>
+      <c r="E14" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="F14" s="59" t="s">
+        <v>144</v>
+      </c>
+      <c r="G14" s="56" t="s">
+        <v>226</v>
+      </c>
+      <c r="H14" s="57"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="57"/>
     </row>
     <row r="15" ht="42.75" spans="1:11">
-      <c r="A15" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="F15" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="G15" s="37" t="s">
+      <c r="A15" s="45" t="s">
         <v>227</v>
       </c>
-      <c r="H15" s="38"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="38"/>
+      <c r="B15" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="D15" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="56" t="s">
+        <v>230</v>
+      </c>
+      <c r="H15" s="57"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="57"/>
     </row>
     <row r="16" ht="42.75" spans="1:11">
-      <c r="A16" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>229</v>
-      </c>
-      <c r="D16" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>230</v>
-      </c>
-      <c r="F16" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="G16" s="37" t="s">
+      <c r="A16" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="H16" s="38"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="38"/>
+      <c r="B16" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>232</v>
+      </c>
+      <c r="D16" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="F16" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G16" s="56" t="s">
+        <v>234</v>
+      </c>
+      <c r="H16" s="57"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="57"/>
     </row>
     <row r="17" ht="42.75" spans="1:11">
-      <c r="A17" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C17" s="34" t="s">
+      <c r="A17" s="45" t="s">
+        <v>235</v>
+      </c>
+      <c r="B17" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="D17" s="55" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" s="53" t="s">
         <v>233</v>
       </c>
-      <c r="D17" s="36" t="s">
-        <v>234</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>230</v>
-      </c>
-      <c r="F17" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="G17" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="38"/>
+      <c r="F17" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" s="60" t="s">
+        <v>238</v>
+      </c>
+      <c r="H17" s="57"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="57"/>
     </row>
     <row r="18" ht="42.75" spans="1:11">
-      <c r="A18" s="26" t="s">
-        <v>236</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="D18" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>238</v>
-      </c>
-      <c r="F18" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="G18" s="37" t="s">
+      <c r="A18" s="45" t="s">
         <v>239</v>
       </c>
-      <c r="H18" s="38"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="38"/>
+      <c r="B18" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="55" t="s">
+        <v>241</v>
+      </c>
+      <c r="F18" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" s="56" t="s">
+        <v>242</v>
+      </c>
+      <c r="H18" s="57"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="57"/>
     </row>
     <row r="19" s="12" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A19" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C19" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="F19" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="G19" s="37" t="s">
+      <c r="A19" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="H19" s="38"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="38"/>
+      <c r="B19" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="D19" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>245</v>
+      </c>
+      <c r="F19" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" s="56" t="s">
+        <v>246</v>
+      </c>
+      <c r="H19" s="57"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="57"/>
     </row>
     <row r="20" s="12" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A20" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="F20" s="35" t="s">
+      <c r="A20" s="45" t="s">
         <v>247</v>
       </c>
-      <c r="G20" s="41" t="s">
+      <c r="B20" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="55" t="s">
         <v>248</v>
       </c>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="38"/>
+      <c r="D20" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="F20" s="54" t="s">
+        <v>250</v>
+      </c>
+      <c r="G20" s="60" t="s">
+        <v>251</v>
+      </c>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
     </row>
     <row r="21" customFormat="1" ht="71.25" spans="1:11">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="45" t="s">
+        <v>252</v>
+      </c>
+      <c r="B21" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>253</v>
+      </c>
+      <c r="D21" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="55" t="s">
         <v>249</v>
       </c>
-      <c r="B21" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="F21" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="G21" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="H21" s="30" t="s">
-        <v>253</v>
-      </c>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
+      <c r="F21" s="54" t="s">
+        <v>254</v>
+      </c>
+      <c r="G21" s="48" t="s">
+        <v>255</v>
+      </c>
+      <c r="H21" s="49" t="s">
+        <v>256</v>
+      </c>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
     </row>
     <row r="22" spans="1:11">
       <c r="C22"/>
@@ -4314,528 +4860,1218 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD36"/>
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="13.125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="25.875" style="33" customWidth="1"/>
+    <col min="3" max="3" width="32.625" style="32" customWidth="1"/>
+    <col min="4" max="4" width="30.875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="42.35" style="32" customWidth="1"/>
+    <col min="6" max="6" width="15.2916666666667" style="32" customWidth="1"/>
+    <col min="7" max="7" width="86.6" style="32" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="32" customWidth="1"/>
+    <col min="9" max="9" width="7.75" style="32" customWidth="1"/>
+    <col min="10" max="10" width="7.125" style="32" customWidth="1"/>
+    <col min="11" max="11" width="10.875" style="32" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="31" customFormat="1" ht="15" spans="1:11">
+      <c r="A1" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="34" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" s="31" customFormat="1" spans="1:11">
+      <c r="A2" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+    </row>
+    <row r="3" s="31" customFormat="1" ht="128.25" spans="1:11">
+      <c r="A3" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="39" t="s">
+        <v>262</v>
+      </c>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+    </row>
+    <row r="4" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A4" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F4" s="37" t="str">
+        <f>SUBSTITUTE(MID(C4,22,30),"'","")</f>
+        <v>About Us</v>
+      </c>
+      <c r="G4" s="37" t="str">
+        <f>"Should navigate user to "&amp;MID(C4,22,30)&amp;". A proper text/information should display on this page"</f>
+        <v>Should navigate user to 'About Us'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+    </row>
+    <row r="5" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A5" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>267</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F5" s="37" t="str">
+        <f t="shared" ref="F5:F18" si="0">SUBSTITUTE(MID(C5,22,30),"'","")</f>
+        <v>Delivery Information</v>
+      </c>
+      <c r="G5" s="37" t="str">
+        <f>"Should navigate user to "&amp;MID(C5,22,30)&amp;". A proper text/information should display on this page"</f>
+        <v>Should navigate user to 'Delivery Information'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+    </row>
+    <row r="6" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A6" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F6" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Privacy Policy</v>
+      </c>
+      <c r="G6" s="37" t="str">
+        <f>"Should navigate user to "&amp;MID(C6,22,30)&amp;". A proper text/information should display on this page"</f>
+        <v>Should navigate user to 'Privacy Policy'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+    </row>
+    <row r="7" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A7" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F7" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Term &amp; Conditions</v>
+      </c>
+      <c r="G7" s="37" t="str">
+        <f t="shared" ref="G7:G18" si="1">"Should navigate user to "&amp;MID(C7,22,30)&amp;". A proper text/information should display on this page"</f>
+        <v>Should navigate user to 'Term &amp; Conditions'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+    </row>
+    <row r="8" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A8" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F8" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Contact Us</v>
+      </c>
+      <c r="G8" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Contact Us'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+    </row>
+    <row r="9" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A9" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F9" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v> Returns</v>
+      </c>
+      <c r="G9" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to ' Returns'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+    </row>
+    <row r="10" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A10" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F10" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Site Map</v>
+      </c>
+      <c r="G10" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Site Map'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+    </row>
+    <row r="11" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A11" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>281</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F11" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Brands</v>
+      </c>
+      <c r="G11" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Brands'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+    </row>
+    <row r="12" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A12" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>284</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F12" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Gift Voucher</v>
+      </c>
+      <c r="G12" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Gift Voucher'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+    </row>
+    <row r="13" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A13" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="B13" s="38" t="s">
+        <v>287</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>288</v>
+      </c>
+      <c r="D13" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F13" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Affiliates</v>
+      </c>
+      <c r="G13" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Affiliates'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+    </row>
+    <row r="14" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A14" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F14" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Specials</v>
+      </c>
+      <c r="G14" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Specials'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="37"/>
+    </row>
+    <row r="15" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A15" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>293</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="D15" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F15" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>My Account</v>
+      </c>
+      <c r="G15" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'My Account'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+    </row>
+    <row r="16" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A16" s="37" t="s">
+        <v>295</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>296</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>297</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F16" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Order History</v>
+      </c>
+      <c r="G16" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Order History'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="37"/>
+    </row>
+    <row r="17" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A17" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F17" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Wish List</v>
+      </c>
+      <c r="G17" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Wish List'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+    </row>
+    <row r="18" s="31" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A18" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="F18" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v>Newletter</v>
+      </c>
+      <c r="G18" s="37" t="str">
+        <f t="shared" si="1"/>
+        <v>Should navigate user to 'Newletter'. A proper text/information should display on this page</v>
+      </c>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="B19" s="40"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="B20" s="40"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="B21" s="40"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="B22" s="40"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="B23" s="40"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="B24" s="40"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="B25" s="40"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="B26" s="40"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="B27" s="40"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="B28" s="40"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="B29" s="40"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="B30" s="40"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="B31" s="40"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="B32" s="40"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="40"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="40"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="40"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:K2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="25.875" style="15" customWidth="1"/>
-    <col min="3" max="3" width="32.625" customWidth="1"/>
-    <col min="4" max="4" width="30.875" customWidth="1"/>
-    <col min="5" max="5" width="42.35" customWidth="1"/>
-    <col min="6" max="6" width="15.2916666666667" customWidth="1"/>
-    <col min="7" max="7" width="86.6" customWidth="1"/>
+    <col min="2" max="2" width="28.5" style="14" customWidth="1"/>
+    <col min="3" max="3" width="46.375" customWidth="1"/>
+    <col min="4" max="4" width="34.375" customWidth="1"/>
+    <col min="5" max="5" width="61.625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="28.75" style="16" customWidth="1"/>
+    <col min="7" max="7" width="56.25" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
     <col min="9" max="9" width="7.75" customWidth="1"/>
     <col min="10" max="10" width="7.125" customWidth="1"/>
     <col min="11" max="11" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="14" customFormat="1" ht="15" spans="1:11">
-      <c r="A1" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" s="16" t="s">
+    <row r="1" ht="15" spans="1:11">
+      <c r="A1" s="17" t="s">
         <v>89</v>
       </c>
+      <c r="B1" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>92</v>
+      </c>
       <c r="E1" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" ht="18" spans="1:11">
+      <c r="A2" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" s="14" customFormat="1" spans="1:11">
-      <c r="A2" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="18"/>
-    </row>
-    <row r="3" s="14" customFormat="1" ht="128.25" spans="1:11">
-      <c r="A3" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="4" s="14" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A4" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F4" s="14" t="str">
-        <f>SUBSTITUTE(MID(C4,22,30),"'","")</f>
-        <v>About Us</v>
-      </c>
-      <c r="G4" s="14" t="str">
-        <f>"Should navigate user to "&amp;MID(C4,22,30)&amp;". A proper text/information should display on this page"</f>
-        <v>Should navigate user to 'About Us'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="5" s="14" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A5" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F5" s="14" t="str">
-        <f t="shared" ref="F5:F18" si="0">SUBSTITUTE(MID(C5,22,30),"'","")</f>
-        <v>Delivery Information</v>
-      </c>
-      <c r="G5" s="14" t="str">
-        <f>"Should navigate user to "&amp;MID(C5,22,30)&amp;". A proper text/information should display on this page"</f>
-        <v>Should navigate user to 'Delivery Information'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="6" s="14" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A6" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F6" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Privacy Policy</v>
-      </c>
-      <c r="G6" s="14" t="str">
-        <f>"Should navigate user to "&amp;MID(C6,22,30)&amp;". A proper text/information should display on this page"</f>
-        <v>Should navigate user to 'Privacy Policy'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="7" s="14" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A7" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F7" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Term &amp; Conditions</v>
-      </c>
-      <c r="G7" s="14" t="str">
-        <f t="shared" ref="G7:G18" si="1">"Should navigate user to "&amp;MID(C7,22,30)&amp;". A proper text/information should display on this page"</f>
-        <v>Should navigate user to 'Term &amp; Conditions'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="8" s="14" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A8" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F8" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Contact Us</v>
-      </c>
-      <c r="G8" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Should navigate user to 'Contact Us'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="9" s="14" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A9" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F9" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v> Returns</v>
-      </c>
-      <c r="G9" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Should navigate user to ' Returns'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="10" s="14" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A10" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F10" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Site Map</v>
-      </c>
-      <c r="G10" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Should navigate user to 'Site Map'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="11" s="14" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A11" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F11" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Brands</v>
-      </c>
-      <c r="G11" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Should navigate user to 'Brands'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="12" s="14" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A12" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F12" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Gift Voucher</v>
-      </c>
-      <c r="G12" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Should navigate user to 'Gift Voucher'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="13" s="14" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A13" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F13" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Affiliates</v>
-      </c>
-      <c r="G13" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Should navigate user to 'Affiliates'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="14" s="14" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A14" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F14" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Specials</v>
-      </c>
-      <c r="G14" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Should navigate user to 'Specials'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="15" s="14" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A15" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F15" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>My Account</v>
-      </c>
-      <c r="G15" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Should navigate user to 'My Account'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="16" s="14" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A16" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>294</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F16" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Order History</v>
-      </c>
-      <c r="G16" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Should navigate user to 'Order History'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="17" s="14" customFormat="1" ht="42.75" spans="1:7">
-      <c r="A17" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>296</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>297</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F17" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Wish List</v>
-      </c>
-      <c r="G17" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Should navigate user to 'Wish List'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="18" s="14" customFormat="1" ht="42.75" spans="1:7">
-      <c r="A18" s="14" t="s">
-        <v>298</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>300</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F18" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v>Newletter</v>
-      </c>
-      <c r="G18" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Should navigate user to 'Newletter'. A proper text/information should display on this page</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="B19" s="21"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="B20" s="21"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="B21" s="21"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="B22" s="21"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="B23" s="21"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="B24" s="21"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="B25" s="21"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="B26" s="21"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="B27" s="21"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="B28" s="21"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="B29" s="21"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="B30" s="21"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="B31" s="21"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="B32" s="21"/>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="21"/>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="21"/>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="21"/>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="21"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="24"/>
+    </row>
+    <row r="3" ht="57" spans="1:11">
+      <c r="A3" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+    </row>
+    <row r="4" ht="57" spans="1:11">
+      <c r="A4" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+    </row>
+    <row r="5" ht="57" spans="1:11">
+      <c r="A5" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+    </row>
+    <row r="6" ht="57" spans="1:11">
+      <c r="A6" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>321</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>322</v>
+      </c>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+    </row>
+    <row r="7" ht="57" spans="1:11">
+      <c r="A7" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+    </row>
+    <row r="8" ht="57" spans="1:11">
+      <c r="A8" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>330</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+    </row>
+    <row r="9" ht="57" spans="1:11">
+      <c r="A9" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>334</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>335</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+    </row>
+    <row r="10" ht="57" spans="1:11">
+      <c r="A10" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>335</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+    </row>
+    <row r="11" ht="57" spans="1:11">
+      <c r="A11" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>342</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>344</v>
+      </c>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+    </row>
+    <row r="12" ht="57" spans="1:11">
+      <c r="A12" s="25" t="s">
+        <v>345</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>346</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>347</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>348</v>
+      </c>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+    </row>
+    <row r="13" ht="57" spans="1:11">
+      <c r="A13" s="25" t="s">
+        <v>349</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>351</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+    </row>
+    <row r="14" ht="57" spans="1:11">
+      <c r="A14" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+    </row>
+    <row r="15" ht="57" spans="1:11">
+      <c r="A15" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>359</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>360</v>
+      </c>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+    </row>
+    <row r="16" ht="57" spans="1:11">
+      <c r="A16" s="25" t="s">
+        <v>361</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>362</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>363</v>
+      </c>
+      <c r="F16" s="84" t="s">
+        <v>364</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+    </row>
+    <row r="17" ht="57" spans="1:11">
+      <c r="A17" s="25" t="s">
+        <v>366</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>367</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>368</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:XFD2"/>
+    <mergeCell ref="A2:K2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A2:K2" location="Scenario!A13" display="Test Scenario"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K15"/>
@@ -4856,42 +6092,42 @@
   <sheetData>
     <row r="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:11">
       <c r="A2" t="s">
-        <v>301</v>
+        <v>18</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="12"/>
@@ -4943,147 +6179,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:XFD4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
-  <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="31.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="30.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="34.75" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.625" customWidth="1"/>
-    <col min="7" max="7" width="64.875" customWidth="1"/>
-    <col min="8" max="8" width="13.375" customWidth="1"/>
-    <col min="9" max="9" width="7.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
-      <c r="A1" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:11">
-      <c r="A2" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" ht="42.75" spans="1:11">
-      <c r="A3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="G3" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="4" ht="42.75" spans="1:11">
-      <c r="A4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" t="s">
-        <v>312</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:XFD2"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A2:XFD2" location="Scenario!A7" display="&lt;&lt;Test Scenario"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/manual test/Open cert/OpenCartFrontend.xlsx
+++ b/manual test/Open cert/OpenCartFrontend.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26580" windowHeight="11580" firstSheet="1" activeTab="6"/>
+    <workbookView windowHeight="12180" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Version" sheetId="10" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="Header" sheetId="4" r:id="rId5"/>
     <sheet name="Footer" sheetId="7" r:id="rId6"/>
     <sheet name="Product Pages" sheetId="8" r:id="rId7"/>
-    <sheet name="Product Listings" sheetId="9" r:id="rId8"/>
+    <sheet name="Shopping Cart page" sheetId="11" r:id="rId8"/>
     <sheet name="Register" sheetId="5" r:id="rId9"/>
     <sheet name="Currency" sheetId="2" r:id="rId10"/>
   </sheets>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="516">
   <si>
     <t>Version</t>
   </si>
@@ -65,6 +65,15 @@
     <t>* 1.0 create test scenario/test case only from FRS only</t>
   </si>
   <si>
+    <t>Status :</t>
+  </si>
+  <si>
+    <t>working</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
     <t>Test Scenario ID</t>
   </si>
   <si>
@@ -80,6 +89,9 @@
     <t>Number of Test Cases</t>
   </si>
   <si>
+    <t>defect</t>
+  </si>
+  <si>
     <t>Note</t>
   </si>
   <si>
@@ -167,138 +179,132 @@
     <t>TS013</t>
   </si>
   <si>
-    <t>Validate the working of 'Slideshow' functionality</t>
+    <t>Validate the working of 'Checkout' functionality</t>
   </si>
   <si>
     <t>TS014</t>
   </si>
   <si>
-    <t>Validate the working of 'Checkout' functionality</t>
+    <t>Validate the working of 'My Account' functionality</t>
   </si>
   <si>
     <t>TS015</t>
   </si>
   <si>
-    <t>Validate the working of 'My Account' functionality</t>
+    <t>Validate the working of 'My Account &gt; Account Information' functionality</t>
   </si>
   <si>
     <t>TS016</t>
   </si>
   <si>
-    <t>Validate the working of 'My Account &gt; Account Information' functionality</t>
+    <t>Validate the working of 'My Account &gt; Change Password' functionality</t>
   </si>
   <si>
     <t>TS017</t>
   </si>
   <si>
-    <t>Validate the working of 'My Account &gt; Change Password' functionality</t>
+    <t>Validate the working of 'My Account Address Book' functionality</t>
   </si>
   <si>
     <t>TS018</t>
   </si>
   <si>
-    <t>Validate the working of 'My Account Address Book' functionality</t>
+    <t>Validate the working of 'My Order &gt; Order History' functionality</t>
   </si>
   <si>
     <t>TS019</t>
   </si>
   <si>
-    <t>Validate the working of 'My Order &gt; Order History' functionality</t>
+    <t>Validate the working of 'My Orders &gt; Order Information' functionality</t>
   </si>
   <si>
     <t>TS020</t>
   </si>
   <si>
-    <t>Validate the working of 'My Orders &gt; Order Information' functionality</t>
+    <t>Validate the working of 'My Orders &gt; Product Returns' functionality</t>
   </si>
   <si>
     <t>TS021</t>
   </si>
   <si>
-    <t>Validate the working of 'My Orders &gt; Product Returns' functionality</t>
+    <t>Validate the working of 'My Order &gt; Downloads' functionality</t>
   </si>
   <si>
     <t>TS022</t>
   </si>
   <si>
-    <t>Validate the working of 'My Order &gt; Downloads' functionality</t>
+    <t>Validate the working of 'My Orders &gt; Reward Points' functionality</t>
   </si>
   <si>
     <t>TS023</t>
   </si>
   <si>
-    <t>Validate the working of 'My Orders &gt; Reward Points' functionality</t>
+    <t>Validate the working of 'My Orders &gt; Returned Request' functionality</t>
   </si>
   <si>
     <t>TS024</t>
   </si>
   <si>
-    <t>Validate the working of 'My Orders &gt; Returned Request' functionality</t>
+    <t>Validate the working of 'My Order &gt; Your Transactions' functionality</t>
   </si>
   <si>
     <t>TS025</t>
   </si>
   <si>
-    <t>Validate the working of 'My Order &gt; Your Transactions' functionality</t>
+    <t>Validate the working of 'My Order &gt; Recurring Payments' functionality</t>
   </si>
   <si>
     <t>TS026</t>
   </si>
   <si>
-    <t>Validate the working of 'My Order &gt; Recurring Payments' functionality</t>
+    <t>Validate the working of 'Affiliate' functionality</t>
   </si>
   <si>
     <t>TS027</t>
   </si>
   <si>
-    <t>Validate the working of 'Affiliate' functionality</t>
+    <t>Validate the working of 'Newsletter' functionality</t>
   </si>
   <si>
     <t>TS028</t>
   </si>
   <si>
-    <t>Validate the working of 'Newsletter' functionality</t>
+    <t>Validate the working of 'Contact Us' functionality</t>
   </si>
   <si>
     <t>TS029</t>
   </si>
   <si>
-    <t>Validate the working of 'Contact Us' functionality</t>
+    <t>Validate the working of 'Gift' functionality</t>
   </si>
   <si>
     <t>TS030</t>
   </si>
   <si>
-    <t>Validate the working of 'Gift' functionality</t>
+    <t>Validate the working of 'Special Offer' functionality</t>
   </si>
   <si>
     <t>TS031</t>
   </si>
   <si>
-    <t>Validate the working of 'Special Offer' functionality</t>
+    <t>Validate the working of 'Header' options' functionality</t>
   </si>
   <si>
     <t>TS032</t>
   </si>
   <si>
-    <t>Validate the working of 'Header' options' functionality</t>
+    <t>Validate the working of 'Top Menu' options' functionality</t>
   </si>
   <si>
     <t>TS033</t>
   </si>
   <si>
-    <t>Validate the working of 'Top Menu' options' functionality</t>
+    <t>Validate the working of 'Footer' options' functionality</t>
   </si>
   <si>
     <t>TS034</t>
   </si>
   <si>
-    <t>Validate the working of 'Footer' options' functionality</t>
-  </si>
-  <si>
-    <t>TS035</t>
-  </si>
-  <si>
     <t>Validate the Application functionality for different currency' functionality</t>
   </si>
   <si>
@@ -338,11 +344,10 @@
     <t>&lt;&lt;Test Scenario</t>
   </si>
   <si>
+    <t>Current status :</t>
+  </si>
+  <si>
     <t>TC_HP_001</t>
-  </si>
-  <si>
-    <t>(TS012)
-Validate the working of 'Home page' functionality</t>
   </si>
   <si>
     <t>Validate top menu</t>
@@ -518,10 +523,6 @@
     <t>TC_TM_01</t>
   </si>
   <si>
-    <t>(TS_032)
-Validate the working of 'Top Menu' options' functionality</t>
-  </si>
-  <si>
     <t>Validate top menu visibility on any page</t>
   </si>
   <si>
@@ -1259,6 +1260,435 @@
   </si>
   <si>
     <t>Should display a required fied or 'please write a review' message</t>
+  </si>
+  <si>
+    <t>TC_PP_016</t>
+  </si>
+  <si>
+    <t>Validate category listing product</t>
+  </si>
+  <si>
+    <t>Open application,
+Select Category from 'top menu'</t>
+  </si>
+  <si>
+    <t>1. Validate category page(Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Should display selection of products based on category</t>
+  </si>
+  <si>
+    <t>TC_PP_017</t>
+  </si>
+  <si>
+    <t>Validate category listing product - 'Category'</t>
+  </si>
+  <si>
+    <t>1. Validate category page displayed corectly (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Should display the following elements :
+Parent category tab on the left side of the screen that list sub-category underneath</t>
+  </si>
+  <si>
+    <t>TC_PP_018</t>
+  </si>
+  <si>
+    <t>Validate sub-category functionality</t>
+  </si>
+  <si>
+    <t>1. Click on selected sub-category - &lt;Refer test data&gt;
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Sub categoty : Mac</t>
+  </si>
+  <si>
+    <t>Product list should change based on selected sub-category</t>
+  </si>
+  <si>
+    <t>TC_PP_019</t>
+  </si>
+  <si>
+    <t>Validate sub-category functionality - empty</t>
+  </si>
+  <si>
+    <t>1. Click on selected  sub-category - &lt;Refer test data&gt;
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Sub categoty : Software</t>
+  </si>
+  <si>
+    <t>Product list should display message 'There is no product in this section'</t>
+  </si>
+  <si>
+    <t>TC_PP_020</t>
+  </si>
+  <si>
+    <t>Validate displayed preference - listing type option</t>
+  </si>
+  <si>
+    <t>1. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>there are 2 type avialable by 'list' or 'grid'</t>
+  </si>
+  <si>
+    <t>TC_PP_021</t>
+  </si>
+  <si>
+    <t>Validate displayed preference - listing type selection</t>
+  </si>
+  <si>
+    <t>1. Select display type - &lt;Refer test data&gt;
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>display type : list</t>
+  </si>
+  <si>
+    <t>Product list should change displayed type to list</t>
+  </si>
+  <si>
+    <t>TC_PP_022</t>
+  </si>
+  <si>
+    <t>Validate displayed preference - sorting option</t>
+  </si>
+  <si>
+    <t>1. Click on sorting dropdown box
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>there are option for sorting as following : by name, price, rating, model</t>
+  </si>
+  <si>
+    <t>TC_PP_023</t>
+  </si>
+  <si>
+    <t>Validate displayed preference - sorting selection</t>
+  </si>
+  <si>
+    <t>1. Click on sorting dropdown box
+2. Select sorting type - &lt;Refer test data&gt;
+3. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Sorting by : Price</t>
+  </si>
+  <si>
+    <t>Product list should displayed and ordering by price</t>
+  </si>
+  <si>
+    <t>TC_PP_024</t>
+  </si>
+  <si>
+    <t>Validate displayed preference - displaying number</t>
+  </si>
+  <si>
+    <t>1. Click on show dropdown box
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Amount of product displayed can change from 15 up to 100</t>
+  </si>
+  <si>
+    <t>TC_PP_025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate displayed preference - displaying number selection </t>
+  </si>
+  <si>
+    <t>1. Click on show dropdown box
+2. Select amount for displaying the product - &lt;Refer test data&gt;
+3. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Amount : 15</t>
+  </si>
+  <si>
+    <t>Amount of product displayed should be maximum at 15</t>
+  </si>
+  <si>
+    <t>TC_PP_026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validate displayed preference - displaying number selection product not enough </t>
+  </si>
+  <si>
+    <t>Amount : 100</t>
+  </si>
+  <si>
+    <t>The remaining amount should not shown at all</t>
+  </si>
+  <si>
+    <t>TC_PP_027</t>
+  </si>
+  <si>
+    <t>Validate access to product comparison page</t>
+  </si>
+  <si>
+    <t>Defect</t>
+  </si>
+  <si>
+    <t>FRS do not specify how to enter compare product page</t>
+  </si>
+  <si>
+    <t>TC_PP_028</t>
+  </si>
+  <si>
+    <t>Validate product comparison page elements</t>
+  </si>
+  <si>
+    <t>Open application,Open compare product page</t>
+  </si>
+  <si>
+    <t>The product comparison page should displayed 2 or more product compare to each other. the specifications that has to compare will contain these following:
+product name, product image, price, features(show differently depend on product type) with a button to add product to cart or remove from compare list</t>
+  </si>
+  <si>
+    <t>TC_PP_029</t>
+  </si>
+  <si>
+    <t>Validate product comparison add product to cart</t>
+  </si>
+  <si>
+    <t>1.Click 'Add to Cart' button underneath selected product - &lt;Refer test data&gt;
+2.Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Process to next page and show a successful added to cart message with a button for return to home page</t>
+  </si>
+  <si>
+    <t>TC_PP_030</t>
+  </si>
+  <si>
+    <t>Validate product comparison remove product from comparison list</t>
+  </si>
+  <si>
+    <t>1.Click 'Remove' button underneath selected product - &lt;Refer test data&gt;
+2.Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>MacBook Air</t>
+  </si>
+  <si>
+    <t>Selected product should be removed from product comparison page</t>
+  </si>
+  <si>
+    <t>TC_SC_001</t>
+  </si>
+  <si>
+    <t>Validate access to shopping cart page</t>
+  </si>
+  <si>
+    <t>Open application,
+Added product to the cart</t>
+  </si>
+  <si>
+    <t>1. Click 'Shopping Cart' in header
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Redirect user to 'Shopping Cart Page'</t>
+  </si>
+  <si>
+    <t>TC_SC_002</t>
+  </si>
+  <si>
+    <t>Validate shopping cart page content - cart</t>
+  </si>
+  <si>
+    <t>Open application,
+Added product to the cart,
+Open shopping cart page</t>
+  </si>
+  <si>
+    <t>Shopping cart page should show following element correctly :
+header, image, product name, model, quantity, unit price, total</t>
+  </si>
+  <si>
+    <t>TC_SC_003</t>
+  </si>
+  <si>
+    <t>Validate cart functionality  - change quantity of the product</t>
+  </si>
+  <si>
+    <t>1. Change quantity -&lt;Refer test data&gt;
+2. Click refresh button next to quality 
+3. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Total price , Eco Tax, VAT should be updated</t>
+  </si>
+  <si>
+    <t>TC_SC_004</t>
+  </si>
+  <si>
+    <t>Validate cart functionality - increase quantity of the product - out of stock</t>
+  </si>
+  <si>
+    <t>Quantity : 200</t>
+  </si>
+  <si>
+    <t>Should show a message "your quantity of the product is more than the current stock please lower the quantity or cancel the order"</t>
+  </si>
+  <si>
+    <t>TC_SC_005</t>
+  </si>
+  <si>
+    <t>Validate cart functionality - decrease quantity of the product - lower than 1</t>
+  </si>
+  <si>
+    <t>Quantity : 0</t>
+  </si>
+  <si>
+    <t>Should not accpet the number 0 in quantity or remove item from cart</t>
+  </si>
+  <si>
+    <t>TC_SC_006</t>
+  </si>
+  <si>
+    <t>Validate cart functionality - remove item</t>
+  </si>
+  <si>
+    <t>1. Click 'X' symbol next to refresh button
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>The product should be removed from cart</t>
+  </si>
+  <si>
+    <t>TC_SC_007</t>
+  </si>
+  <si>
+    <t>Validate shopping cart page content - option</t>
+  </si>
+  <si>
+    <t>User can use these following option :
+apply coupon, estimating shipping &amp; taxes, use gift certificate</t>
+  </si>
+  <si>
+    <t>TC_SC_008</t>
+  </si>
+  <si>
+    <t>Validate coupon tab show</t>
+  </si>
+  <si>
+    <t>1. Click on 'Use coupon code' (Validate ER-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. coupon tab should appear </t>
+  </si>
+  <si>
+    <t>TC_SC_009</t>
+  </si>
+  <si>
+    <t>Validate coupon tab hidden</t>
+  </si>
+  <si>
+    <t>Open application,
+Added product to the cart,
+Open shopping cart page,
+Open a coupon tab</t>
+  </si>
+  <si>
+    <t>1. coupon tab should hidden</t>
+  </si>
+  <si>
+    <t>TC_SC_010</t>
+  </si>
+  <si>
+    <t>Validate valid coupon</t>
+  </si>
+  <si>
+    <t>TC_SC_011</t>
+  </si>
+  <si>
+    <t>Validate invalid coupon</t>
+  </si>
+  <si>
+    <t>TC_SC_012</t>
+  </si>
+  <si>
+    <t>Validate estimate &amp; shipping taxes show</t>
+  </si>
+  <si>
+    <t>TC_SC_013</t>
+  </si>
+  <si>
+    <t>Validate estimate &amp; shipping taxes hidden</t>
+  </si>
+  <si>
+    <t>TC_SC_014</t>
+  </si>
+  <si>
+    <t>Validate use gift certificate shown</t>
+  </si>
+  <si>
+    <t>TC_SC_015</t>
+  </si>
+  <si>
+    <t>Validate use gift certificate hidden</t>
+  </si>
+  <si>
+    <t>TC_SC_016</t>
+  </si>
+  <si>
+    <t>Validate valid gift certificate</t>
+  </si>
+  <si>
+    <t>TC_SC_017</t>
+  </si>
+  <si>
+    <t>Validate invalid gift certificate</t>
+  </si>
+  <si>
+    <t>TC_SC_018</t>
+  </si>
+  <si>
+    <t>Validate shopping cart page content - detailed price</t>
+  </si>
+  <si>
+    <t>User can confirm the price details on the item which show under the extra option which contain:
+Sub-total, Eco Tax, Vat, Total</t>
+  </si>
+  <si>
+    <t>TC_SC_019</t>
+  </si>
+  <si>
+    <t>Validate shopping cart page content - detailed price calculation</t>
+  </si>
+  <si>
+    <t>Result of detailed price should shown correctly</t>
+  </si>
+  <si>
+    <t>TC_SC_020</t>
+  </si>
+  <si>
+    <t>Continue Shopping' button</t>
+  </si>
+  <si>
+    <t>TC_SC_021</t>
+  </si>
+  <si>
+    <t>Checkout' button</t>
+  </si>
+  <si>
+    <t>TC_SC_022</t>
+  </si>
+  <si>
+    <t>TC_SC_023</t>
+  </si>
+  <si>
+    <t>TC_SC_024</t>
+  </si>
+  <si>
+    <t>TC_SC_025</t>
+  </si>
+  <si>
+    <t>TC_SC_026</t>
   </si>
   <si>
     <t>TC_CF_001</t>
@@ -1307,7 +1737,7 @@
     <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;฿&quot;* #,##0_-;\-&quot;฿&quot;* #,##0_-;_-&quot;฿&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1356,22 +1786,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="TH Sarabun PSK"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="TH Sarabun PSK"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
       <name val="TH Sarabun PSK"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1497,7 +1920,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1512,7 +1935,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1703,7 +2144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1724,52 +2165,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1896,7 +2291,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1905,122 +2303,119 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2066,36 +2461,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2114,71 +2503,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2204,24 +2569,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2231,50 +2578,53 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2328,7 +2678,21 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="19">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2522,25 +2886,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="totalRow" dxfId="6"/>
+      <tableStyleElement type="firstColumn" dxfId="5"/>
+      <tableStyleElement type="lastColumn" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
+      <tableStyleElement type="pageFieldValues" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2817,46 +3181,46 @@
   </cols>
   <sheetData>
     <row r="3" ht="15" spans="2:3">
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="82" t="s">
+      <c r="C3" s="67" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:3">
-      <c r="B4" s="83">
+      <c r="B4" s="67">
         <v>1</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="67" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="15" spans="2:3">
-      <c r="B5" s="83">
+      <c r="B5" s="67">
         <v>2</v>
       </c>
-      <c r="C5" s="83"/>
+      <c r="C5" s="67"/>
     </row>
     <row r="6" ht="15" spans="2:3">
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
     </row>
     <row r="7" ht="15" spans="2:3">
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
     </row>
     <row r="8" ht="15" spans="2:3">
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
     </row>
     <row r="9" ht="15" spans="2:3">
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
     </row>
     <row r="10" ht="15" spans="2:3">
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2885,42 +3249,42 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -2929,48 +3293,48 @@
     </row>
     <row r="3" ht="42.75" spans="1:11">
       <c r="A3" t="s">
-        <v>370</v>
+        <v>505</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>371</v>
+        <v>506</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>372</v>
+        <v>507</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>373</v>
+        <v>508</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>374</v>
+        <v>509</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>375</v>
+        <v>510</v>
       </c>
       <c r="G3" t="s">
-        <v>376</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" ht="42.75" spans="1:11">
       <c r="A4" t="s">
-        <v>377</v>
+        <v>512</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>371</v>
+        <v>506</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>378</v>
+        <v>513</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>373</v>
+        <v>508</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>379</v>
+        <v>514</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G4" t="s">
-        <v>380</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -2988,7 +3352,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
@@ -2996,524 +3360,729 @@
     <col min="3" max="3" width="69.75" customWidth="1"/>
     <col min="4" max="4" width="10.375" customWidth="1"/>
     <col min="5" max="5" width="21" style="1" customWidth="1"/>
-    <col min="6" max="6" width="48.625" customWidth="1"/>
-    <col min="8" max="8" width="69.75" customWidth="1"/>
+    <col min="6" max="6" width="14.5583333333333" customWidth="1"/>
+    <col min="7" max="7" width="48.625" customWidth="1"/>
+    <col min="9" max="9" width="69.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="18" spans="1:9">
+    <row r="2" ht="18" spans="1:10">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-    </row>
-    <row r="3" ht="18" spans="1:9">
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+    </row>
+    <row r="3" ht="18" spans="1:10">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="F3" s="41"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
       <c r="B4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="70" t="s">
+      <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="70" t="s">
+      <c r="E4" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="70" t="s">
+    </row>
+    <row r="5" spans="1:10">
+      <c r="E5" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="70" t="s">
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="70" t="s">
+      <c r="B6" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="70" t="s">
+      <c r="C6" s="56" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" ht="18" spans="1:9">
-      <c r="A7" s="11" t="s">
+      <c r="D6" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E6" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="F6" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="1">
+      <c r="G6" s="56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="18" spans="1:10">
+      <c r="A7" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="59">
         <v>0</v>
       </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" ht="18" spans="1:9">
-      <c r="A8" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="71" t="s">
+      <c r="F7" s="17"/>
+      <c r="G7" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" ht="18" spans="1:10">
+      <c r="A8" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="1">
+      <c r="C8" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="59">
         <v>0</v>
       </c>
-      <c r="F8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="71" t="s">
+      <c r="F8" s="17"/>
+      <c r="G8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="1">
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="17"/>
+      <c r="E9" s="59">
         <v>0</v>
       </c>
-      <c r="F9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="71" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="F9" s="17"/>
+      <c r="G9" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="17"/>
+      <c r="E10" s="59">
         <v>0</v>
       </c>
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="71" t="s">
+      <c r="F10" s="17"/>
+      <c r="G10" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="17"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="17"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+    </row>
+    <row r="13" ht="18" spans="1:10">
+      <c r="A13" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="60" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="60"/>
+      <c r="E13" s="61">
+        <f>COUNTA('Product Pages'!A3:A202)</f>
+        <v>30</v>
+      </c>
+      <c r="F13" s="17">
+        <f>COUNTIF('Product Pages'!J3:J9999,"Defect")</f>
+        <v>1</v>
+      </c>
+      <c r="G13" s="17"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="17"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="58" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="59">
+        <f>COUNTA('Shopping Cart page'!A1:A999)</f>
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="71" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" ht="18" spans="1:9">
-      <c r="A13" s="11" t="s">
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+    </row>
+    <row r="18" customFormat="1" spans="1:7">
+      <c r="A18" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="72"/>
-      <c r="E13" s="73">
-        <f>COUNTA('Product Pages'!A3:A200)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="71" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="71" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="71" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="71" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" spans="1:5">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="74" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="75" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="76"/>
-      <c r="E18" s="77">
+      <c r="C18" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64">
         <f>COUNTA(HomePage!A3:A9998)</f>
         <v>11</v>
       </c>
-    </row>
-    <row r="19" customFormat="1" spans="1:5">
-      <c r="A19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="74" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="71" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
+      <c r="F18" s="17">
+        <f>COUNTIF(HomePage!J3:J9999,"Defect")</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="17"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="71" t="s">
+      <c r="B19" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="58" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
+      <c r="D19" s="17"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="71" t="s">
+      <c r="B20" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="58" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
+      <c r="D20" s="17"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="71" t="s">
+      <c r="B21" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="58" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
+      <c r="D21" s="17"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B24" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="71" t="s">
+      <c r="B22" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="58" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
+      <c r="D22" s="17"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="71" t="s">
+      <c r="B23" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="58" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" t="s">
+      <c r="D23" s="17"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="B26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="71" t="s">
+      <c r="B24" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="58" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
+      <c r="D24" s="17"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="71" t="s">
+      <c r="B25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="58" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
+      <c r="D25" s="17"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="71" t="s">
+      <c r="B26" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="58" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
+      <c r="D26" s="17"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="71" t="s">
+      <c r="B27" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="58" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
+      <c r="D27" s="17"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C30" s="71" t="s">
+      <c r="B28" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="58" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" t="s">
+      <c r="D28" s="17"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B31" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="71" t="s">
+      <c r="B29" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="58" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" t="s">
+      <c r="D29" s="17"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B32" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="71" t="s">
+      <c r="B30" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="58" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" t="s">
+      <c r="D30" s="17"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B33" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="78" t="s">
+      <c r="B31" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="58" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" t="s">
+      <c r="D31" s="17"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B34" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="78" t="s">
+      <c r="B32" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="62" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" t="s">
+      <c r="D32" s="17"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B35" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="78" t="s">
+      <c r="B33" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="62" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" t="s">
+      <c r="D33" s="17"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B36" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" s="78" t="s">
+      <c r="B34" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="62" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" t="s">
+      <c r="D34" s="17"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B37" t="s">
-        <v>26</v>
-      </c>
-      <c r="C37" s="71" t="s">
+      <c r="B35" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="62" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="38" customFormat="1" spans="1:5">
-      <c r="A38" t="s">
+      <c r="D35" s="17"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B38" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="C38" s="72" t="s">
+      <c r="B36" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="D38" s="72"/>
-      <c r="E38" s="77">
+      <c r="D36" s="17"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+    </row>
+    <row r="37" customFormat="1" spans="1:7">
+      <c r="A37" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="58" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="63" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" s="64"/>
+      <c r="E37" s="64">
         <f>COUNTA(Header!A3:A200)</f>
         <v>19</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" t="s">
-        <v>82</v>
-      </c>
-      <c r="B39" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" s="72" t="s">
-        <v>83</v>
-      </c>
-      <c r="D39" s="72"/>
-      <c r="E39" s="73">
-        <f>COUNTA('Top Menu'!A2:A200)</f>
+      <c r="F37" s="17">
+        <f>COUNTIF(Header!J3:J9999,"Defect")</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="17"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="60"/>
+      <c r="E38" s="61">
+        <f>COUNTA('Top Menu'!A3:A201)</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" t="s">
-        <v>84</v>
-      </c>
-      <c r="B40" t="s">
-        <v>26</v>
-      </c>
-      <c r="C40" s="72" t="s">
-        <v>85</v>
-      </c>
-      <c r="D40" s="72"/>
-      <c r="E40" s="73">
+      <c r="F38" s="17">
+        <f>COUNTIF('Top Menu'!J3:J9999,"defect")</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="17"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="D39" s="60"/>
+      <c r="E39" s="61">
         <f>COUNTA(Footer!A3:A200)</f>
         <v>16</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" t="s">
-        <v>86</v>
-      </c>
-      <c r="B41" t="s">
-        <v>26</v>
-      </c>
-      <c r="C41" s="71" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="80"/>
-      <c r="B42" s="80"/>
-      <c r="C42" s="80"/>
-      <c r="D42" s="80" t="s">
+      <c r="F39" s="17">
+        <f>COUNTIF(Footer!J3:J9999,"defect")</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="17"/>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E42" s="81">
-        <f>SUM(E7:E41)</f>
-        <v>66</v>
+      <c r="B40" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C40" s="58" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="17"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="36"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="E41" s="66">
+        <f>SUM(E7:E40)</f>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
   </mergeCells>
+  <conditionalFormatting sqref="C13:E13">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>'Product Pages'!$D$2="complete"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>'Product Pages'!$D$2="working"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:E17">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>'Shopping Cart page'!$D$2="working"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>'Shopping Cart page'!$D$2="complete"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:D18">
+    <cfRule type="expression" dxfId="1" priority="18">
+      <formula>HomePage!$C$2="working"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="17">
+      <formula>HomePage!$C$2="complete"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E18">
+    <cfRule type="expression" dxfId="0" priority="19">
+      <formula>HomePage!$C$2="complete"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="20">
+      <formula>HomePage!$C$2="working"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C37:D37">
+    <cfRule type="expression" dxfId="0" priority="11">
+      <formula>'Top Menu'!$D$2="complete"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="12">
+      <formula>Header!$D$2="working"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E37">
+    <cfRule type="expression" dxfId="0" priority="13">
+      <formula>'Top Menu'!$D$2="complete"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="14">
+      <formula>Header!$D$2="working"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C38:E38">
+    <cfRule type="expression" dxfId="0" priority="15">
+      <formula>'Top Menu'!$D$2="Complete"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="16">
+      <formula>'Top Menu'!$D$2="Working"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C39:E39">
+    <cfRule type="expression" dxfId="0" priority="9">
+      <formula>Footer!$D$2="complete"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="10">
+      <formula>Footer!$D$2="working"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A7" location="Register!A1" display="TS001"/>
     <hyperlink ref="B2" r:id="rId1" display="https://demo.opencart.com/" tooltip="https://demo.opencart.com/"/>
     <hyperlink ref="A8" location="TS002!A1" display="TS002"/>
     <hyperlink ref="B3" r:id="rId2" display="https://drive.google.com/drive/folders/1nBs25k9jTb06qrV-5fTC75gtPOR6uW4V"/>
     <hyperlink ref="A18" location="HomePage!A1" display="TS012"/>
-    <hyperlink ref="A38" location="Header!A1" display="TS032"/>
-    <hyperlink ref="A39" location="'Top Menu'!A1" display="TS033"/>
+    <hyperlink ref="A37" location="Header!A1" display="TS031"/>
+    <hyperlink ref="A38" location="'Top Menu'!A1" display="TS032"/>
     <hyperlink ref="A13" location="'Product Pages'!A1" display="TS007"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3527,8 +4096,8 @@
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="40.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5666666666667" customWidth="1"/>
+    <col min="2" max="2" width="49" style="1" customWidth="1"/>
     <col min="3" max="3" width="44.5" style="8" customWidth="1"/>
     <col min="4" max="4" width="30.875" customWidth="1"/>
     <col min="5" max="5" width="52.375" style="8" customWidth="1"/>
@@ -3541,351 +4110,358 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
-      <c r="A1" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="43" t="s">
+      <c r="A1" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="B1" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="C1" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="D1" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="E1" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="F1" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="42" t="s">
+      <c r="G1" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="K1" s="42" t="s">
+      <c r="H1" s="15" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="2" s="11" customFormat="1" ht="18" spans="1:11">
-      <c r="A2" s="44" t="s">
+      <c r="I1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
+      <c r="K1" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" ht="18" spans="1:11">
+      <c r="A2" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" ht="142.5" spans="1:11">
-      <c r="A3" s="45" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="46" t="s">
+      <c r="A3" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="B3" s="24" t="str">
+        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <v>(TS012)Validate the working of 'Home page' functionality</v>
+      </c>
+      <c r="C3" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="D3" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="E3" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
+      <c r="F3" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
     </row>
     <row r="4" ht="71.25" spans="1:11">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="24" t="str">
+        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <v>(TS012)Validate the working of 'Home page' functionality</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+    </row>
+    <row r="5" ht="42.75" spans="1:11">
+      <c r="A5" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="24" t="str">
+        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <v>(TS012)Validate the working of 'Home page' functionality</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="49" t="s">
-        <v>109</v>
-      </c>
-      <c r="F4" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-    </row>
-    <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="B5" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="D5" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="49" t="s">
-        <v>114</v>
-      </c>
-      <c r="F5" s="45" t="s">
+      <c r="G5" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="24" t="str">
+        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <v>(TS012)Validate the working of 'Home page' functionality</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G5" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-    </row>
-    <row r="6" ht="28.5" spans="1:11">
-      <c r="A6" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="B6" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="F6" s="45" t="s">
+      <c r="E6" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="24" t="str">
+        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <v>(TS012)Validate the working of 'Home page' functionality</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G6" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-    </row>
-    <row r="7" ht="28.5" spans="1:11">
-      <c r="A7" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="49" t="s">
-        <v>122</v>
-      </c>
-      <c r="F7" s="45" t="s">
+      <c r="E7" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+    </row>
+    <row r="8" ht="28.5" spans="1:11">
+      <c r="A8" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="24" t="str">
+        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <v>(TS012)Validate the working of 'Home page' functionality</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G7" s="46" t="s">
-        <v>123</v>
-      </c>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-    </row>
-    <row r="8" ht="28.5" spans="1:11">
-      <c r="A8" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="49" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" s="45" t="s">
+      <c r="E8" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+    </row>
+    <row r="9" ht="28.5" spans="1:11">
+      <c r="A9" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="24" t="str">
+        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <v>(TS012)Validate the working of 'Home page' functionality</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G8" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-    </row>
-    <row r="9" ht="28.5" spans="1:11">
-      <c r="A9" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="B9" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="45" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="66" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="G9" s="46" t="s">
+      <c r="E9" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
+      <c r="F9" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
     </row>
     <row r="10" ht="114" spans="1:11">
-      <c r="A10" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" s="45" t="s">
+      <c r="A10" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="24" t="str">
+        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <v>(TS012)Validate the working of 'Home page' functionality</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="24" t="str">
+        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <v>(TS012)Validate the working of 'Home page' functionality</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+    </row>
+    <row r="12" ht="28.5" spans="1:11">
+      <c r="A12" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="24" t="str">
+        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <v>(TS012)Validate the working of 'Home page' functionality</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="D10" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="F10" s="45" t="s">
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+    </row>
+    <row r="13" ht="71.25" spans="1:11">
+      <c r="A13" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" s="24" t="str">
+        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <v>(TS012)Validate the working of 'Home page' functionality</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="D13" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="67" t="s">
-        <v>136</v>
-      </c>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-    </row>
-    <row r="11" ht="28.5" spans="1:11">
-      <c r="A11" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="D11" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="F11" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="G11" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-    </row>
-    <row r="12" ht="28.5" spans="1:11">
-      <c r="A12" s="45" t="s">
-        <v>141</v>
-      </c>
-      <c r="B12" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="G12" s="46" t="s">
-        <v>132</v>
-      </c>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-    </row>
-    <row r="13" ht="71.25" spans="1:11">
-      <c r="A13" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="B13" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="D13" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="F13" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="G13" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
+      <c r="E13" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
     </row>
     <row r="14" spans="1:11">
       <c r="B14" s="7"/>
@@ -3932,8 +4508,12 @@
       <c r="B27" s="7"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2">
+      <formula1>"working,complete"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A2:XFD2" location="Scenario!A8" display="&lt;&lt;Test Scenario"/>
     <hyperlink ref="A2" location="Scenario!A18" display="&lt;&lt;Test Scenario"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3944,11 +4524,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="30.8833333333333" style="61" customWidth="1"/>
+    <col min="2" max="2" width="30.8833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="45.25" customWidth="1"/>
     <col min="4" max="4" width="30.875" customWidth="1"/>
     <col min="5" max="5" width="59.9916666666667" customWidth="1"/>
@@ -3960,178 +4540,207 @@
     <col min="11" max="11" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" spans="1:11">
-      <c r="A1" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="18" t="s">
+    <row r="1" ht="15" spans="1:11">
+      <c r="A1" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="E1" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="F1" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="17" t="s">
+      <c r="G1" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="H1" s="15" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="2" ht="69" customHeight="1" spans="1:11">
-      <c r="A2" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="B2" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="C2" s="25" t="s">
+      <c r="I1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" ht="37" customHeight="1" spans="1:11">
+      <c r="A2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="42"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+    </row>
+    <row r="3" ht="69" customHeight="1" spans="1:11">
+      <c r="A3" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="B3" s="24" t="str">
+        <f>"("&amp;Scenario!A38&amp;")"&amp;" 
+"&amp;Scenario!C38</f>
+        <v>(TS032) 
+Validate the working of 'Top Menu' options' functionality</v>
+      </c>
+      <c r="C3" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="63" t="s">
+      <c r="D3" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="E3" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+    </row>
+    <row r="4" ht="128.25" spans="1:11">
+      <c r="A4" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="24" t="str">
+        <f>"("&amp;Scenario!A38&amp;")"&amp;" 
+"&amp;Scenario!C38</f>
+        <v>(TS032) 
+Validate the working of 'Top Menu' options' functionality</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-    </row>
-    <row r="3" ht="142.5" spans="1:11">
-      <c r="A3" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="B3" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="D3" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="F3" s="25" t="s">
+      <c r="E4" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+    </row>
+    <row r="5" ht="42.75" spans="1:11">
+      <c r="A5" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="24" t="str">
+        <f>"("&amp;Scenario!A38&amp;")"&amp;" 
+"&amp;Scenario!C38</f>
+        <v>(TS032) 
+Validate the working of 'Top Menu' options' functionality</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G3" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-    </row>
-    <row r="4" ht="42.75" spans="1:11">
-      <c r="A4" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="F4" s="25" t="s">
+      <c r="E5" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="F5" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-    </row>
-    <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="25" t="s">
+      <c r="G5" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="B5" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="25" t="s">
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+    </row>
+    <row r="6" ht="42.75" spans="1:11">
+      <c r="A6" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="D5" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="27" t="s">
+      <c r="B6" s="24" t="str">
+        <f>"("&amp;Scenario!A38&amp;")"&amp;" 
+"&amp;Scenario!C38</f>
+        <v>(TS032) 
+Validate the working of 'Top Menu' options' functionality</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="D6" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="F6" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-    </row>
-    <row r="6" ht="42.75" spans="1:11">
-      <c r="A6" s="25" t="s">
+      <c r="G6" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="B6" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="25" t="s">
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+    </row>
+    <row r="7" ht="42.75" spans="1:11">
+      <c r="A7" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="B7" s="24" t="str">
+        <f>"("&amp;Scenario!A38&amp;")"&amp;" 
+"&amp;Scenario!C38</f>
+        <v>(TS032) 
+Validate the working of 'Top Menu' options' functionality</v>
+      </c>
+      <c r="C7" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="D7" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="E7" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="F7" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="B7"/>
+      <c r="G7" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
     </row>
     <row r="8" spans="1:11">
       <c r="B8"/>
@@ -4163,7 +4772,15 @@
     <row r="17" spans="2:2">
       <c r="B17"/>
     </row>
+    <row r="18" spans="2:2">
+      <c r="B18"/>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2">
+      <formula1>"working,complete"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -4181,7 +4798,7 @@
     <col min="4" max="4" width="38.3833333333333" customWidth="1"/>
     <col min="5" max="5" width="53.025" style="3" customWidth="1"/>
     <col min="6" max="6" width="24.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="72.85" style="41" customWidth="1"/>
+    <col min="7" max="7" width="72.85" style="22" customWidth="1"/>
     <col min="8" max="8" width="19.2916666666667" style="12" customWidth="1"/>
     <col min="9" max="9" width="7.75" customWidth="1"/>
     <col min="10" max="10" width="7.125" customWidth="1"/>
@@ -4189,569 +4806,573 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:11">
-      <c r="A1" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="43" t="s">
+      <c r="A1" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="B1" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="C1" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="D1" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="E1" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="F1" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="42" t="s">
+      <c r="G1" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="K1" s="42" t="s">
+      <c r="H1" s="16" t="s">
         <v>98</v>
       </c>
+      <c r="I1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="2" ht="18" spans="1:11">
-      <c r="A2" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
+      <c r="A2" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="23"/>
+      <c r="C2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="23"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
     </row>
     <row r="3" ht="114" spans="1:11">
-      <c r="A3" s="45" t="s">
-        <v>175</v>
-      </c>
-      <c r="B3" s="50" t="s">
+      <c r="A3" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="B3" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="C3" s="41" t="s">
         <v>178</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="D3" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="E3" s="42" t="s">
+        <v>180</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+    </row>
+    <row r="4" ht="42.75" spans="1:11">
+      <c r="A4" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="H4" s="25"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+    </row>
+    <row r="5" ht="42.75" spans="1:11">
+      <c r="A5" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G3" s="52" t="s">
-        <v>180</v>
-      </c>
-      <c r="H3" s="49"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-    </row>
-    <row r="4" ht="42.75" spans="1:11">
-      <c r="A4" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="C4" s="46" t="s">
-        <v>182</v>
-      </c>
-      <c r="D4" s="51" t="s">
-        <v>178</v>
-      </c>
-      <c r="E4" s="51" t="s">
-        <v>183</v>
-      </c>
-      <c r="F4" s="47" t="s">
+      <c r="E5" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="H5" s="25"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+    </row>
+    <row r="6" ht="42.75" spans="1:11">
+      <c r="A6" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="H4" s="49"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-    </row>
-    <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="B5" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>186</v>
-      </c>
-      <c r="D5" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>187</v>
-      </c>
-      <c r="F5" s="47" t="s">
+      <c r="E6" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="H6" s="25"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+    </row>
+    <row r="7" ht="42.75" spans="1:11">
+      <c r="A7" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D7" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="G5" s="48" t="s">
-        <v>188</v>
-      </c>
-      <c r="H5" s="49"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-    </row>
-    <row r="6" ht="42.75" spans="1:11">
-      <c r="A6" s="45" t="s">
-        <v>189</v>
-      </c>
-      <c r="B6" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>190</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="F6" s="47" t="s">
+      <c r="E7" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="H7" s="25"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+    </row>
+    <row r="8" ht="42.75" spans="1:11">
+      <c r="A8" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>199</v>
+      </c>
+      <c r="D8" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="G6" s="48" t="s">
-        <v>192</v>
-      </c>
-      <c r="H6" s="49"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-    </row>
-    <row r="7" ht="42.75" spans="1:11">
-      <c r="A7" s="45" t="s">
-        <v>193</v>
-      </c>
-      <c r="B7" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="C7" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="53" t="s">
-        <v>195</v>
-      </c>
-      <c r="F7" s="47" t="s">
+      <c r="E8" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="F8" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="H8" s="47"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="47"/>
+    </row>
+    <row r="9" ht="42.75" spans="1:11">
+      <c r="A9" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="D9" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="E9" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="H7" s="49"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-    </row>
-    <row r="8" ht="42.75" spans="1:11">
-      <c r="A8" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="B8" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="53" t="s">
-        <v>198</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="53" t="s">
-        <v>195</v>
-      </c>
-      <c r="F8" s="54" t="s">
+      <c r="F9" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="H9" s="47"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+    </row>
+    <row r="10" ht="42.75" spans="1:11">
+      <c r="A10" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="D10" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="G8" s="56" t="s">
-        <v>199</v>
-      </c>
-      <c r="H8" s="57"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="57"/>
-    </row>
-    <row r="9" ht="42.75" spans="1:11">
-      <c r="A9" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="B9" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="53" t="s">
-        <v>201</v>
-      </c>
-      <c r="D9" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="53" t="s">
-        <v>195</v>
-      </c>
-      <c r="F9" s="54" t="s">
+      <c r="E10" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>207</v>
+      </c>
+      <c r="H10" s="47"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="47"/>
+    </row>
+    <row r="11" ht="42.75" spans="1:11">
+      <c r="A11" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="G9" s="56" t="s">
-        <v>202</v>
-      </c>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-    </row>
-    <row r="10" ht="42.75" spans="1:11">
-      <c r="A10" s="45" t="s">
-        <v>203</v>
-      </c>
-      <c r="B10" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C10" s="53" t="s">
-        <v>204</v>
-      </c>
-      <c r="D10" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="53" t="s">
-        <v>205</v>
-      </c>
-      <c r="F10" s="54" t="s">
+      <c r="E11" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="F11" s="49" t="s">
+        <v>211</v>
+      </c>
+      <c r="G11" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="H11" s="47"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="47"/>
+    </row>
+    <row r="12" ht="57" spans="1:11">
+      <c r="A12" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>214</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" s="49" t="s">
+        <v>211</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>217</v>
+      </c>
+      <c r="H12" s="47"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="47"/>
+    </row>
+    <row r="13" ht="57" spans="1:11">
+      <c r="A13" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="F13" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="G13" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="H13" s="47"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="47"/>
+    </row>
+    <row r="14" ht="57" spans="1:11">
+      <c r="A14" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>224</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="H14" s="47"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="47"/>
+    </row>
+    <row r="15" ht="42.75" spans="1:11">
+      <c r="A15" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="D15" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="56" t="s">
-        <v>206</v>
-      </c>
-      <c r="H10" s="57"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="58"/>
-      <c r="K10" s="57"/>
-    </row>
-    <row r="11" ht="42.75" spans="1:11">
-      <c r="A11" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B11" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C11" s="53" t="s">
-        <v>208</v>
-      </c>
-      <c r="D11" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" s="55" t="s">
-        <v>209</v>
-      </c>
-      <c r="F11" s="59" t="s">
-        <v>210</v>
-      </c>
-      <c r="G11" s="60" t="s">
-        <v>211</v>
-      </c>
-      <c r="H11" s="57"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="57"/>
-    </row>
-    <row r="12" ht="57" spans="1:11">
-      <c r="A12" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C12" s="53" t="s">
-        <v>213</v>
-      </c>
-      <c r="D12" s="55" t="s">
-        <v>214</v>
-      </c>
-      <c r="E12" s="55" t="s">
-        <v>215</v>
-      </c>
-      <c r="F12" s="59" t="s">
-        <v>210</v>
-      </c>
-      <c r="G12" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="H12" s="57"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="57"/>
-    </row>
-    <row r="13" ht="57" spans="1:11">
-      <c r="A13" s="45" t="s">
-        <v>217</v>
-      </c>
-      <c r="B13" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C13" s="53" t="s">
-        <v>218</v>
-      </c>
-      <c r="D13" s="55" t="s">
-        <v>214</v>
-      </c>
-      <c r="E13" s="55" t="s">
-        <v>219</v>
-      </c>
-      <c r="F13" s="54" t="s">
-        <v>220</v>
-      </c>
-      <c r="G13" s="56" t="s">
-        <v>221</v>
-      </c>
-      <c r="H13" s="57"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="57"/>
-    </row>
-    <row r="14" ht="57" spans="1:11">
-      <c r="A14" s="45" t="s">
-        <v>222</v>
-      </c>
-      <c r="B14" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C14" s="53" t="s">
-        <v>223</v>
-      </c>
-      <c r="D14" s="55" t="s">
-        <v>224</v>
-      </c>
-      <c r="E14" s="55" t="s">
-        <v>225</v>
-      </c>
-      <c r="F14" s="59" t="s">
-        <v>144</v>
-      </c>
-      <c r="G14" s="56" t="s">
-        <v>226</v>
-      </c>
-      <c r="H14" s="57"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="57"/>
-    </row>
-    <row r="15" ht="42.75" spans="1:11">
-      <c r="A15" s="45" t="s">
-        <v>227</v>
-      </c>
-      <c r="B15" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="53" t="s">
-        <v>228</v>
-      </c>
-      <c r="D15" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="53" t="s">
-        <v>229</v>
-      </c>
-      <c r="F15" s="54" t="s">
+      <c r="E15" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="H15" s="47"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="47"/>
+    </row>
+    <row r="16" ht="42.75" spans="1:11">
+      <c r="A16" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>233</v>
+      </c>
+      <c r="D16" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="G15" s="56" t="s">
-        <v>230</v>
-      </c>
-      <c r="H15" s="57"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="57"/>
-    </row>
-    <row r="16" ht="42.75" spans="1:11">
-      <c r="A16" s="45" t="s">
-        <v>231</v>
-      </c>
-      <c r="B16" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C16" s="53" t="s">
-        <v>232</v>
-      </c>
-      <c r="D16" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" s="53" t="s">
-        <v>233</v>
-      </c>
-      <c r="F16" s="54" t="s">
+      <c r="E16" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="F16" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="H16" s="47"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="47"/>
+    </row>
+    <row r="17" ht="42.75" spans="1:11">
+      <c r="A17" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="F17" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="50" t="s">
+        <v>239</v>
+      </c>
+      <c r="H17" s="47"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="47"/>
+    </row>
+    <row r="18" ht="42.75" spans="1:11">
+      <c r="A18" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="D18" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="G16" s="56" t="s">
-        <v>234</v>
-      </c>
-      <c r="H16" s="57"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="57"/>
-    </row>
-    <row r="17" ht="42.75" spans="1:11">
-      <c r="A17" s="45" t="s">
-        <v>235</v>
-      </c>
-      <c r="B17" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C17" s="53" t="s">
-        <v>236</v>
-      </c>
-      <c r="D17" s="55" t="s">
-        <v>237</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>233</v>
-      </c>
-      <c r="F17" s="59" t="s">
+      <c r="E18" s="45" t="s">
+        <v>242</v>
+      </c>
+      <c r="F18" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="G18" s="46" t="s">
+        <v>243</v>
+      </c>
+      <c r="H18" s="47"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="47"/>
+    </row>
+    <row r="19" s="12" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A19" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="D19" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="G17" s="60" t="s">
-        <v>238</v>
-      </c>
-      <c r="H17" s="57"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="57"/>
-    </row>
-    <row r="18" ht="42.75" spans="1:11">
-      <c r="A18" s="45" t="s">
-        <v>239</v>
-      </c>
-      <c r="B18" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>240</v>
-      </c>
-      <c r="D18" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="55" t="s">
-        <v>241</v>
-      </c>
-      <c r="F18" s="59" t="s">
+      <c r="E19" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="F19" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="G19" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="H19" s="47"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="47"/>
+    </row>
+    <row r="20" s="12" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A20" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="B20" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C20" s="45" t="s">
+        <v>249</v>
+      </c>
+      <c r="D20" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="G18" s="56" t="s">
-        <v>242</v>
-      </c>
-      <c r="H18" s="57"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="57"/>
-    </row>
-    <row r="19" s="12" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A19" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="B19" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C19" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="D19" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" s="53" t="s">
-        <v>245</v>
-      </c>
-      <c r="F19" s="54" t="s">
+      <c r="E20" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="F20" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>252</v>
+      </c>
+      <c r="H20" s="47"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="47"/>
+    </row>
+    <row r="21" customFormat="1" ht="71.25" spans="1:11">
+      <c r="A21" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="B21" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="D21" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="G19" s="56" t="s">
-        <v>246</v>
-      </c>
-      <c r="H19" s="57"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="58"/>
-      <c r="K19" s="57"/>
-    </row>
-    <row r="20" s="12" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A20" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="B20" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C20" s="55" t="s">
-        <v>248</v>
-      </c>
-      <c r="D20" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" s="55" t="s">
-        <v>249</v>
-      </c>
-      <c r="F20" s="54" t="s">
+      <c r="E21" s="45" t="s">
         <v>250</v>
       </c>
-      <c r="G20" s="60" t="s">
-        <v>251</v>
-      </c>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-    </row>
-    <row r="21" customFormat="1" ht="71.25" spans="1:11">
-      <c r="A21" s="45" t="s">
-        <v>252</v>
-      </c>
-      <c r="B21" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>253</v>
-      </c>
-      <c r="D21" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" s="55" t="s">
-        <v>249</v>
-      </c>
-      <c r="F21" s="54" t="s">
-        <v>254</v>
-      </c>
-      <c r="G21" s="48" t="s">
+      <c r="F21" s="44" t="s">
         <v>255</v>
       </c>
-      <c r="H21" s="49" t="s">
+      <c r="G21" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
+      <c r="H21" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
     </row>
     <row r="22" spans="1:11">
       <c r="C22"/>
@@ -4852,6 +5473,11 @@
       <c r="H35"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2">
+      <formula1>"working,complete"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="A2" location="Scenario!A37" display="Test Scenario"/>
   </hyperlinks>
@@ -4866,590 +5492,596 @@
   <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" style="32" customWidth="1"/>
-    <col min="2" max="2" width="25.875" style="33" customWidth="1"/>
-    <col min="3" max="3" width="32.625" style="32" customWidth="1"/>
-    <col min="4" max="4" width="30.875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="42.35" style="32" customWidth="1"/>
-    <col min="6" max="6" width="15.2916666666667" style="32" customWidth="1"/>
-    <col min="7" max="7" width="86.6" style="32" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="32" customWidth="1"/>
-    <col min="9" max="9" width="7.75" style="32" customWidth="1"/>
-    <col min="10" max="10" width="7.125" style="32" customWidth="1"/>
-    <col min="11" max="11" width="10.875" style="32" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="32"/>
+    <col min="1" max="1" width="13.125" style="36" customWidth="1"/>
+    <col min="2" max="2" width="25.875" style="37" customWidth="1"/>
+    <col min="3" max="3" width="32.625" style="36" customWidth="1"/>
+    <col min="4" max="4" width="30.875" style="36" customWidth="1"/>
+    <col min="5" max="5" width="42.35" style="36" customWidth="1"/>
+    <col min="6" max="6" width="15.2916666666667" style="36" customWidth="1"/>
+    <col min="7" max="7" width="86.6" style="36" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="36" customWidth="1"/>
+    <col min="9" max="9" width="7.75" style="36" customWidth="1"/>
+    <col min="10" max="10" width="7.125" style="36" customWidth="1"/>
+    <col min="11" max="11" width="10.875" style="36" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" s="31" customFormat="1" ht="15" spans="1:11">
-      <c r="A1" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="35" t="s">
+    <row r="1" s="36" customFormat="1" ht="15" spans="1:11">
+      <c r="A1" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="B1" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="C1" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="D1" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="E1" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="F1" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="34" t="s">
+      <c r="G1" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="H1" s="15" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="2" s="31" customFormat="1" spans="1:11">
-      <c r="A2" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-    </row>
-    <row r="3" s="31" customFormat="1" ht="128.25" spans="1:11">
-      <c r="A3" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="B3" s="38" t="s">
+      <c r="I1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" s="36" customFormat="1" spans="1:11">
+      <c r="A2" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+    </row>
+    <row r="3" s="36" customFormat="1" ht="128.25" spans="1:11">
+      <c r="A3" s="23" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="B3" s="24" t="s">
         <v>259</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="C3" s="23" t="s">
         <v>260</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="D3" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="F3" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="G3" s="39" t="s">
+      <c r="E3" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-    </row>
-    <row r="4" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A4" s="37" t="s">
+      <c r="F3" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="B4" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C4" s="37" t="s">
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+    </row>
+    <row r="4" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A4" s="23" t="s">
         <v>264</v>
       </c>
-      <c r="D4" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E4" s="39" t="s">
+      <c r="B4" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" s="23" t="s">
         <v>265</v>
       </c>
-      <c r="F4" s="37" t="str">
+      <c r="D4" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F4" s="23" t="str">
         <f>SUBSTITUTE(MID(C4,22,30),"'","")</f>
         <v>About Us</v>
       </c>
-      <c r="G4" s="37" t="str">
+      <c r="G4" s="23" t="str">
         <f>"Should navigate user to "&amp;MID(C4,22,30)&amp;". A proper text/information should display on this page"</f>
         <v>Should navigate user to 'About Us'. A proper text/information should display on this page</v>
       </c>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-    </row>
-    <row r="5" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A5" s="37" t="s">
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+    </row>
+    <row r="5" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A5" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" s="25" t="s">
         <v>266</v>
       </c>
-      <c r="B5" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C5" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="D5" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F5" s="37" t="str">
+      <c r="F5" s="23" t="str">
         <f t="shared" ref="F5:F18" si="0">SUBSTITUTE(MID(C5,22,30),"'","")</f>
         <v>Delivery Information</v>
       </c>
-      <c r="G5" s="37" t="str">
+      <c r="G5" s="23" t="str">
         <f>"Should navigate user to "&amp;MID(C5,22,30)&amp;". A proper text/information should display on this page"</f>
         <v>Should navigate user to 'Delivery Information'. A proper text/information should display on this page</v>
       </c>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-    </row>
-    <row r="6" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A6" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C6" s="37" t="s">
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+    </row>
+    <row r="6" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A6" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="D6" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F6" s="37" t="str">
+      <c r="B6" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F6" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Privacy Policy</v>
       </c>
-      <c r="G6" s="37" t="str">
+      <c r="G6" s="23" t="str">
         <f>"Should navigate user to "&amp;MID(C6,22,30)&amp;". A proper text/information should display on this page"</f>
         <v>Should navigate user to 'Privacy Policy'. A proper text/information should display on this page</v>
       </c>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="37"/>
-    </row>
-    <row r="7" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A7" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C7" s="37" t="s">
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+    </row>
+    <row r="7" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A7" s="23" t="s">
         <v>271</v>
       </c>
-      <c r="D7" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E7" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F7" s="37" t="str">
+      <c r="B7" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F7" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Term &amp; Conditions</v>
       </c>
-      <c r="G7" s="37" t="str">
+      <c r="G7" s="23" t="str">
         <f t="shared" ref="G7:G18" si="1">"Should navigate user to "&amp;MID(C7,22,30)&amp;". A proper text/information should display on this page"</f>
         <v>Should navigate user to 'Term &amp; Conditions'. A proper text/information should display on this page</v>
       </c>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="37"/>
-    </row>
-    <row r="8" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A8" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C8" s="37" t="s">
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+    </row>
+    <row r="8" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A8" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="D8" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F8" s="37" t="str">
+      <c r="B8" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F8" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Contact Us</v>
       </c>
-      <c r="G8" s="37" t="str">
+      <c r="G8" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Contact Us'. A proper text/information should display on this page</v>
       </c>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-    </row>
-    <row r="9" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A9" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="B9" s="38" t="s">
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+    </row>
+    <row r="9" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A9" s="23" t="s">
         <v>275</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="B9" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="D9" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E9" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F9" s="37" t="str">
+      <c r="C9" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" s="23" t="str">
         <f t="shared" si="0"/>
         <v> Returns</v>
       </c>
-      <c r="G9" s="37" t="str">
+      <c r="G9" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to ' Returns'. A proper text/information should display on this page</v>
       </c>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-    </row>
-    <row r="10" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A10" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="B10" s="38" t="s">
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+    </row>
+    <row r="10" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A10" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="B10" s="24" t="s">
         <v>279</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F10" s="37" t="str">
+      <c r="C10" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F10" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Site Map</v>
       </c>
-      <c r="G10" s="37" t="str">
+      <c r="G10" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Site Map'. A proper text/information should display on this page</v>
       </c>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-    </row>
-    <row r="11" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A11" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="B11" s="38" t="s">
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+    </row>
+    <row r="11" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A11" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="B11" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="D11" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F11" s="37" t="str">
+      <c r="C11" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F11" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Brands</v>
       </c>
-      <c r="G11" s="37" t="str">
+      <c r="G11" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Brands'. A proper text/information should display on this page</v>
       </c>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
-    </row>
-    <row r="12" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A12" s="37" t="s">
-        <v>283</v>
-      </c>
-      <c r="B12" s="38" t="s">
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+    </row>
+    <row r="12" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A12" s="23" t="s">
         <v>284</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="B12" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F12" s="37" t="str">
+      <c r="C12" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F12" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Gift Voucher</v>
       </c>
-      <c r="G12" s="37" t="str">
+      <c r="G12" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Gift Voucher'. A proper text/information should display on this page</v>
       </c>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="37"/>
-    </row>
-    <row r="13" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A13" s="37" t="s">
-        <v>286</v>
-      </c>
-      <c r="B13" s="38" t="s">
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+    </row>
+    <row r="13" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A13" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="B13" s="24" t="s">
         <v>288</v>
       </c>
-      <c r="D13" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F13" s="37" t="str">
+      <c r="C13" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F13" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Affiliates</v>
       </c>
-      <c r="G13" s="37" t="str">
+      <c r="G13" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Affiliates'. A proper text/information should display on this page</v>
       </c>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="37"/>
-    </row>
-    <row r="14" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A14" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="B14" s="38" t="s">
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+    </row>
+    <row r="14" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A14" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="B14" s="24" t="s">
         <v>291</v>
       </c>
-      <c r="D14" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F14" s="37" t="str">
+      <c r="C14" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F14" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Specials</v>
       </c>
-      <c r="G14" s="37" t="str">
+      <c r="G14" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Specials'. A proper text/information should display on this page</v>
       </c>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="37"/>
-    </row>
-    <row r="15" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A15" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="B15" s="38" t="s">
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+    </row>
+    <row r="15" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A15" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="B15" s="24" t="s">
         <v>294</v>
       </c>
-      <c r="D15" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F15" s="37" t="str">
+      <c r="C15" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F15" s="23" t="str">
         <f t="shared" si="0"/>
         <v>My Account</v>
       </c>
-      <c r="G15" s="37" t="str">
+      <c r="G15" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'My Account'. A proper text/information should display on this page</v>
       </c>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="37"/>
-    </row>
-    <row r="16" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A16" s="37" t="s">
-        <v>295</v>
-      </c>
-      <c r="B16" s="38" t="s">
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+    </row>
+    <row r="16" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A16" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="B16" s="24" t="s">
         <v>297</v>
       </c>
-      <c r="D16" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F16" s="37" t="str">
+      <c r="C16" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F16" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Order History</v>
       </c>
-      <c r="G16" s="37" t="str">
+      <c r="G16" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Order History'. A proper text/information should display on this page</v>
       </c>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-    </row>
-    <row r="17" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A17" s="37" t="s">
-        <v>298</v>
-      </c>
-      <c r="B17" s="38" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+    </row>
+    <row r="17" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A17" s="23" t="s">
         <v>299</v>
       </c>
-      <c r="C17" s="37" t="s">
+      <c r="B17" s="24" t="s">
         <v>300</v>
       </c>
-      <c r="D17" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E17" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F17" s="37" t="str">
+      <c r="C17" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F17" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Wish List</v>
       </c>
-      <c r="G17" s="37" t="str">
+      <c r="G17" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Wish List'. A proper text/information should display on this page</v>
       </c>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-    </row>
-    <row r="18" s="31" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A18" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="B18" s="38" t="s">
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+    </row>
+    <row r="18" s="36" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A18" s="23" t="s">
         <v>302</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="B18" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="D18" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="F18" s="37" t="str">
+      <c r="C18" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="F18" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Newletter</v>
       </c>
-      <c r="G18" s="37" t="str">
+      <c r="G18" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Newletter'. A proper text/information should display on this page</v>
       </c>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="B19" s="40"/>
+      <c r="B19" s="38"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="B20" s="40"/>
+      <c r="B20" s="38"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="B21" s="40"/>
+      <c r="B21" s="38"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="B22" s="40"/>
+      <c r="B22" s="38"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="B23" s="40"/>
+      <c r="B23" s="38"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="B24" s="40"/>
+      <c r="B24" s="38"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="B25" s="40"/>
+      <c r="B25" s="38"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="B26" s="40"/>
+      <c r="B26" s="38"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="B27" s="40"/>
+      <c r="B27" s="38"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="B28" s="40"/>
+      <c r="B28" s="38"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="B29" s="40"/>
+      <c r="B29" s="38"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="B30" s="40"/>
+      <c r="B30" s="38"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="B31" s="40"/>
+      <c r="B31" s="38"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="B32" s="40"/>
+      <c r="B32" s="38"/>
     </row>
     <row r="33" spans="2:2">
-      <c r="B33" s="40"/>
+      <c r="B33" s="38"/>
     </row>
     <row r="34" spans="2:2">
-      <c r="B34" s="40"/>
+      <c r="B34" s="38"/>
     </row>
     <row r="35" spans="2:2">
-      <c r="B35" s="40"/>
+      <c r="B35" s="38"/>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" s="40"/>
+      <c r="B36" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:K2"/>
-  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2">
+      <formula1>"working,complete"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -5458,602 +6090,959 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="28.5" style="14" customWidth="1"/>
-    <col min="3" max="3" width="46.375" customWidth="1"/>
-    <col min="4" max="4" width="34.375" customWidth="1"/>
-    <col min="5" max="5" width="61.625" style="15" customWidth="1"/>
-    <col min="6" max="6" width="28.75" style="16" customWidth="1"/>
-    <col min="7" max="7" width="56.25" customWidth="1"/>
+    <col min="2" max="2" width="28.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="72.125" customWidth="1"/>
+    <col min="4" max="4" width="38.0833333333333" customWidth="1"/>
+    <col min="5" max="5" width="61.625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="28.75" style="22" customWidth="1"/>
+    <col min="7" max="7" width="64.75" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
     <col min="9" max="9" width="7.75" customWidth="1"/>
     <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
+    <col min="11" max="11" width="42.725" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:11">
-      <c r="A1" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="E1" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="F1" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="17" t="s">
+      <c r="G1" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="H1" s="15" t="s">
         <v>98</v>
       </c>
+      <c r="I1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="2" ht="18" spans="1:11">
-      <c r="A2" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="24"/>
+      <c r="A2" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2"/>
+      <c r="F2"/>
     </row>
     <row r="3" ht="57" spans="1:11">
-      <c r="A3" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="B3" s="26" t="s">
+      <c r="A3" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="B3" s="24" t="s">
         <v>306</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="C3" s="23" t="s">
         <v>307</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="D3" s="25" t="s">
         <v>308</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="E3" s="26" t="s">
         <v>309</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="F3" s="27" t="s">
         <v>310</v>
       </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
+      <c r="G3" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
     </row>
     <row r="4" ht="57" spans="1:11">
-      <c r="A4" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C4" s="25" t="s">
+      <c r="A4" s="23" t="s">
         <v>312</v>
       </c>
-      <c r="D4" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="E4" s="28" t="s">
+      <c r="B4" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="23" t="s">
         <v>313</v>
       </c>
-      <c r="F4" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="G4" s="27" t="s">
+      <c r="D4" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="E4" s="26" t="s">
         <v>314</v>
       </c>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
+      <c r="F4" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
     </row>
     <row r="5" ht="57" spans="1:11">
-      <c r="A5" s="25" t="s">
-        <v>315</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C5" s="25" t="s">
+      <c r="A5" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="D5" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="E5" s="27" t="s">
+      <c r="B5" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>317</v>
       </c>
-      <c r="F5" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="G5" s="25" t="s">
+      <c r="D5" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="E5" s="25" t="s">
         <v>318</v>
       </c>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
+      <c r="F5" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
     </row>
     <row r="6" ht="57" spans="1:11">
-      <c r="A6" s="25" t="s">
-        <v>319</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C6" s="25" t="s">
+      <c r="A6" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="D6" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="E6" s="28" t="s">
+      <c r="B6" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="G6" s="27" t="s">
+      <c r="D6" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="E6" s="26" t="s">
         <v>322</v>
       </c>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
+      <c r="F6" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
     </row>
     <row r="7" ht="57" spans="1:11">
-      <c r="A7" s="25" t="s">
-        <v>323</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C7" s="25" t="s">
+      <c r="A7" s="23" t="s">
         <v>324</v>
       </c>
-      <c r="D7" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="E7" s="27" t="s">
+      <c r="B7" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" s="23" t="s">
         <v>325</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="D7" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>326</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="F7" s="27" t="s">
         <v>327</v>
       </c>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
+      <c r="G7" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
     </row>
     <row r="8" ht="57" spans="1:11">
-      <c r="A8" s="25" t="s">
-        <v>328</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C8" s="25" t="s">
+      <c r="A8" s="23" t="s">
         <v>329</v>
       </c>
-      <c r="D8" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>325</v>
-      </c>
-      <c r="F8" s="30" t="s">
+      <c r="B8" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C8" s="23" t="s">
         <v>330</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="D8" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="F8" s="28" t="s">
         <v>331</v>
       </c>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
+      <c r="G8" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
     </row>
     <row r="9" ht="57" spans="1:11">
-      <c r="A9" s="25" t="s">
-        <v>332</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C9" s="25" t="s">
+      <c r="A9" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="B9" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C9" s="23" t="s">
         <v>334</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="D9" s="25" t="s">
         <v>335</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="G9" s="27" t="s">
+      <c r="E9" s="26" t="s">
         <v>336</v>
       </c>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
+      <c r="F9" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
     </row>
     <row r="10" ht="57" spans="1:11">
-      <c r="A10" s="25" t="s">
-        <v>337</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C10" s="25" t="s">
+      <c r="A10" s="23" t="s">
         <v>338</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="B10" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C10" s="23" t="s">
         <v>339</v>
       </c>
-      <c r="E10" s="28" t="s">
-        <v>335</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="G10" s="27" t="s">
+      <c r="D10" s="25" t="s">
         <v>340</v>
       </c>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
+      <c r="E10" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>341</v>
+      </c>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
     </row>
     <row r="11" ht="57" spans="1:11">
-      <c r="A11" s="25" t="s">
-        <v>341</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C11" s="25" t="s">
+      <c r="A11" s="23" t="s">
         <v>342</v>
       </c>
-      <c r="D11" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="E11" s="27" t="s">
+      <c r="B11" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C11" s="23" t="s">
         <v>343</v>
       </c>
-      <c r="F11" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="G11" s="25" t="s">
+      <c r="D11" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="E11" s="25" t="s">
         <v>344</v>
       </c>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
+      <c r="F11" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
     </row>
     <row r="12" ht="57" spans="1:11">
-      <c r="A12" s="25" t="s">
-        <v>345</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C12" s="25" t="s">
+      <c r="A12" s="23" t="s">
         <v>346</v>
       </c>
-      <c r="D12" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="E12" s="27" t="s">
+      <c r="B12" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C12" s="23" t="s">
         <v>347</v>
       </c>
-      <c r="F12" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="G12" s="25" t="s">
+      <c r="D12" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="E12" s="25" t="s">
         <v>348</v>
       </c>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
+      <c r="F12" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
     </row>
     <row r="13" ht="57" spans="1:11">
-      <c r="A13" s="25" t="s">
-        <v>349</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C13" s="25" t="s">
+      <c r="A13" s="23" t="s">
         <v>350</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="E13" s="27" t="s">
+      <c r="B13" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C13" s="23" t="s">
         <v>351</v>
       </c>
-      <c r="F13" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="G13" s="25" t="s">
+      <c r="D13" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="E13" s="25" t="s">
         <v>352</v>
       </c>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
+      <c r="F13" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
     </row>
     <row r="14" ht="57" spans="1:11">
-      <c r="A14" s="25" t="s">
-        <v>353</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C14" s="25" t="s">
+      <c r="A14" s="23" t="s">
         <v>354</v>
       </c>
-      <c r="D14" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="E14" s="27" t="s">
+      <c r="B14" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C14" s="23" t="s">
         <v>355</v>
       </c>
-      <c r="F14" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="G14" s="25" t="s">
+      <c r="D14" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="E14" s="25" t="s">
         <v>356</v>
       </c>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
+      <c r="F14" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
     </row>
     <row r="15" ht="57" spans="1:11">
-      <c r="A15" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C15" s="25" t="s">
+      <c r="A15" s="23" t="s">
         <v>358</v>
       </c>
-      <c r="D15" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="E15" s="28" t="s">
+      <c r="B15" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C15" s="23" t="s">
         <v>359</v>
       </c>
-      <c r="F15" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="G15" s="25" t="s">
+      <c r="D15" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="E15" s="26" t="s">
         <v>360</v>
       </c>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
+      <c r="F15" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
     </row>
     <row r="16" ht="57" spans="1:11">
-      <c r="A16" s="25" t="s">
-        <v>361</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C16" s="25" t="s">
+      <c r="A16" s="23" t="s">
         <v>362</v>
       </c>
-      <c r="D16" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="E16" s="27" t="s">
+      <c r="B16" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>363</v>
       </c>
-      <c r="F16" s="84" t="s">
+      <c r="D16" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="E16" s="25" t="s">
         <v>364</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="F16" s="68" t="s">
         <v>365</v>
       </c>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
+      <c r="G16" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
     </row>
     <row r="17" ht="57" spans="1:11">
-      <c r="A17" s="25" t="s">
-        <v>366</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C17" s="25" t="s">
+      <c r="A17" s="23" t="s">
         <v>367</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>307</v>
-      </c>
-      <c r="E17" s="27" t="s">
+      <c r="B17" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C17" s="23" t="s">
         <v>368</v>
       </c>
-      <c r="F17" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="G17" s="25" t="s">
+      <c r="D17" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>369</v>
       </c>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
-      <c r="F23"/>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="B24"/>
-      <c r="C24"/>
-      <c r="D24"/>
-      <c r="E24"/>
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27"/>
-      <c r="F27"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="B29"/>
-      <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="B31"/>
-      <c r="C31"/>
-      <c r="D31"/>
-      <c r="E31"/>
-      <c r="F31"/>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="B32"/>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
+      <c r="F17" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+    </row>
+    <row r="18" ht="57" spans="1:11">
+      <c r="A18" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+    </row>
+    <row r="19" ht="57" spans="1:11">
+      <c r="A19" s="23" t="s">
+        <v>376</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+    </row>
+    <row r="20" ht="57" spans="1:11">
+      <c r="A20" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+    </row>
+    <row r="21" ht="57" spans="1:11">
+      <c r="A21" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" ht="57" spans="1:11">
+      <c r="A22" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" ht="57" spans="1:11">
+      <c r="A23" s="23" t="s">
+        <v>394</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" ht="57" spans="1:11">
+      <c r="A24" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>402</v>
+      </c>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" ht="57" spans="1:11">
+      <c r="A25" s="23" t="s">
+        <v>403</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>406</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>407</v>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" ht="57" spans="1:11">
+      <c r="A26" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" ht="57" spans="1:11">
+      <c r="A27" s="23" t="s">
+        <v>412</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" ht="57" spans="1:11">
+      <c r="A28" s="23" t="s">
+        <v>417</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>418</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>419</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+    </row>
+    <row r="29" ht="57" spans="1:11">
+      <c r="A29" s="30" t="s">
+        <v>421</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>306</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="D29" s="33"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34" t="s">
+        <v>423</v>
+      </c>
+      <c r="K29" s="34" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="30" ht="57" spans="1:11">
+      <c r="A30" s="23" t="s">
+        <v>425</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+    </row>
+    <row r="31" ht="57" spans="1:11">
+      <c r="A31" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>431</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" ht="57" spans="1:11">
+      <c r="A32" s="23" t="s">
+        <v>433</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>437</v>
+      </c>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33"/>
-      <c r="C33"/>
-      <c r="D33"/>
       <c r="E33"/>
       <c r="F33"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" ht="57" spans="2:6">
       <c r="B34"/>
-      <c r="C34"/>
-      <c r="D34"/>
       <c r="E34"/>
       <c r="F34"/>
     </row>
+    <row r="35" ht="57" spans="2:6">
+      <c r="B35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+    </row>
+    <row r="36" ht="57" spans="2:6">
+      <c r="B36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38"/>
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39"/>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40"/>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41"/>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42"/>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43"/>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44"/>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46"/>
+    </row>
+    <row r="47" spans="2:6">
+      <c r="B47"/>
+    </row>
+    <row r="48" spans="2:6">
+      <c r="B48"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49"/>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51"/>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52"/>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:K2"/>
-  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2">
+      <formula1>"working,complete"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3:J32">
+      <formula1>"Pass,Defect"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A2:K2" location="Scenario!A13" display="Test Scenario"/>
+    <hyperlink ref="A2" location="Scenario!A13" display="Test Scenario"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -6063,9 +7052,730 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="52.6" style="14" customWidth="1"/>
+    <col min="3" max="3" width="60.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="38.0833333333333" customWidth="1"/>
+    <col min="5" max="5" width="43.3833333333333" customWidth="1"/>
+    <col min="6" max="6" width="28.75" customWidth="1"/>
+    <col min="7" max="7" width="64.75" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="7.75" customWidth="1"/>
+    <col min="10" max="10" width="7.125" customWidth="1"/>
+    <col min="11" max="11" width="42.725" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" spans="1:11">
+      <c r="A1" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="17"/>
+      <c r="B2" s="18"/>
+      <c r="C2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="19"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+    </row>
+    <row r="3" ht="28.5" spans="1:11">
+      <c r="A3" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="B3" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+    </row>
+    <row r="4" ht="42.75" spans="1:11">
+      <c r="A4" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="B4" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+    </row>
+    <row r="5" ht="42.75" spans="1:11">
+      <c r="A5" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>450</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+    </row>
+    <row r="6" ht="42.75" spans="1:11">
+      <c r="A6" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="B6" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+    </row>
+    <row r="7" ht="42.75" spans="1:11">
+      <c r="A7" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="B7" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>456</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+    </row>
+    <row r="8" ht="42.75" spans="1:11">
+      <c r="A8" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="B8" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>460</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+    </row>
+    <row r="9" ht="42.75" spans="1:11">
+      <c r="A9" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="B9" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" ht="42.75" spans="1:11">
+      <c r="A10" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="B10" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+    </row>
+    <row r="11" ht="57" spans="1:11">
+      <c r="A11" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="B11" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>472</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+    </row>
+    <row r="12" ht="28.5" spans="1:11">
+      <c r="A12" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="B12" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="D12" s="19"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+    </row>
+    <row r="13" ht="28.5" spans="1:11">
+      <c r="A13" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="B13" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="D13" s="19"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+    </row>
+    <row r="14" ht="28.5" spans="1:11">
+      <c r="A14" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="B14" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>479</v>
+      </c>
+      <c r="D14" s="19"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+    </row>
+    <row r="15" ht="28.5" spans="1:11">
+      <c r="A15" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="B15" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>481</v>
+      </c>
+      <c r="D15" s="19"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" ht="28.5" spans="1:11">
+      <c r="A16" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="B16" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="D16" s="19"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+    </row>
+    <row r="17" ht="28.5" spans="1:11">
+      <c r="A17" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="B17" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="D17" s="19"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+    </row>
+    <row r="18" ht="28.5" spans="1:11">
+      <c r="A18" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="B18" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="D18" s="19"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+    </row>
+    <row r="19" ht="28.5" spans="1:11">
+      <c r="A19" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="B19" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>489</v>
+      </c>
+      <c r="D19" s="19"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+    </row>
+    <row r="20" ht="42.75" spans="1:11">
+      <c r="A20" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="B20" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+    </row>
+    <row r="21" ht="42.75" spans="1:11">
+      <c r="A21" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="B21" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>494</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" ht="28.5" spans="1:11">
+      <c r="A22" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="B22" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C22" s="69" t="s">
+        <v>497</v>
+      </c>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" ht="28.5" spans="1:11">
+      <c r="A23" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="B23" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C23" s="69" t="s">
+        <v>499</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" ht="28.5" spans="1:11">
+      <c r="A24" s="17" t="s">
+        <v>500</v>
+      </c>
+      <c r="B24" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" ht="28.5" spans="1:11">
+      <c r="A25" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="B25" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" ht="28.5" spans="1:11">
+      <c r="A26" s="17" t="s">
+        <v>502</v>
+      </c>
+      <c r="B26" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" ht="28.5" spans="1:11">
+      <c r="A27" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="B27" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" ht="28.5" spans="1:11">
+      <c r="A28" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="B28" s="18" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2">
+      <formula1>"working,complete"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -6092,42 +7802,42 @@
   <sheetData>
     <row r="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:11">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="12"/>

--- a/manual test/Open cert/OpenCartFrontend.xlsx
+++ b/manual test/Open cert/OpenCartFrontend.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12180" firstSheet="1" activeTab="1"/>
+    <workbookView windowHeight="11580" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Version" sheetId="10" r:id="rId1"/>
     <sheet name="Scenario" sheetId="1" r:id="rId2"/>
-    <sheet name="HomePage" sheetId="3" r:id="rId3"/>
-    <sheet name="Top Menu" sheetId="6" r:id="rId4"/>
-    <sheet name="Header" sheetId="4" r:id="rId5"/>
-    <sheet name="Footer" sheetId="7" r:id="rId6"/>
-    <sheet name="Product Pages" sheetId="8" r:id="rId7"/>
-    <sheet name="Shopping Cart page" sheetId="11" r:id="rId8"/>
-    <sheet name="Register" sheetId="5" r:id="rId9"/>
-    <sheet name="Currency" sheetId="2" r:id="rId10"/>
+    <sheet name="UserAccountAccess&amp;Validation" sheetId="5" r:id="rId3"/>
+    <sheet name="Userfeature" sheetId="12" r:id="rId4"/>
+    <sheet name="HomePage" sheetId="3" r:id="rId5"/>
+    <sheet name="Top Menu" sheetId="6" r:id="rId6"/>
+    <sheet name="Header" sheetId="4" r:id="rId7"/>
+    <sheet name="Footer" sheetId="7" r:id="rId8"/>
+    <sheet name="Product Pages" sheetId="8" r:id="rId9"/>
+    <sheet name="Shopping Cart page" sheetId="11" r:id="rId10"/>
+    <sheet name="Currency" sheetId="2" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="669">
   <si>
     <t>Version</t>
   </si>
@@ -119,6 +120,9 @@
     <t>Validate the working of 'Logout' functionality</t>
   </si>
   <si>
+    <t>Not in FRS / Still not testable in this current verion</t>
+  </si>
+  <si>
     <t>TS004</t>
   </si>
   <si>
@@ -339,6 +343,213 @@
   </si>
   <si>
     <t>Comments</t>
+  </si>
+  <si>
+    <t>TC_ACC_001</t>
+  </si>
+  <si>
+    <t>Validate login - default</t>
+  </si>
+  <si>
+    <t>TC_ACC_002</t>
+  </si>
+  <si>
+    <t>Validate Login - email valid</t>
+  </si>
+  <si>
+    <t>TC_ACC_003</t>
+  </si>
+  <si>
+    <t>Validate Login - email format</t>
+  </si>
+  <si>
+    <t>TC_ACC_004</t>
+  </si>
+  <si>
+    <t>Validate Login - email boundary - below</t>
+  </si>
+  <si>
+    <t>TC_ACC_005</t>
+  </si>
+  <si>
+    <t>Validate Login - email boundary - above</t>
+  </si>
+  <si>
+    <t>TC_ACC_006</t>
+  </si>
+  <si>
+    <t>Validate Login - password valid</t>
+  </si>
+  <si>
+    <t>TC_ACC_007</t>
+  </si>
+  <si>
+    <t>Validate Login - password invalid</t>
+  </si>
+  <si>
+    <t>TC_ACC_008</t>
+  </si>
+  <si>
+    <t>Validate Login - password boundary - below</t>
+  </si>
+  <si>
+    <t>TC_ACC_009</t>
+  </si>
+  <si>
+    <t>Validate Login - password boundary - above</t>
+  </si>
+  <si>
+    <t>TC_ACC_010</t>
+  </si>
+  <si>
+    <t>Validate Login - pass</t>
+  </si>
+  <si>
+    <t>TC_ACC_011</t>
+  </si>
+  <si>
+    <t>Validate Login - fail</t>
+  </si>
+  <si>
+    <t>TC_ACC_012</t>
+  </si>
+  <si>
+    <t>Validate Login - forgot password</t>
+  </si>
+  <si>
+    <t>TC_ACC_013</t>
+  </si>
+  <si>
+    <t>Validate Register new Account</t>
+  </si>
+  <si>
+    <t>TC_ACC_014</t>
+  </si>
+  <si>
+    <t>Validate Register - default</t>
+  </si>
+  <si>
+    <t>TC_ACC_015</t>
+  </si>
+  <si>
+    <t>Validate Register - first name - valid</t>
+  </si>
+  <si>
+    <t>TC_ACC_016</t>
+  </si>
+  <si>
+    <t>Validate Register - first name - null</t>
+  </si>
+  <si>
+    <t>TC_ACC_017</t>
+  </si>
+  <si>
+    <t>Validate Register - first name - boundary - below</t>
+  </si>
+  <si>
+    <t>TC_ACC_018</t>
+  </si>
+  <si>
+    <t>Validate Register - first name - boundary - above</t>
+  </si>
+  <si>
+    <t>TC_ACC_019</t>
+  </si>
+  <si>
+    <t>Validate Register - last name - not support characters</t>
+  </si>
+  <si>
+    <t>TC_ACC_020</t>
+  </si>
+  <si>
+    <t>Validate Register - last name - valid</t>
+  </si>
+  <si>
+    <t>TC_ACC_021</t>
+  </si>
+  <si>
+    <t>Validate Register - last name - null</t>
+  </si>
+  <si>
+    <t>TC_ACC_022</t>
+  </si>
+  <si>
+    <t>Validate Register - last name - boundary - below</t>
+  </si>
+  <si>
+    <t>TC_ACC_023</t>
+  </si>
+  <si>
+    <t>Validate Register - last name - boundary - above</t>
+  </si>
+  <si>
+    <t>TC_ACC_024</t>
+  </si>
+  <si>
+    <t>TC_ACC_025</t>
+  </si>
+  <si>
+    <t>Validate Register - email - valid</t>
+  </si>
+  <si>
+    <t>TC_ACC_026</t>
+  </si>
+  <si>
+    <t>Validate Register - email - null</t>
+  </si>
+  <si>
+    <t>TC_ACC_027</t>
+  </si>
+  <si>
+    <t>Validate Register - email - boundary - below</t>
+  </si>
+  <si>
+    <t>TC_ACC_028</t>
+  </si>
+  <si>
+    <t>Validate Register - email - boundary - above</t>
+  </si>
+  <si>
+    <t>TC_ACC_029</t>
+  </si>
+  <si>
+    <t>Validate Register - email - not support characters</t>
+  </si>
+  <si>
+    <t>TC_ACC_030</t>
+  </si>
+  <si>
+    <t>Validate Register - email - format</t>
+  </si>
+  <si>
+    <t>TC_ACC_031</t>
+  </si>
+  <si>
+    <t>Validate Register - subscribe</t>
+  </si>
+  <si>
+    <t>TC_ACC_032</t>
+  </si>
+  <si>
+    <t>Validate Register - policy</t>
+  </si>
+  <si>
+    <t>TC_ACC_033</t>
+  </si>
+  <si>
+    <t>Validate Register - success</t>
+  </si>
+  <si>
+    <t>TC_ACC_034</t>
+  </si>
+  <si>
+    <t>Validate user can logout</t>
+  </si>
+  <si>
+    <t>TC_ACC_035</t>
+  </si>
+  <si>
+    <t>Validate forgot password function</t>
   </si>
   <si>
     <t>&lt;&lt;Test Scenario</t>
@@ -1603,49 +1814,348 @@
     <t>Validate valid coupon</t>
   </si>
   <si>
+    <t>1. Enter coupon code -&lt;Refer test data&gt;
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>HNY2026</t>
+  </si>
+  <si>
+    <t>Coupon code should be accepct and calculated discount should display</t>
+  </si>
+  <si>
     <t>TC_SC_011</t>
   </si>
   <si>
-    <t>Validate invalid coupon</t>
+    <t>Validate invalid coupon - expired</t>
+  </si>
+  <si>
+    <t>1. Click on 'Use coupon code' (Validate ER-1)
+2. Enter coupon code -&lt;Refer test data&gt;
+3. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>HNY2000</t>
+  </si>
+  <si>
+    <t>Should display message "this coupon code is expired"</t>
   </si>
   <si>
     <t>TC_SC_012</t>
   </si>
   <si>
+    <t>Validate invalid coupon - wrong coupon</t>
+  </si>
+  <si>
+    <t>FACEBOOK</t>
+  </si>
+  <si>
+    <t>Should display message "this coupon code is invalid"</t>
+  </si>
+  <si>
+    <t>TC_SC_013</t>
+  </si>
+  <si>
+    <t>Validate invalid coupon - boundary</t>
+  </si>
+  <si>
+    <t>A,Happynewyaer2026</t>
+  </si>
+  <si>
+    <t>Should not accpet coupon that not in boundary ( 5-10 characters)</t>
+  </si>
+  <si>
+    <t>TC_SC_014</t>
+  </si>
+  <si>
     <t>Validate estimate &amp; shipping taxes show</t>
   </si>
   <si>
-    <t>TC_SC_013</t>
+    <t>1. Click on 'Estimate Shipping &amp; Taxes' 
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Estimate Shipping &amp; Taxes' should appear below the tab, should contain following details : 
+Country input, Region input, Post code input and Get Quotes button.</t>
+  </si>
+  <si>
+    <t>TC_SC_015</t>
   </si>
   <si>
     <t>Validate estimate &amp; shipping taxes hidden</t>
   </si>
   <si>
-    <t>TC_SC_014</t>
+    <t>Open application,
+Added product to the cart,
+Open shopping cart page,
+Open estimate &amp; shipping taxes tab</t>
+  </si>
+  <si>
+    <t>The tab should hidden</t>
+  </si>
+  <si>
+    <t>TC_SC_016</t>
+  </si>
+  <si>
+    <t>(TS010) 
+Validate the working of 'Shopping Cart' functionality</t>
+  </si>
+  <si>
+    <t>Validate country selection - default</t>
+  </si>
+  <si>
+    <t>Default country should be 'United Kingdom'</t>
+  </si>
+  <si>
+    <t>TC_SC_017</t>
+  </si>
+  <si>
+    <t>Validate country selection</t>
+  </si>
+  <si>
+    <t>1. Click dropdown button on Country tab (Validate ER-1)
+2. Select country - &lt;Refer test data&gt;
+3. Validate result (Validate ER-2)</t>
+  </si>
+  <si>
+    <t>Thailand</t>
+  </si>
+  <si>
+    <t>1. Country list should appear in dropdown selection format
+2. Selected country should show in country tab</t>
+  </si>
+  <si>
+    <t>TC_SC_018</t>
+  </si>
+  <si>
+    <t>Validate country selection - required field</t>
+  </si>
+  <si>
+    <t>1. Select country -&lt;Refer test data&gt;
+2. Click 'Get Quotes' button
+3. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Country : Please Select</t>
+  </si>
+  <si>
+    <t>Country should not be possible to send null option,Country tab should be required field</t>
+  </si>
+  <si>
+    <t>TC_SC_019</t>
+  </si>
+  <si>
+    <t>Validate 'Region/State' selection - default</t>
+  </si>
+  <si>
+    <t>1.Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Default option should be --None-- due to not yet select country</t>
+  </si>
+  <si>
+    <t>TC_SC_020</t>
+  </si>
+  <si>
+    <t>Validate 'Region/State' selection - selection list</t>
+  </si>
+  <si>
+    <t>1. Select country -&lt;Refer test data&gt;
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Country : Thailand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. All Region/State in selected country should appear on region/state drop down list </t>
+  </si>
+  <si>
+    <t>TC_SC_021</t>
+  </si>
+  <si>
+    <t>Validate 'Region/State' selection - selection</t>
+  </si>
+  <si>
+    <t>Open application,
+Added product to the cart,
+Open shopping cart page,
+Open estimate &amp; shipping taxes tab,
+Select country</t>
+  </si>
+  <si>
+    <t>1. Select country -&lt;Refer test data (country)&gt;
+2. Validate result (Validate ER-1)
+3. Select state -&lt;Refer test data (state/region)&gt;
+4. Validate result (Validate ER-2)</t>
+  </si>
+  <si>
+    <t>Country : Thailand,
+Region/State : krabi</t>
+  </si>
+  <si>
+    <t>1. All Region/State in selected country should appear on region/state drop down list 
+2. Selected option should show in 'Region/State' tab</t>
+  </si>
+  <si>
+    <t>TC_SC_022</t>
+  </si>
+  <si>
+    <t>Validate 'Region/State' selection - invalid</t>
+  </si>
+  <si>
+    <t>1. Select country -&lt;Refer test data (country)&gt;
+2. Validate result (Validate ER-1)
+3. Select state -&lt;Refer test data (state/region)&gt;
+4. Validate result (Validate ER-2,ER-3,ER-4)</t>
+  </si>
+  <si>
+    <t>Country : Thailand
+Region/State : Please Select</t>
+  </si>
+  <si>
+    <t>1. All Region/State in selected country should appear on region/state drop down list 
+2. Region/state should not be possible to send null option
+3. Region/state tab should be required field
+4. Error message 'Please select region / state !' should appear</t>
+  </si>
+  <si>
+    <t>TC_SC_023</t>
+  </si>
+  <si>
+    <t>Validate 'Post Code' data - valid</t>
+  </si>
+  <si>
+    <t>1. Enter post code -&lt;Refer test data&gt;
+2. Click 'Get Quotes' button
+3. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Post code : 13000</t>
+  </si>
+  <si>
+    <t>1. Should accept entered post code</t>
+  </si>
+  <si>
+    <t>TC_SC_024</t>
+  </si>
+  <si>
+    <t>Validate 'Post Code' data - invalid (not usable in any format)</t>
+  </si>
+  <si>
+    <t>Post code : abcdefg</t>
+  </si>
+  <si>
+    <t>1. Should show error message 'Please input valid post code'</t>
+  </si>
+  <si>
+    <t>TC_SC_025</t>
+  </si>
+  <si>
+    <t>Validate 'Post Code' data - invalid (usable in other region but not selected one)</t>
+  </si>
+  <si>
+    <t>Post code : A1A</t>
+  </si>
+  <si>
+    <t>TC_SC_026</t>
+  </si>
+  <si>
+    <t>Validate estimate &amp; shipping taxes calculation</t>
+  </si>
+  <si>
+    <t>1. Select country,region/state,postcode -&lt;Refer test data&gt;
+2. Click 'Get Quotes' button
+3. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Country : Thailand,
+Region/State : Bangkok,
+Post code : 10230</t>
+  </si>
+  <si>
+    <t>1. Show calculated shipping fee &amp; method available</t>
+  </si>
+  <si>
+    <t>TC_SC_027</t>
+  </si>
+  <si>
+    <t>Validate shipping method selection</t>
+  </si>
+  <si>
+    <t>Open application,
+Added product to the cart,
+Open shopping cart page,
+Open estimate &amp; shipping taxes tab,
+calculated shipping location</t>
+  </si>
+  <si>
+    <t>1. Select shipping method -&lt;Refer test data&gt;
+2. Click 'Apply Shipping' button</t>
+  </si>
+  <si>
+    <t>Flat Shipping Rate - $5.00</t>
+  </si>
+  <si>
+    <t>1. Shipping fee should appear and calculated in price calculation</t>
+  </si>
+  <si>
+    <t>TC_SC_028</t>
   </si>
   <si>
     <t>Validate use gift certificate shown</t>
   </si>
   <si>
-    <t>TC_SC_015</t>
+    <t>1. Click on 'Use Gift Certificate' 
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>1. gift certificate input tab should appear below 'Use Gift Certificate'</t>
+  </si>
+  <si>
+    <t>TC_SC_029</t>
   </si>
   <si>
     <t>Validate use gift certificate hidden</t>
   </si>
   <si>
-    <t>TC_SC_016</t>
+    <t>Open application,
+Added product to the cart,
+Open shopping cart page,
+Open gift certificate tab</t>
+  </si>
+  <si>
+    <t>1. gift certificate input tab should disappear</t>
+  </si>
+  <si>
+    <t>TC_SC_030</t>
   </si>
   <si>
     <t>Validate valid gift certificate</t>
   </si>
   <si>
-    <t>TC_SC_017</t>
+    <t>1. Input gift certificate
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>MyGift2026</t>
+  </si>
+  <si>
+    <t>1. code accpet and show result (discount / free item ) on shopping cart / calculation tab</t>
+  </si>
+  <si>
+    <t>TC_SC_031</t>
   </si>
   <si>
     <t>Validate invalid gift certificate</t>
   </si>
   <si>
-    <t>TC_SC_018</t>
+    <t>MyGift 2555,null,A</t>
+  </si>
+  <si>
+    <t>Should show message ' Warning: Gift Certificate is either invalid or the balance has been used up!'</t>
+  </si>
+  <si>
+    <t>TC_SC_032</t>
   </si>
   <si>
     <t>Validate shopping cart page content - detailed price</t>
@@ -1655,7 +2165,7 @@
 Sub-total, Eco Tax, Vat, Total</t>
   </si>
   <si>
-    <t>TC_SC_019</t>
+    <t>TC_SC_033</t>
   </si>
   <si>
     <t>Validate shopping cart page content - detailed price calculation</t>
@@ -1664,31 +2174,30 @@
     <t>Result of detailed price should shown correctly</t>
   </si>
   <si>
-    <t>TC_SC_020</t>
-  </si>
-  <si>
-    <t>Continue Shopping' button</t>
-  </si>
-  <si>
-    <t>TC_SC_021</t>
-  </si>
-  <si>
-    <t>Checkout' button</t>
-  </si>
-  <si>
-    <t>TC_SC_022</t>
-  </si>
-  <si>
-    <t>TC_SC_023</t>
-  </si>
-  <si>
-    <t>TC_SC_024</t>
-  </si>
-  <si>
-    <t>TC_SC_025</t>
-  </si>
-  <si>
-    <t>TC_SC_026</t>
+    <t>TC_SC_034</t>
+  </si>
+  <si>
+    <t>Validate 'Continue Shopping' button</t>
+  </si>
+  <si>
+    <t>1. Click on 'Continue Shopping' button
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Should redirect user to home page / all record item should still in cart</t>
+  </si>
+  <si>
+    <t>TC_SC_035</t>
+  </si>
+  <si>
+    <t>Validate 'Checkout' button</t>
+  </si>
+  <si>
+    <t>1. Click on 'Checkout' button
+2. Validate result (Validate ER-1)</t>
+  </si>
+  <si>
+    <t>Should redirect user to checkout page</t>
   </si>
   <si>
     <t>TC_CF_001</t>
@@ -1737,7 +2246,7 @@
     <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;฿&quot;* #,##0_-;\-&quot;฿&quot;* #,##0_-;_-&quot;฿&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1770,12 +2279,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="14"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
       <name val="TH Sarabun PSK"/>
       <charset val="0"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="TH Sarabun PSK"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft Yahei"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1797,6 +2315,14 @@
       <color theme="0"/>
       <name val="TH Sarabun PSK"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="14"/>
+      <color rgb="FF0000FF"/>
+      <name val="TH Sarabun PSK"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1920,7 +2446,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1930,12 +2456,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2285,137 +2805,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2446,154 +2966,151 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -2602,29 +3119,11 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2678,7 +3177,21 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2886,25 +3399,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="totalRow" dxfId="6"/>
-      <tableStyleElement type="firstColumn" dxfId="5"/>
-      <tableStyleElement type="lastColumn" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="3"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
+      <tableStyleElement type="wholeTable" dxfId="10"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstColumn" dxfId="7"/>
+      <tableStyleElement type="lastColumn" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="4"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="18"/>
-      <tableStyleElement type="totalRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
-      <tableStyleElement type="pageFieldValues" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="totalRow" dxfId="19"/>
+      <tableStyleElement type="firstRowStripe" dxfId="18"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="17"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="16"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="14"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="13"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="12"/>
+      <tableStyleElement type="pageFieldValues" dxfId="11"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3181,46 +3694,46 @@
   </cols>
   <sheetData>
     <row r="3" ht="15" spans="2:3">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="61" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:3">
-      <c r="B4" s="67">
+      <c r="B4" s="61">
         <v>1</v>
       </c>
-      <c r="C4" s="67" t="s">
+      <c r="C4" s="61" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="15" spans="2:3">
-      <c r="B5" s="67">
+      <c r="B5" s="61">
         <v>2</v>
       </c>
-      <c r="C5" s="67"/>
+      <c r="C5" s="61"/>
     </row>
     <row r="6" ht="15" spans="2:3">
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
     </row>
     <row r="7" ht="15" spans="2:3">
-      <c r="B7" s="67"/>
-      <c r="C7" s="67"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
     </row>
     <row r="8" ht="15" spans="2:3">
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
     </row>
     <row r="9" ht="15" spans="2:3">
-      <c r="B9" s="67"/>
-      <c r="C9" s="67"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
     </row>
     <row r="10" ht="15" spans="2:3">
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3229,6 +3742,1102 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="52.6" style="1" customWidth="1"/>
+    <col min="3" max="3" width="60.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="38.0833333333333" customWidth="1"/>
+    <col min="5" max="5" width="47.3416666666667" customWidth="1"/>
+    <col min="6" max="6" width="28.75" customWidth="1"/>
+    <col min="7" max="7" width="64.75" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="7.75" customWidth="1"/>
+    <col min="10" max="10" width="7.125" customWidth="1"/>
+    <col min="11" max="11" width="42.725" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" spans="1:11">
+      <c r="A1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="12"/>
+      <c r="B2" s="13"/>
+      <c r="C2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="14"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" ht="28.5" spans="1:11">
+      <c r="A3" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="B3" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>510</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" ht="42.75" spans="1:11">
+      <c r="A4" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="B4" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>514</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>516</v>
+      </c>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+    </row>
+    <row r="5" ht="42.75" spans="1:11">
+      <c r="A5" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="B5" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>518</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+    </row>
+    <row r="6" ht="42.75" spans="1:11">
+      <c r="A6" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="B6" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+    </row>
+    <row r="7" ht="42.75" spans="1:11">
+      <c r="A7" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="B7" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>526</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+    </row>
+    <row r="8" ht="42.75" spans="1:11">
+      <c r="A8" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="B8" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>530</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>531</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+    </row>
+    <row r="9" ht="42.75" spans="1:11">
+      <c r="A9" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="B9" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>534</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>535</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+    </row>
+    <row r="10" ht="42.75" spans="1:11">
+      <c r="A10" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="B10" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>537</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>539</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+    </row>
+    <row r="11" ht="57" spans="1:11">
+      <c r="A11" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="B11" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" ht="57" spans="1:11">
+      <c r="A12" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="B12" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>545</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>548</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" ht="57" spans="1:11">
+      <c r="A13" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="B13" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>550</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>552</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>553</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" ht="57" spans="1:11">
+      <c r="A14" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="B14" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>555</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>557</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+    </row>
+    <row r="15" ht="57" spans="1:11">
+      <c r="A15" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="B15" s="13" t="str">
+        <f>"("&amp;Scenario!A17&amp;")"&amp;" 
+"&amp;Scenario!C17</f>
+        <v>(TS011) 
+Validate the working of 'Shopping Cart page' functionality</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>561</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" ht="42.75" spans="1:11">
+      <c r="A16" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="B16" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>563</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>565</v>
+      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+    </row>
+    <row r="17" ht="57" spans="1:11">
+      <c r="A17" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="B17" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>567</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>569</v>
+      </c>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+    </row>
+    <row r="18" ht="57" spans="1:11">
+      <c r="A18" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>572</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>573</v>
+      </c>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+    </row>
+    <row r="19" ht="57" spans="1:11">
+      <c r="A19" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>575</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>578</v>
+      </c>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+    </row>
+    <row r="20" ht="57" spans="1:11">
+      <c r="A20" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>580</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>583</v>
+      </c>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+    </row>
+    <row r="21" ht="57" spans="1:11">
+      <c r="A21" s="12" t="s">
+        <v>584</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>585</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>587</v>
+      </c>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+    </row>
+    <row r="22" ht="57" spans="1:11">
+      <c r="A22" s="12" t="s">
+        <v>588</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>589</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>592</v>
+      </c>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+    </row>
+    <row r="23" ht="71.25" spans="1:11">
+      <c r="A23" s="12" t="s">
+        <v>593</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>594</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>595</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>596</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>598</v>
+      </c>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+    </row>
+    <row r="24" ht="71.25" spans="1:11">
+      <c r="A24" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>600</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>595</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>603</v>
+      </c>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+    </row>
+    <row r="25" ht="57" spans="1:11">
+      <c r="A25" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>606</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+    </row>
+    <row r="26" ht="57" spans="1:11">
+      <c r="A26" s="12" t="s">
+        <v>609</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>606</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+    </row>
+    <row r="27" ht="57" spans="1:11">
+      <c r="A27" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>614</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>606</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+    </row>
+    <row r="28" ht="57" spans="1:11">
+      <c r="A28" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>617</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>618</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>619</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>620</v>
+      </c>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+    </row>
+    <row r="29" ht="71.25" spans="1:11">
+      <c r="A29" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>571</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>622</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>623</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>624</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>626</v>
+      </c>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+    </row>
+    <row r="30" ht="42.75" spans="1:11">
+      <c r="A30" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="B30" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>629</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>630</v>
+      </c>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+    </row>
+    <row r="31" ht="57" spans="1:11">
+      <c r="A31" s="12" t="s">
+        <v>631</v>
+      </c>
+      <c r="B31" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>632</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>629</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>634</v>
+      </c>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+    </row>
+    <row r="32" ht="57" spans="1:11">
+      <c r="A32" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="B32" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>636</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>637</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>639</v>
+      </c>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+    </row>
+    <row r="33" ht="57" spans="1:11">
+      <c r="A33" s="12" t="s">
+        <v>640</v>
+      </c>
+      <c r="B33" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>641</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>637</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>643</v>
+      </c>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+    </row>
+    <row r="34" ht="42.75" spans="1:11">
+      <c r="A34" s="12" t="s">
+        <v>644</v>
+      </c>
+      <c r="B34" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>646</v>
+      </c>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+    </row>
+    <row r="35" ht="42.75" spans="1:11">
+      <c r="A35" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="B35" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>648</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+    </row>
+    <row r="36" ht="42.75" spans="1:11">
+      <c r="A36" s="12" t="s">
+        <v>650</v>
+      </c>
+      <c r="B36" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+    </row>
+    <row r="37" ht="42.75" spans="1:11">
+      <c r="A37" s="12" t="s">
+        <v>654</v>
+      </c>
+      <c r="B37" s="13" t="str">
+        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
+"&amp;Scenario!C16</f>
+        <v>(TS010) 
+Validate the working of 'Shopping Cart' functionality</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>655</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>515</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>656</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>657</v>
+      </c>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2">
+      <formula1>"working,complete"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:XFD4"/>
@@ -3249,42 +4858,42 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>15</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>101</v>
+        <v>171</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -3293,48 +4902,48 @@
     </row>
     <row r="3" ht="42.75" spans="1:11">
       <c r="A3" t="s">
-        <v>505</v>
+        <v>658</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>506</v>
+        <v>659</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>507</v>
+        <v>660</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>508</v>
+        <v>661</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>509</v>
+        <v>662</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>510</v>
+        <v>663</v>
       </c>
       <c r="G3" t="s">
-        <v>511</v>
+        <v>664</v>
       </c>
     </row>
     <row r="4" ht="42.75" spans="1:11">
       <c r="A4" t="s">
-        <v>512</v>
+        <v>665</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>506</v>
+        <v>659</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>513</v>
+        <v>666</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>508</v>
+        <v>661</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>514</v>
+        <v>667</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="G4" t="s">
-        <v>515</v>
+        <v>668</v>
       </c>
     </row>
   </sheetData>
@@ -3374,27 +4983,27 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" ht="18" spans="1:10">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:10">
       <c r="B4" t="s">
@@ -3403,607 +5012,611 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="51" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="E5" s="55" t="s">
+      <c r="E5" s="52" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="56" t="s">
+      <c r="F6" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="56" t="s">
+      <c r="G6" s="53" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:10">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="59">
-        <v>0</v>
-      </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17" t="s">
+      <c r="D7" s="12"/>
+      <c r="E7" s="31">
+        <f>COUNTIF('UserAccountAccess&amp;Validation'!B:B,"*TS001*")</f>
+        <v>21</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:10">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="59">
-        <v>0</v>
-      </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17" t="s">
+      <c r="D8" s="12"/>
+      <c r="E8" s="31">
+        <f>COUNTIF('UserAccountAccess&amp;Validation'!B:B,"*TS002*")</f>
+        <v>12</v>
+      </c>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="59">
-        <v>0</v>
-      </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17" t="s">
+      <c r="D9" s="12"/>
+      <c r="E9" s="31">
+        <f>COUNTIF('UserAccountAccess&amp;Validation'!B:B,"*TS003*")</f>
+        <v>1</v>
+      </c>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="31">
+        <f>COUNTIF('UserAccountAccess&amp;Validation'!B:B,"*TS004*")</f>
+        <v>1</v>
+      </c>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="59">
-        <v>0</v>
-      </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="17" t="s">
+      <c r="A11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="B11" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
+      <c r="C11" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="58" t="s">
+      <c r="A12" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="59"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="B12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
     </row>
     <row r="13" ht="18" spans="1:10">
-      <c r="A13" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="60" t="s">
+      <c r="A13" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="61">
+      <c r="B13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="54"/>
+      <c r="E13" s="55">
         <f>COUNTA('Product Pages'!A3:A202)</f>
         <v>30</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="12">
         <f>COUNTIF('Product Pages'!J3:J9999,"Defect")</f>
         <v>1</v>
       </c>
-      <c r="G13" s="17"/>
+      <c r="G13" s="12"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17" s="31">
+        <f>COUNTA('Shopping Cart page'!A1:A1008)</f>
         <v>36</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="58" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="58" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="59">
-        <f>COUNTA('Shopping Cart page'!A1:A999)</f>
-        <v>27</v>
-      </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
     </row>
     <row r="18" customFormat="1" spans="1:7">
-      <c r="A18" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="63" t="s">
+      <c r="A18" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64">
+      <c r="B18" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58">
         <f>COUNTA(HomePage!A3:A9998)</f>
         <v>11</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="12">
         <f>COUNTIF(HomePage!J3:J9999,"Defect")</f>
         <v>0</v>
       </c>
-      <c r="G18" s="17"/>
+      <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="58" t="s">
+      <c r="A19" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+      <c r="B19" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="58" t="s">
+      <c r="A20" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
+      <c r="B20" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="58" t="s">
+      <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+      <c r="B21" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="12"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="58" t="s">
+      <c r="A22" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
+      <c r="B22" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="12"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="58" t="s">
+      <c r="A23" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
+      <c r="B23" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="12"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="58" t="s">
+      <c r="A24" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
+      <c r="B24" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="58" t="s">
+      <c r="A25" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
+      <c r="B25" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="58" t="s">
+      <c r="A26" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
+      <c r="B26" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="58" t="s">
+      <c r="A27" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
+      <c r="B27" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="12"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="58" t="s">
+      <c r="A28" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
+      <c r="B28" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="12"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="58" t="s">
+      <c r="A29" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="17"/>
-      <c r="E29" s="59"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
+      <c r="B29" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="12"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="58" t="s">
+      <c r="A30" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="17"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
+      <c r="B30" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C31" s="58" t="s">
+      <c r="A31" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="17"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
+      <c r="B31" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="12"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C32" s="62" t="s">
+      <c r="A32" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="59"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
+      <c r="B32" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="12"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="62" t="s">
+      <c r="A33" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D33" s="17"/>
-      <c r="E33" s="59"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
+      <c r="B33" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="12"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="62" t="s">
+      <c r="A34" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="17"/>
-      <c r="E34" s="59"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
+      <c r="B34" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="12"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="62" t="s">
+      <c r="A35" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="17"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
+      <c r="B35" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="12"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="58" t="s">
+      <c r="A36" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
+      <c r="B36" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="12"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
     </row>
     <row r="37" customFormat="1" spans="1:7">
-      <c r="A37" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B37" s="58" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="63" t="s">
+      <c r="A37" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64">
+      <c r="B37" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58">
         <f>COUNTA(Header!A3:A200)</f>
         <v>19</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F37" s="12">
         <f>COUNTIF(Header!J3:J9999,"Defect")</f>
         <v>0</v>
       </c>
-      <c r="G37" s="17"/>
+      <c r="G37" s="12"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="60" t="s">
+      <c r="A38" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="60"/>
-      <c r="E38" s="61">
+      <c r="B38" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="54"/>
+      <c r="E38" s="55">
         <f>COUNTA('Top Menu'!A3:A201)</f>
         <v>5</v>
       </c>
-      <c r="F38" s="17">
+      <c r="F38" s="12">
         <f>COUNTIF('Top Menu'!J3:J9999,"defect")</f>
         <v>0</v>
       </c>
-      <c r="G38" s="17"/>
+      <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="60" t="s">
+      <c r="A39" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="60"/>
-      <c r="E39" s="61">
+      <c r="B39" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="D39" s="54"/>
+      <c r="E39" s="55">
         <f>COUNTA(Footer!A3:A200)</f>
         <v>16</v>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="12">
         <f>COUNTIF(Footer!J3:J9999,"defect")</f>
         <v>0</v>
       </c>
-      <c r="G39" s="17"/>
+      <c r="G39" s="12"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" s="58" t="s">
+      <c r="A40" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="17"/>
-      <c r="E40" s="59"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
+      <c r="B40" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" s="12"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="36"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="65" t="s">
-        <v>90</v>
-      </c>
-      <c r="E41" s="66">
+      <c r="A41" s="26"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="E41" s="60">
         <f>SUM(E7:E40)</f>
-        <v>108</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -4020,11 +5633,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:E17">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>'Shopping Cart page'!$D$2="complete"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>'Shopping Cart page'!$D$2="working"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>'Shopping Cart page'!$D$2="complete"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:D18">
@@ -4093,6 +5706,568 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="56.625" style="43" customWidth="1"/>
+    <col min="3" max="3" width="48.625" customWidth="1"/>
+    <col min="4" max="4" width="36.25" customWidth="1"/>
+    <col min="5" max="5" width="23.375" customWidth="1"/>
+    <col min="6" max="6" width="13.25" customWidth="1"/>
+    <col min="7" max="7" width="28.5" customWidth="1"/>
+    <col min="8" max="8" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="7.75" customWidth="1"/>
+    <col min="10" max="10" width="7.125" customWidth="1"/>
+    <col min="11" max="11" width="10.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" spans="1:11">
+      <c r="A1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" ht="36" spans="1:11">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="45" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>TS002
+Validate the working of 'Login' functionality</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" ht="28.5" spans="1:11">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>TS002
+Validate the working of 'Login' functionality</v>
+      </c>
+      <c r="C3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+    </row>
+    <row r="4" ht="28.5" spans="1:11">
+      <c r="A4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>TS002
+Validate the working of 'Login' functionality</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5" spans="1:11">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>TS002
+Validate the working of 'Login' functionality</v>
+      </c>
+      <c r="C5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="29"/>
+    </row>
+    <row r="6" customFormat="1" ht="28.5" spans="1:11">
+      <c r="A6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>TS002
+Validate the working of 'Login' functionality</v>
+      </c>
+      <c r="C6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="29"/>
+    </row>
+    <row r="7" ht="28.5" spans="1:11">
+      <c r="A7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="47" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>TS002
+Validate the working of 'Login' functionality</v>
+      </c>
+      <c r="C7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="29"/>
+    </row>
+    <row r="8" ht="28.5" spans="1:11">
+      <c r="A8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>TS002
+Validate the working of 'Login' functionality</v>
+      </c>
+      <c r="C8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="29"/>
+    </row>
+    <row r="9" ht="28.5" spans="1:11">
+      <c r="A9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B9" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>TS002
+Validate the working of 'Login' functionality</v>
+      </c>
+      <c r="C9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="29"/>
+    </row>
+    <row r="10" ht="28.5" spans="1:11">
+      <c r="A10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>TS002
+Validate the working of 'Login' functionality</v>
+      </c>
+      <c r="C10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D10" s="29"/>
+    </row>
+    <row r="11" ht="28.5" spans="1:11">
+      <c r="A11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>TS002
+Validate the working of 'Login' functionality</v>
+      </c>
+      <c r="C11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D11" s="29"/>
+    </row>
+    <row r="12" ht="28.5" spans="1:11">
+      <c r="A12" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>TS002
+Validate the working of 'Login' functionality</v>
+      </c>
+      <c r="C12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="29"/>
+    </row>
+    <row r="13" ht="28.5" spans="1:11">
+      <c r="A13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>TS002
+Validate the working of 'Login' functionality</v>
+      </c>
+      <c r="C13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" s="29"/>
+    </row>
+    <row r="14" ht="28.5" spans="1:11">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="29"/>
+    </row>
+    <row r="15" ht="28.5" spans="1:11">
+      <c r="A15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B15" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="29"/>
+    </row>
+    <row r="16" ht="28.5" spans="1:11">
+      <c r="A16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" s="29"/>
+    </row>
+    <row r="17" ht="28.5" spans="1:4">
+      <c r="A17" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C17" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="29"/>
+    </row>
+    <row r="18" ht="28.5" spans="1:4">
+      <c r="A18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D18" s="29"/>
+    </row>
+    <row r="19" ht="28.5" spans="1:4">
+      <c r="A19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C19" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="29"/>
+    </row>
+    <row r="20" ht="28.5" spans="1:4">
+      <c r="A20" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" s="29"/>
+    </row>
+    <row r="21" ht="28.5" spans="1:4">
+      <c r="A21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="47" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C21" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="29"/>
+    </row>
+    <row r="22" ht="28.5" spans="1:4">
+      <c r="A22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" s="47" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C22" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="29"/>
+    </row>
+    <row r="23" ht="28.5" spans="1:4">
+      <c r="A23" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="47" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C23" t="s">
+        <v>145</v>
+      </c>
+      <c r="D23" s="29"/>
+    </row>
+    <row r="24" ht="28.5" spans="1:4">
+      <c r="A24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="47" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="29"/>
+    </row>
+    <row r="25" ht="28.5" spans="1:4">
+      <c r="A25" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="47" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C25" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="29"/>
+    </row>
+    <row r="26" ht="33" spans="1:4">
+      <c r="A26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="48" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C26" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="29"/>
+    </row>
+    <row r="27" ht="33" spans="1:4">
+      <c r="A27" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="48" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C27" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" s="29"/>
+    </row>
+    <row r="28" ht="33" spans="1:4">
+      <c r="A28" t="s">
+        <v>153</v>
+      </c>
+      <c r="B28" s="48" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C28" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" s="29"/>
+    </row>
+    <row r="29" ht="33" spans="1:4">
+      <c r="A29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" s="48" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" s="29"/>
+    </row>
+    <row r="30" ht="33" spans="1:4">
+      <c r="A30" t="s">
+        <v>157</v>
+      </c>
+      <c r="B30" s="48" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C30" t="s">
+        <v>158</v>
+      </c>
+      <c r="D30" s="29"/>
+    </row>
+    <row r="31" ht="33" spans="1:4">
+      <c r="A31" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" s="48" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C31" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" s="29"/>
+    </row>
+    <row r="32" ht="33" spans="1:4">
+      <c r="A32" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" s="48" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C32" t="s">
+        <v>162</v>
+      </c>
+      <c r="D32" s="29"/>
+    </row>
+    <row r="33" ht="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>163</v>
+      </c>
+      <c r="B33" s="48" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C33" t="s">
+        <v>164</v>
+      </c>
+      <c r="D33" s="29"/>
+    </row>
+    <row r="34" ht="28.5" spans="1:4">
+      <c r="A34" t="s">
+        <v>165</v>
+      </c>
+      <c r="B34" s="43" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>TS001
+Validate the working of 'Register an account' functionality</v>
+      </c>
+      <c r="C34" t="s">
+        <v>166</v>
+      </c>
+      <c r="D34" s="29"/>
+    </row>
+    <row r="35" ht="28.5" spans="1:4">
+      <c r="A35" t="s">
+        <v>167</v>
+      </c>
+      <c r="B35" s="43" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A9,Scenario!C9)</f>
+        <v>TS003
+Validate the working of 'Logout' functionality</v>
+      </c>
+      <c r="C35" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" ht="28.5" spans="1:4">
+      <c r="A36" t="s">
+        <v>169</v>
+      </c>
+      <c r="B36" s="43" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
+        <v>TS004
+Validate the working of 'Forgot Password' functionality</v>
+      </c>
+      <c r="C36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" location="Scenario!A1" display="=TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
@@ -4110,358 +6285,358 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
-      <c r="A1" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="15" t="s">
+      <c r="A1" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="B1" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="D1" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="E1" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="F1" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="G1" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="H1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" s="15" t="s">
+      <c r="J1" s="10" t="s">
         <v>100</v>
       </c>
+      <c r="K1" s="10" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="2" customFormat="1" ht="18" spans="1:11">
-      <c r="A2" s="11" t="s">
-        <v>101</v>
+      <c r="A2" s="19" t="s">
+        <v>171</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>172</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" ht="142.5" spans="1:11">
-      <c r="A3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" s="24" t="str">
+      <c r="A3" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="13" t="str">
         <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
+      <c r="C3" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
     </row>
     <row r="4" ht="71.25" spans="1:11">
-      <c r="A4" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="24" t="str">
+      <c r="A4" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="13" t="str">
         <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
-      <c r="C4" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
+      <c r="C4" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" s="24" t="str">
+      <c r="A5" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="13" t="str">
         <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
-      <c r="C5" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G5" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
+      <c r="C5" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" s="24" t="str">
+      <c r="A6" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="13" t="str">
         <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G6" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
+      <c r="C6" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" s="24" t="str">
+      <c r="A7" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="13" t="str">
         <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G7" s="41" t="s">
-        <v>125</v>
-      </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
+      <c r="C7" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
     </row>
     <row r="8" ht="28.5" spans="1:11">
-      <c r="A8" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" s="24" t="str">
+      <c r="A8" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8" s="13" t="str">
         <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G8" s="42" t="s">
-        <v>129</v>
-      </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
+      <c r="C8" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
     </row>
     <row r="9" ht="28.5" spans="1:11">
-      <c r="A9" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="B9" s="24" t="str">
+      <c r="A9" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" s="13" t="str">
         <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
-      <c r="C9" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="G9" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
+      <c r="C9" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" ht="114" spans="1:11">
-      <c r="A10" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="B10" s="24" t="str">
+      <c r="A10" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" s="13" t="str">
         <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
-      <c r="C10" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G10" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
+      <c r="C10" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>208</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="B11" s="24" t="str">
+      <c r="A11" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B11" s="13" t="str">
         <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
-      <c r="C11" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E11" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
+      <c r="C11" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" ht="28.5" spans="1:11">
-      <c r="A12" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="B12" s="24" t="str">
+      <c r="A12" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" s="13" t="str">
         <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
-      <c r="C12" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="G12" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
+      <c r="C12" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
     </row>
     <row r="13" ht="71.25" spans="1:11">
-      <c r="A13" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="24" t="str">
+      <c r="A13" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B13" s="13" t="str">
         <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
-      <c r="C13" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G13" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
+      <c r="C13" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
     </row>
     <row r="14" spans="1:11">
       <c r="B14" s="7"/>
@@ -4521,7 +6696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K18"/>
@@ -4541,206 +6716,206 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:11">
-      <c r="A1" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="15" t="s">
+      <c r="A1" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="B1" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="D1" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="E1" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="F1" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="G1" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="H1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" s="15" t="s">
+      <c r="J1" s="10" t="s">
         <v>100</v>
       </c>
+      <c r="K1" s="10" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="2" ht="37" customHeight="1" spans="1:11">
-      <c r="A2" s="23"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="17" t="s">
-        <v>102</v>
+      <c r="A2" s="12"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="12" t="s">
+        <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
+        <v>11</v>
+      </c>
+      <c r="E2" s="33"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" ht="69" customHeight="1" spans="1:11">
-      <c r="A3" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="24" t="str">
+      <c r="A3" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" s="13" t="str">
         <f>"("&amp;Scenario!A38&amp;")"&amp;" 
 "&amp;Scenario!C38</f>
         <v>(TS032) 
 Validate the working of 'Top Menu' options' functionality</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>153</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>154</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
+      <c r="C3" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
     </row>
     <row r="4" ht="128.25" spans="1:11">
-      <c r="A4" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="B4" s="24" t="str">
+      <c r="A4" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="13" t="str">
         <f>"("&amp;Scenario!A38&amp;")"&amp;" 
 "&amp;Scenario!C38</f>
         <v>(TS032) 
 Validate the working of 'Top Menu' options' functionality</v>
       </c>
-      <c r="C4" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
+      <c r="C4" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="B5" s="24" t="str">
+      <c r="A5" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" s="13" t="str">
         <f>"("&amp;Scenario!A38&amp;")"&amp;" 
 "&amp;Scenario!C38</f>
         <v>(TS032) 
 Validate the working of 'Top Menu' options' functionality</v>
       </c>
-      <c r="C5" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
+      <c r="C5" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
     </row>
     <row r="6" ht="42.75" spans="1:11">
-      <c r="A6" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="B6" s="24" t="str">
+      <c r="A6" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B6" s="13" t="str">
         <f>"("&amp;Scenario!A38&amp;")"&amp;" 
 "&amp;Scenario!C38</f>
         <v>(TS032) 
 Validate the working of 'Top Menu' options' functionality</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
+      <c r="C6" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" ht="42.75" spans="1:11">
-      <c r="A7" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="B7" s="24" t="str">
+      <c r="A7" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B7" s="13" t="str">
         <f>"("&amp;Scenario!A38&amp;")"&amp;" 
 "&amp;Scenario!C38</f>
         <v>(TS032) 
 Validate the working of 'Top Menu' options' functionality</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>172</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
+      <c r="C7" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
     </row>
     <row r="8" spans="1:11">
       <c r="B8"/>
@@ -4786,7 +6961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K35"/>
@@ -4798,581 +6973,581 @@
     <col min="4" max="4" width="38.3833333333333" customWidth="1"/>
     <col min="5" max="5" width="53.025" style="3" customWidth="1"/>
     <col min="6" max="6" width="24.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="72.85" style="22" customWidth="1"/>
-    <col min="8" max="8" width="19.2916666666667" style="12" customWidth="1"/>
+    <col min="7" max="7" width="72.85" style="18" customWidth="1"/>
+    <col min="8" max="8" width="19.2916666666667" style="29" customWidth="1"/>
     <col min="9" max="9" width="7.75" customWidth="1"/>
     <col min="10" max="10" width="7.125" customWidth="1"/>
     <col min="11" max="11" width="41.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:11">
-      <c r="A1" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="15" t="s">
+      <c r="A1" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="B1" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="D1" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="E1" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="F1" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="G1" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="H1" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" s="15" t="s">
+      <c r="J1" s="10" t="s">
         <v>100</v>
       </c>
+      <c r="K1" s="10" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="2" ht="18" spans="1:11">
-      <c r="A2" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" s="23"/>
+      <c r="A2" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="12"/>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="23"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
+        <v>11</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" ht="114" spans="1:11">
-      <c r="A3" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="B3" s="24" t="s">
+      <c r="A3" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="F3" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="C3" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>179</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>180</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="H3" s="25"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
+      <c r="G3" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="H3" s="14"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
     </row>
     <row r="4" ht="42.75" spans="1:11">
-      <c r="A4" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="B4" s="24" t="s">
+      <c r="A4" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="F4" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="C4" s="41" t="s">
-        <v>183</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>179</v>
-      </c>
-      <c r="E4" s="42" t="s">
-        <v>184</v>
-      </c>
-      <c r="F4" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="H4" s="25"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
+      <c r="G4" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="H4" s="14"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="B5" s="24" t="s">
+      <c r="A5" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="F5" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="C5" s="41" t="s">
-        <v>187</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="F5" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="H5" s="25"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
+      <c r="G5" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="H5" s="14"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
     </row>
     <row r="6" ht="42.75" spans="1:11">
-      <c r="A6" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="B6" s="24" t="s">
+      <c r="A6" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="F6" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="C6" s="41" t="s">
-        <v>191</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="H6" s="25"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
+      <c r="G6" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="H6" s="14"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" ht="42.75" spans="1:11">
-      <c r="A7" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="B7" s="24" t="s">
+      <c r="A7" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="F7" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="C7" s="41" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="H7" s="25"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
+      <c r="G7" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="H7" s="14"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
     </row>
     <row r="8" ht="42.75" spans="1:11">
-      <c r="A8" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="B8" s="44" t="s">
+      <c r="A8" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="F8" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="C8" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="F8" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="G8" s="46" t="s">
-        <v>200</v>
-      </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="47"/>
+      <c r="G8" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="H8" s="38"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="38"/>
     </row>
     <row r="9" ht="42.75" spans="1:11">
-      <c r="A9" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="B9" s="44" t="s">
+      <c r="A9" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="C9" s="43" t="s">
-        <v>202</v>
-      </c>
-      <c r="D9" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="F9" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="G9" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="H9" s="47"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
+      <c r="G9" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="H9" s="38"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
     </row>
     <row r="10" ht="42.75" spans="1:11">
-      <c r="A10" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="B10" s="44" t="s">
+      <c r="A10" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="F10" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="C10" s="43" t="s">
-        <v>205</v>
-      </c>
-      <c r="D10" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>206</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="G10" s="46" t="s">
-        <v>207</v>
-      </c>
-      <c r="H10" s="47"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="47"/>
+      <c r="G10" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="H10" s="38"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="38"/>
     </row>
     <row r="11" ht="42.75" spans="1:11">
-      <c r="A11" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="B11" s="44" t="s">
+      <c r="A11" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="G11" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="H11" s="38"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="38"/>
+    </row>
+    <row r="12" ht="57" spans="1:11">
+      <c r="A12" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>285</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>286</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>281</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="H12" s="38"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="38"/>
+    </row>
+    <row r="13" ht="57" spans="1:11">
+      <c r="A13" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>285</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="G13" s="37" t="s">
+        <v>292</v>
+      </c>
+      <c r="H13" s="38"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="38"/>
+    </row>
+    <row r="14" ht="57" spans="1:11">
+      <c r="A14" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>296</v>
+      </c>
+      <c r="F14" s="40" t="s">
+        <v>216</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>297</v>
+      </c>
+      <c r="H14" s="38"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="38"/>
+    </row>
+    <row r="15" ht="42.75" spans="1:11">
+      <c r="A15" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="F15" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="C11" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="D11" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>210</v>
-      </c>
-      <c r="F11" s="49" t="s">
-        <v>211</v>
-      </c>
-      <c r="G11" s="50" t="s">
-        <v>212</v>
-      </c>
-      <c r="H11" s="47"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="47"/>
-    </row>
-    <row r="12" ht="57" spans="1:11">
-      <c r="A12" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="B12" s="44" t="s">
+      <c r="G15" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="H15" s="38"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="38"/>
+    </row>
+    <row r="16" ht="42.75" spans="1:11">
+      <c r="A16" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>304</v>
+      </c>
+      <c r="F16" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="C12" s="43" t="s">
-        <v>214</v>
-      </c>
-      <c r="D12" s="45" t="s">
-        <v>215</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>216</v>
-      </c>
-      <c r="F12" s="49" t="s">
-        <v>211</v>
-      </c>
-      <c r="G12" s="46" t="s">
-        <v>217</v>
-      </c>
-      <c r="H12" s="47"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="47"/>
-    </row>
-    <row r="13" ht="57" spans="1:11">
-      <c r="A13" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="B13" s="44" t="s">
+      <c r="G16" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="H16" s="38"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="38"/>
+    </row>
+    <row r="17" ht="42.75" spans="1:11">
+      <c r="A17" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>304</v>
+      </c>
+      <c r="F17" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="C13" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="D13" s="45" t="s">
-        <v>215</v>
-      </c>
-      <c r="E13" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="F13" s="44" t="s">
-        <v>221</v>
-      </c>
-      <c r="G13" s="46" t="s">
-        <v>222</v>
-      </c>
-      <c r="H13" s="47"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="47"/>
-    </row>
-    <row r="14" ht="57" spans="1:11">
-      <c r="A14" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="B14" s="44" t="s">
+      <c r="G17" s="41" t="s">
+        <v>309</v>
+      </c>
+      <c r="H17" s="38"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="38"/>
+    </row>
+    <row r="18" ht="42.75" spans="1:11">
+      <c r="A18" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>312</v>
+      </c>
+      <c r="F18" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="C14" s="43" t="s">
-        <v>224</v>
-      </c>
-      <c r="D14" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>226</v>
-      </c>
-      <c r="F14" s="49" t="s">
-        <v>146</v>
-      </c>
-      <c r="G14" s="46" t="s">
-        <v>227</v>
-      </c>
-      <c r="H14" s="47"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="47"/>
-    </row>
-    <row r="15" ht="42.75" spans="1:11">
-      <c r="A15" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="B15" s="44" t="s">
+      <c r="G18" s="37" t="s">
+        <v>313</v>
+      </c>
+      <c r="H18" s="38"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="38"/>
+    </row>
+    <row r="19" s="29" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A19" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="F19" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="43" t="s">
-        <v>229</v>
-      </c>
-      <c r="D15" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" s="43" t="s">
-        <v>230</v>
-      </c>
-      <c r="F15" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="G15" s="46" t="s">
-        <v>231</v>
-      </c>
-      <c r="H15" s="47"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="47"/>
-    </row>
-    <row r="16" ht="42.75" spans="1:11">
-      <c r="A16" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="B16" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="D16" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="F16" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="G16" s="46" t="s">
-        <v>235</v>
-      </c>
-      <c r="H16" s="47"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="47"/>
-    </row>
-    <row r="17" ht="42.75" spans="1:11">
-      <c r="A17" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="B17" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>237</v>
-      </c>
-      <c r="D17" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="E17" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="F17" s="49" t="s">
-        <v>107</v>
-      </c>
-      <c r="G17" s="50" t="s">
-        <v>239</v>
-      </c>
-      <c r="H17" s="47"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="47"/>
-    </row>
-    <row r="18" ht="42.75" spans="1:11">
-      <c r="A18" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B18" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="D18" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" s="45" t="s">
-        <v>242</v>
-      </c>
-      <c r="F18" s="49" t="s">
-        <v>107</v>
-      </c>
-      <c r="G18" s="46" t="s">
-        <v>243</v>
-      </c>
-      <c r="H18" s="47"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="48"/>
-      <c r="K18" s="47"/>
-    </row>
-    <row r="19" s="12" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A19" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="B19" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>245</v>
-      </c>
-      <c r="D19" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="E19" s="43" t="s">
-        <v>246</v>
-      </c>
-      <c r="F19" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="G19" s="46" t="s">
+      <c r="G19" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="H19" s="38"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="38"/>
+    </row>
+    <row r="20" s="29" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A20" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>247</v>
       </c>
-      <c r="H19" s="47"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="47"/>
-    </row>
-    <row r="20" s="12" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A20" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="B20" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="C20" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="D20" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" s="45" t="s">
-        <v>250</v>
-      </c>
-      <c r="F20" s="44" t="s">
-        <v>251</v>
-      </c>
-      <c r="G20" s="50" t="s">
-        <v>252</v>
-      </c>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="47"/>
+      <c r="C20" s="36" t="s">
+        <v>319</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>320</v>
+      </c>
+      <c r="F20" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="G20" s="41" t="s">
+        <v>322</v>
+      </c>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
     </row>
     <row r="21" customFormat="1" ht="71.25" spans="1:11">
-      <c r="A21" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="B21" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="C21" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="D21" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" s="45" t="s">
-        <v>250</v>
-      </c>
-      <c r="F21" s="44" t="s">
-        <v>255</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="H21" s="25" t="s">
-        <v>257</v>
-      </c>
-      <c r="I21" s="23"/>
-      <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
+      <c r="A21" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>324</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>320</v>
+      </c>
+      <c r="F21" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>327</v>
+      </c>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
     </row>
     <row r="22" spans="1:11">
       <c r="C22"/>
@@ -5486,595 +7661,595 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" style="36" customWidth="1"/>
-    <col min="2" max="2" width="25.875" style="37" customWidth="1"/>
-    <col min="3" max="3" width="32.625" style="36" customWidth="1"/>
-    <col min="4" max="4" width="30.875" style="36" customWidth="1"/>
-    <col min="5" max="5" width="42.35" style="36" customWidth="1"/>
-    <col min="6" max="6" width="15.2916666666667" style="36" customWidth="1"/>
-    <col min="7" max="7" width="86.6" style="36" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="36" customWidth="1"/>
-    <col min="9" max="9" width="7.75" style="36" customWidth="1"/>
-    <col min="10" max="10" width="7.125" style="36" customWidth="1"/>
-    <col min="11" max="11" width="10.875" style="36" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="36"/>
+    <col min="1" max="1" width="13.125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="25.875" style="27" customWidth="1"/>
+    <col min="3" max="3" width="32.625" style="26" customWidth="1"/>
+    <col min="4" max="4" width="30.875" style="26" customWidth="1"/>
+    <col min="5" max="5" width="42.35" style="26" customWidth="1"/>
+    <col min="6" max="6" width="15.2916666666667" style="26" customWidth="1"/>
+    <col min="7" max="7" width="86.6" style="26" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="26" customWidth="1"/>
+    <col min="9" max="9" width="7.75" style="26" customWidth="1"/>
+    <col min="10" max="10" width="7.125" style="26" customWidth="1"/>
+    <col min="11" max="11" width="10.875" style="26" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" s="36" customFormat="1" ht="15" spans="1:11">
-      <c r="A1" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="15" t="s">
+    <row r="1" s="26" customFormat="1" ht="15" spans="1:11">
+      <c r="A1" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="B1" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="D1" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="E1" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="F1" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="G1" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="H1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" s="15" t="s">
+      <c r="J1" s="10" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="2" s="36" customFormat="1" spans="1:11">
-      <c r="A2" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" s="27"/>
+      <c r="K1" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" s="26" customFormat="1" spans="1:11">
+      <c r="A2" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="21"/>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-    </row>
-    <row r="3" s="36" customFormat="1" ht="128.25" spans="1:11">
-      <c r="A3" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>263</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-    </row>
-    <row r="4" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A4" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F4" s="23" t="str">
+        <v>11</v>
+      </c>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+    </row>
+    <row r="3" s="26" customFormat="1" ht="128.25" spans="1:11">
+      <c r="A3" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A4" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F4" s="12" t="str">
         <f>SUBSTITUTE(MID(C4,22,30),"'","")</f>
         <v>About Us</v>
       </c>
-      <c r="G4" s="23" t="str">
+      <c r="G4" s="12" t="str">
         <f>"Should navigate user to "&amp;MID(C4,22,30)&amp;". A proper text/information should display on this page"</f>
         <v>Should navigate user to 'About Us'. A proper text/information should display on this page</v>
       </c>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-    </row>
-    <row r="5" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A5" s="23" t="s">
-        <v>267</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>268</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F5" s="23" t="str">
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+    </row>
+    <row r="5" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A5" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F5" s="12" t="str">
         <f t="shared" ref="F5:F18" si="0">SUBSTITUTE(MID(C5,22,30),"'","")</f>
         <v>Delivery Information</v>
       </c>
-      <c r="G5" s="23" t="str">
+      <c r="G5" s="12" t="str">
         <f>"Should navigate user to "&amp;MID(C5,22,30)&amp;". A proper text/information should display on this page"</f>
         <v>Should navigate user to 'Delivery Information'. A proper text/information should display on this page</v>
       </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-    </row>
-    <row r="6" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A6" s="23" t="s">
-        <v>269</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F6" s="23" t="str">
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+    </row>
+    <row r="6" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A6" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F6" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Privacy Policy</v>
       </c>
-      <c r="G6" s="23" t="str">
+      <c r="G6" s="12" t="str">
         <f>"Should navigate user to "&amp;MID(C6,22,30)&amp;". A proper text/information should display on this page"</f>
         <v>Should navigate user to 'Privacy Policy'. A proper text/information should display on this page</v>
       </c>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-    </row>
-    <row r="7" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A7" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F7" s="23" t="str">
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+    </row>
+    <row r="7" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A7" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Term &amp; Conditions</v>
       </c>
-      <c r="G7" s="23" t="str">
+      <c r="G7" s="12" t="str">
         <f t="shared" ref="G7:G18" si="1">"Should navigate user to "&amp;MID(C7,22,30)&amp;". A proper text/information should display on this page"</f>
         <v>Should navigate user to 'Term &amp; Conditions'. A proper text/information should display on this page</v>
       </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-    </row>
-    <row r="8" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A8" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F8" s="23" t="str">
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+    </row>
+    <row r="8" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A8" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F8" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Contact Us</v>
       </c>
-      <c r="G8" s="23" t="str">
+      <c r="G8" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Contact Us'. A proper text/information should display on this page</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-    </row>
-    <row r="9" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A9" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>276</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F9" s="23" t="str">
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+    </row>
+    <row r="9" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A9" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F9" s="12" t="str">
         <f t="shared" si="0"/>
         <v> Returns</v>
       </c>
-      <c r="G9" s="23" t="str">
+      <c r="G9" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to ' Returns'. A proper text/information should display on this page</v>
       </c>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
-    </row>
-    <row r="10" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A10" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F10" s="23" t="str">
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+    </row>
+    <row r="10" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A10" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F10" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Site Map</v>
       </c>
-      <c r="G10" s="23" t="str">
+      <c r="G10" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Site Map'. A proper text/information should display on this page</v>
       </c>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
-    </row>
-    <row r="11" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A11" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F11" s="23" t="str">
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+    </row>
+    <row r="11" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A11" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F11" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Brands</v>
       </c>
-      <c r="G11" s="23" t="str">
+      <c r="G11" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Brands'. A proper text/information should display on this page</v>
       </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-    </row>
-    <row r="12" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A12" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>286</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F12" s="23" t="str">
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A12" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F12" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Gift Voucher</v>
       </c>
-      <c r="G12" s="23" t="str">
+      <c r="G12" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Gift Voucher'. A proper text/information should display on this page</v>
       </c>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-    </row>
-    <row r="13" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A13" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F13" s="23" t="str">
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A13" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F13" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Affiliates</v>
       </c>
-      <c r="G13" s="23" t="str">
+      <c r="G13" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Affiliates'. A proper text/information should display on this page</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-    </row>
-    <row r="14" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A14" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F14" s="23" t="str">
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A14" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F14" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Specials</v>
       </c>
-      <c r="G14" s="23" t="str">
+      <c r="G14" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Specials'. A proper text/information should display on this page</v>
       </c>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-    </row>
-    <row r="15" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A15" s="23" t="s">
-        <v>293</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F15" s="23" t="str">
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+    </row>
+    <row r="15" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A15" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F15" s="12" t="str">
         <f t="shared" si="0"/>
         <v>My Account</v>
       </c>
-      <c r="G15" s="23" t="str">
+      <c r="G15" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'My Account'. A proper text/information should display on this page</v>
       </c>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-    </row>
-    <row r="16" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A16" s="23" t="s">
-        <v>296</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>297</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F16" s="23" t="str">
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A16" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F16" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Order History</v>
       </c>
-      <c r="G16" s="23" t="str">
+      <c r="G16" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Order History'. A proper text/information should display on this page</v>
       </c>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-    </row>
-    <row r="17" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A17" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>301</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F17" s="23" t="str">
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+    </row>
+    <row r="17" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A17" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F17" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Wish List</v>
       </c>
-      <c r="G17" s="23" t="str">
+      <c r="G17" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Wish List'. A proper text/information should display on this page</v>
       </c>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-    </row>
-    <row r="18" s="36" customFormat="1" ht="42.75" spans="1:11">
-      <c r="A18" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>303</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="F18" s="23" t="str">
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+    </row>
+    <row r="18" s="26" customFormat="1" ht="42.75" spans="1:11">
+      <c r="A18" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="F18" s="12" t="str">
         <f t="shared" si="0"/>
         <v>Newletter</v>
       </c>
-      <c r="G18" s="23" t="str">
+      <c r="G18" s="12" t="str">
         <f t="shared" si="1"/>
         <v>Should navigate user to 'Newletter'. A proper text/information should display on this page</v>
       </c>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="B19" s="38"/>
+      <c r="B19" s="28"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="B20" s="38"/>
+      <c r="B20" s="28"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="B21" s="38"/>
+      <c r="B21" s="28"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="B22" s="38"/>
+      <c r="B22" s="28"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="B23" s="38"/>
+      <c r="B23" s="28"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="B24" s="38"/>
+      <c r="B24" s="28"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="B25" s="38"/>
+      <c r="B25" s="28"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="B26" s="38"/>
+      <c r="B26" s="28"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="B27" s="38"/>
+      <c r="B27" s="28"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="B28" s="38"/>
+      <c r="B28" s="28"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="B29" s="38"/>
+      <c r="B29" s="28"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="B30" s="38"/>
+      <c r="B30" s="28"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="B31" s="38"/>
+      <c r="B31" s="28"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="B32" s="38"/>
+      <c r="B32" s="28"/>
     </row>
     <row r="33" spans="2:2">
-      <c r="B33" s="38"/>
+      <c r="B33" s="28"/>
     </row>
     <row r="34" spans="2:2">
-      <c r="B34" s="38"/>
+      <c r="B34" s="28"/>
     </row>
     <row r="35" spans="2:2">
-      <c r="B35" s="38"/>
+      <c r="B35" s="28"/>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" s="38"/>
+      <c r="B36" s="28"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -6087,7 +8262,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K53"/>
@@ -6097,8 +8272,8 @@
     <col min="2" max="2" width="28.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="72.125" customWidth="1"/>
     <col min="4" max="4" width="38.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="61.625" style="21" customWidth="1"/>
-    <col min="6" max="6" width="28.75" style="22" customWidth="1"/>
+    <col min="5" max="5" width="61.625" style="17" customWidth="1"/>
+    <col min="6" max="6" width="28.75" style="18" customWidth="1"/>
     <col min="7" max="7" width="64.75" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
     <col min="9" max="9" width="7.75" customWidth="1"/>
@@ -6107,47 +8282,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:11">
-      <c r="A1" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="15" t="s">
+      <c r="A1" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="B1" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="D1" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="E1" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="F1" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="G1" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="H1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" s="15" t="s">
+      <c r="J1" s="10" t="s">
         <v>100</v>
       </c>
+      <c r="K1" s="10" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="2" ht="18" spans="1:11">
-      <c r="A2" s="11" t="s">
-        <v>92</v>
+      <c r="A2" s="19" t="s">
+        <v>93</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>172</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
@@ -6156,827 +8331,827 @@
       <c r="F2"/>
     </row>
     <row r="3" ht="57" spans="1:11">
-      <c r="A3" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
+      <c r="A3" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
     </row>
     <row r="4" ht="57" spans="1:11">
-      <c r="A4" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>315</v>
-      </c>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
+      <c r="A4" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" ht="57" spans="1:11">
-      <c r="A5" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>318</v>
-      </c>
-      <c r="F5" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
+      <c r="A5" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
     </row>
     <row r="6" ht="57" spans="1:11">
-      <c r="A6" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>323</v>
-      </c>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
+      <c r="A6" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" ht="57" spans="1:11">
-      <c r="A7" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>326</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>327</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>328</v>
-      </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
+      <c r="A7" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
     </row>
     <row r="8" ht="57" spans="1:11">
-      <c r="A8" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="D8" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>326</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>331</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>332</v>
-      </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
+      <c r="A8" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>401</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
     </row>
     <row r="9" ht="57" spans="1:11">
-      <c r="A9" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>334</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>335</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>336</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>337</v>
-      </c>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
+      <c r="A9" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" ht="57" spans="1:11">
-      <c r="A10" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>340</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>336</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>341</v>
-      </c>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="23"/>
+      <c r="A10" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" ht="57" spans="1:11">
-      <c r="A11" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>343</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>344</v>
-      </c>
-      <c r="F11" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
+      <c r="A11" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>413</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" ht="57" spans="1:11">
-      <c r="A12" s="23" t="s">
-        <v>346</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>348</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>349</v>
-      </c>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
+      <c r="A12" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
     </row>
     <row r="13" ht="57" spans="1:11">
-      <c r="A13" s="23" t="s">
-        <v>350</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>351</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>352</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>353</v>
-      </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
+      <c r="A13" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
     </row>
     <row r="14" ht="57" spans="1:11">
-      <c r="A14" s="23" t="s">
-        <v>354</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>355</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>356</v>
-      </c>
-      <c r="F14" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G14" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
+      <c r="A14" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
     </row>
     <row r="15" ht="57" spans="1:11">
-      <c r="A15" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>359</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>360</v>
-      </c>
-      <c r="F15" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G15" s="23" t="s">
-        <v>361</v>
-      </c>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
+      <c r="A15" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>430</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
     </row>
     <row r="16" ht="57" spans="1:11">
-      <c r="A16" s="23" t="s">
-        <v>362</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>363</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>364</v>
-      </c>
-      <c r="F16" s="68" t="s">
-        <v>365</v>
-      </c>
-      <c r="G16" s="23" t="s">
-        <v>366</v>
-      </c>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
+      <c r="A16" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="F16" s="62" t="s">
+        <v>435</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
     </row>
     <row r="17" ht="57" spans="1:11">
-      <c r="A17" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>368</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>369</v>
-      </c>
-      <c r="F17" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
+      <c r="A17" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
     </row>
     <row r="18" ht="57" spans="1:11">
-      <c r="A18" s="23" t="s">
-        <v>371</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>372</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>374</v>
-      </c>
-      <c r="F18" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
+      <c r="A18" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
     </row>
     <row r="19" ht="57" spans="1:11">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="B19" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="F19" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G19" s="19" t="s">
-        <v>379</v>
-      </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
+      <c r="C19" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
     </row>
     <row r="20" ht="57" spans="1:11">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+    </row>
+    <row r="21" ht="57" spans="1:11">
+      <c r="A21" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+    </row>
+    <row r="22" ht="57" spans="1:11">
+      <c r="A22" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="F22" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="B20" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>382</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>383</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>384</v>
-      </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-    </row>
-    <row r="21" ht="57" spans="1:11">
-      <c r="A21" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>386</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>387</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>389</v>
-      </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-    </row>
-    <row r="22" ht="57" spans="1:11">
-      <c r="A22" s="23" t="s">
-        <v>390</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>391</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>392</v>
-      </c>
-      <c r="F22" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>393</v>
-      </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
+      <c r="G22" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
     </row>
     <row r="23" ht="57" spans="1:11">
-      <c r="A23" s="23" t="s">
-        <v>394</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>395</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>396</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>397</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>398</v>
-      </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
+      <c r="A23" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>466</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
     </row>
     <row r="24" ht="57" spans="1:11">
-      <c r="A24" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>400</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>401</v>
-      </c>
-      <c r="F24" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>402</v>
-      </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
+      <c r="A24" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>471</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
     </row>
     <row r="25" ht="57" spans="1:11">
-      <c r="A25" s="23" t="s">
-        <v>403</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>404</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>405</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
+      <c r="A25" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>475</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
     </row>
     <row r="26" ht="57" spans="1:11">
-      <c r="A26" s="23" t="s">
-        <v>408</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>410</v>
-      </c>
-      <c r="F26" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>411</v>
-      </c>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
+      <c r="A26" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>480</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
     </row>
     <row r="27" ht="57" spans="1:11">
-      <c r="A27" s="23" t="s">
-        <v>412</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>413</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>415</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>416</v>
-      </c>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
+      <c r="A27" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>484</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
     </row>
     <row r="28" ht="57" spans="1:11">
-      <c r="A28" s="23" t="s">
-        <v>417</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>418</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
+      <c r="A28" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>488</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>484</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
     </row>
     <row r="29" ht="57" spans="1:11">
-      <c r="A29" s="30" t="s">
-        <v>421</v>
-      </c>
-      <c r="B29" s="31" t="s">
-        <v>306</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>422</v>
-      </c>
-      <c r="D29" s="33"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="34" t="s">
-        <v>423</v>
-      </c>
-      <c r="K29" s="34" t="s">
-        <v>424</v>
+      <c r="A29" s="23" t="s">
+        <v>491</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>376</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>492</v>
+      </c>
+      <c r="D29" s="15"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23" t="s">
+        <v>493</v>
+      </c>
+      <c r="K29" s="23" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="30" ht="57" spans="1:11">
-      <c r="A30" s="23" t="s">
-        <v>425</v>
-      </c>
-      <c r="B30" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>426</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>392</v>
-      </c>
-      <c r="F30" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>428</v>
-      </c>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
+      <c r="A30" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>498</v>
+      </c>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
     </row>
     <row r="31" ht="57" spans="1:11">
-      <c r="A31" s="23" t="s">
-        <v>429</v>
-      </c>
-      <c r="B31" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>430</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>431</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="G31" s="19" t="s">
-        <v>432</v>
-      </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
+      <c r="A31" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>501</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>502</v>
+      </c>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
     </row>
     <row r="32" ht="57" spans="1:11">
-      <c r="A32" s="23" t="s">
-        <v>433</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>434</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>435</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>436</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
+      <c r="A32" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>504</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33"/>
       <c r="E33"/>
       <c r="F33"/>
     </row>
-    <row r="34" ht="57" spans="2:6">
+    <row r="34" spans="2:6">
       <c r="B34"/>
       <c r="E34"/>
       <c r="F34"/>
     </row>
-    <row r="35" ht="57" spans="2:6">
+    <row r="35" spans="2:6">
       <c r="B35"/>
       <c r="E35"/>
       <c r="F35"/>
     </row>
-    <row r="36" ht="57" spans="2:6">
+    <row r="36" spans="2:6">
       <c r="B36"/>
       <c r="E36"/>
       <c r="F36"/>
@@ -7047,846 +9222,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="52.6" style="14" customWidth="1"/>
-    <col min="3" max="3" width="60.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="38.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="43.3833333333333" customWidth="1"/>
-    <col min="6" max="6" width="28.75" customWidth="1"/>
-    <col min="7" max="7" width="64.75" customWidth="1"/>
-    <col min="8" max="8" width="13.375" customWidth="1"/>
-    <col min="9" max="9" width="7.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="11" width="42.725" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" spans="1:11">
-      <c r="A1" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="17"/>
-      <c r="B2" s="18"/>
-      <c r="C2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="19"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-    </row>
-    <row r="3" ht="28.5" spans="1:11">
-      <c r="A3" s="17" t="s">
-        <v>438</v>
-      </c>
-      <c r="B3" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>440</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-    </row>
-    <row r="4" ht="42.75" spans="1:11">
-      <c r="A4" s="17" t="s">
-        <v>443</v>
-      </c>
-      <c r="B4" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>444</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>392</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>446</v>
-      </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-    </row>
-    <row r="5" ht="42.75" spans="1:11">
-      <c r="A5" s="17" t="s">
-        <v>447</v>
-      </c>
-      <c r="B5" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>448</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-    </row>
-    <row r="6" ht="42.75" spans="1:11">
-      <c r="A6" s="17" t="s">
-        <v>451</v>
-      </c>
-      <c r="B6" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>452</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>453</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>454</v>
-      </c>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-    </row>
-    <row r="7" ht="42.75" spans="1:11">
-      <c r="A7" s="17" t="s">
-        <v>455</v>
-      </c>
-      <c r="B7" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>456</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>458</v>
-      </c>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-    </row>
-    <row r="8" ht="42.75" spans="1:11">
-      <c r="A8" s="17" t="s">
-        <v>459</v>
-      </c>
-      <c r="B8" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>460</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>461</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>462</v>
-      </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-    </row>
-    <row r="9" ht="42.75" spans="1:11">
-      <c r="A9" s="17" t="s">
-        <v>463</v>
-      </c>
-      <c r="B9" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>464</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>392</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>465</v>
-      </c>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-    </row>
-    <row r="10" ht="42.75" spans="1:11">
-      <c r="A10" s="17" t="s">
-        <v>466</v>
-      </c>
-      <c r="B10" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>467</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>468</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>469</v>
-      </c>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-    </row>
-    <row r="11" ht="57" spans="1:11">
-      <c r="A11" s="17" t="s">
-        <v>470</v>
-      </c>
-      <c r="B11" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>471</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>472</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>468</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>473</v>
-      </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-    </row>
-    <row r="12" ht="28.5" spans="1:11">
-      <c r="A12" s="17" t="s">
-        <v>474</v>
-      </c>
-      <c r="B12" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>475</v>
-      </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-    </row>
-    <row r="13" ht="28.5" spans="1:11">
-      <c r="A13" s="17" t="s">
-        <v>476</v>
-      </c>
-      <c r="B13" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>477</v>
-      </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-    </row>
-    <row r="14" ht="28.5" spans="1:11">
-      <c r="A14" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="B14" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>479</v>
-      </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-    </row>
-    <row r="15" ht="28.5" spans="1:11">
-      <c r="A15" s="17" t="s">
-        <v>480</v>
-      </c>
-      <c r="B15" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>481</v>
-      </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-    </row>
-    <row r="16" ht="28.5" spans="1:11">
-      <c r="A16" s="17" t="s">
-        <v>482</v>
-      </c>
-      <c r="B16" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>483</v>
-      </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-    </row>
-    <row r="17" ht="28.5" spans="1:11">
-      <c r="A17" s="17" t="s">
-        <v>484</v>
-      </c>
-      <c r="B17" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>485</v>
-      </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-    </row>
-    <row r="18" ht="28.5" spans="1:11">
-      <c r="A18" s="17" t="s">
-        <v>486</v>
-      </c>
-      <c r="B18" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>487</v>
-      </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-    </row>
-    <row r="19" ht="28.5" spans="1:11">
-      <c r="A19" s="17" t="s">
-        <v>488</v>
-      </c>
-      <c r="B19" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>489</v>
-      </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-    </row>
-    <row r="20" ht="42.75" spans="1:11">
-      <c r="A20" s="17" t="s">
-        <v>490</v>
-      </c>
-      <c r="B20" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>491</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>392</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-    </row>
-    <row r="21" ht="42.75" spans="1:11">
-      <c r="A21" s="17" t="s">
-        <v>493</v>
-      </c>
-      <c r="B21" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>392</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-    </row>
-    <row r="22" ht="28.5" spans="1:11">
-      <c r="A22" s="17" t="s">
-        <v>496</v>
-      </c>
-      <c r="B22" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C22" s="69" t="s">
-        <v>497</v>
-      </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-    </row>
-    <row r="23" ht="28.5" spans="1:11">
-      <c r="A23" s="17" t="s">
-        <v>498</v>
-      </c>
-      <c r="B23" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C23" s="69" t="s">
-        <v>499</v>
-      </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-    </row>
-    <row r="24" ht="28.5" spans="1:11">
-      <c r="A24" s="17" t="s">
-        <v>500</v>
-      </c>
-      <c r="B24" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-    </row>
-    <row r="25" ht="28.5" spans="1:11">
-      <c r="A25" s="17" t="s">
-        <v>501</v>
-      </c>
-      <c r="B25" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-    </row>
-    <row r="26" ht="28.5" spans="1:11">
-      <c r="A26" s="17" t="s">
-        <v>502</v>
-      </c>
-      <c r="B26" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-    </row>
-    <row r="27" ht="28.5" spans="1:11">
-      <c r="A27" s="17" t="s">
-        <v>503</v>
-      </c>
-      <c r="B27" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-    </row>
-    <row r="28" ht="28.5" spans="1:11">
-      <c r="A28" s="17" t="s">
-        <v>504</v>
-      </c>
-      <c r="B28" s="18" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
-        <v>(TS010) 
-Validate the working of 'Shopping Cart' functionality</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2">
-      <formula1>"working,complete"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="10.5" customWidth="1"/>
-    <col min="3" max="3" width="34.75" customWidth="1"/>
-    <col min="4" max="4" width="36.25" customWidth="1"/>
-    <col min="5" max="5" width="23.375" customWidth="1"/>
-    <col min="6" max="6" width="13.25" customWidth="1"/>
-    <col min="7" max="7" width="28.5" customWidth="1"/>
-    <col min="8" max="8" width="13.375" customWidth="1"/>
-    <col min="9" max="9" width="7.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" spans="1:11">
-      <c r="A1" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" ht="18" spans="1:11">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="12"/>
-      <c r="E2" s="12"/>
-    </row>
-    <row r="3" ht="18" spans="1:11">
-      <c r="B3" s="13"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-    </row>
-    <row r="4" ht="18" spans="1:11">
-      <c r="B4" s="13"/>
-      <c r="D4" s="12"/>
-    </row>
-    <row r="5" ht="18" spans="1:11">
-      <c r="B5" s="13"/>
-    </row>
-    <row r="6" ht="18" spans="1:11">
-      <c r="B6" s="13"/>
-    </row>
-    <row r="7" ht="18" spans="1:11">
-      <c r="B7" s="13"/>
-    </row>
-    <row r="8" ht="18" spans="1:11">
-      <c r="B8" s="11"/>
-    </row>
-    <row r="9" ht="18" spans="1:11">
-      <c r="B9" s="13"/>
-    </row>
-    <row r="10" ht="18" spans="1:11">
-      <c r="B10" s="13"/>
-    </row>
-    <row r="11" ht="18" spans="1:11">
-      <c r="B11" s="13"/>
-    </row>
-    <row r="12" ht="18" spans="1:11">
-      <c r="B12" s="13"/>
-    </row>
-    <row r="13" ht="18" spans="1:11">
-      <c r="B13" s="13"/>
-    </row>
-    <row r="14" ht="18" spans="1:11">
-      <c r="B14" s="11"/>
-    </row>
-    <row r="15" ht="18" spans="1:11">
-      <c r="B15" s="11"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/manual test/Open cert/OpenCartFrontend.xlsx
+++ b/manual test/Open cert/OpenCartFrontend.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="11580" firstSheet="1" activeTab="1"/>
+    <workbookView windowHeight="12180" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Version" sheetId="10" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="673">
   <si>
     <t>Version</t>
   </si>
@@ -45,7 +45,13 @@
     <t>Detail</t>
   </si>
   <si>
-    <t>Create test scenario &amp; test case from FRS only.</t>
+    <t>start date</t>
+  </si>
+  <si>
+    <t>Create test scenario &amp; test case based from FRS only.</t>
+  </si>
+  <si>
+    <t>Update test scenario &amp; test case based from demo</t>
   </si>
   <si>
     <t>Open Cart Frontend</t>
@@ -73,6 +79,12 @@
   </si>
   <si>
     <t>complete</t>
+  </si>
+  <si>
+    <t>Current Scenario doing + done</t>
+  </si>
+  <si>
+    <t>Scenario left</t>
   </si>
   <si>
     <t>Test Scenario ID</t>
@@ -2446,7 +2458,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2480,6 +2492,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2811,7 +2829,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2835,16 +2853,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2853,85 +2871,85 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2984,9 +3002,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3065,9 +3080,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3120,6 +3132,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -3177,14 +3195,7 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3196,13 +3207,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3399,25 +3403,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="10"/>
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstColumn" dxfId="7"/>
-      <tableStyleElement type="lastColumn" dxfId="6"/>
-      <tableStyleElement type="firstRowStripe" dxfId="5"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="4"/>
+      <tableStyleElement type="wholeTable" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="totalRow" dxfId="6"/>
+      <tableStyleElement type="firstColumn" dxfId="5"/>
+      <tableStyleElement type="lastColumn" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="20"/>
-      <tableStyleElement type="totalRow" dxfId="19"/>
-      <tableStyleElement type="firstRowStripe" dxfId="18"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="17"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="16"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="14"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="13"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="12"/>
-      <tableStyleElement type="pageFieldValues" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
+      <tableStyleElement type="pageFieldValues" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3686,54 +3690,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:C10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <dimension ref="B3:D10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="13.5" customWidth="1"/>
-    <col min="3" max="3" width="46.875" customWidth="1"/>
+    <col min="3" max="3" width="50.875" customWidth="1"/>
+    <col min="4" max="4" width="9.375"/>
   </cols>
   <sheetData>
-    <row r="3" ht="15" spans="2:3">
-      <c r="B3" s="61" t="s">
+    <row r="3" ht="15" spans="2:4">
+      <c r="B3" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="59" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" ht="15" spans="2:3">
-      <c r="B4" s="61">
+      <c r="D3" s="60" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="2:4">
+      <c r="B4" s="59">
         <v>1</v>
       </c>
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="61">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="2:4">
+      <c r="B5" s="59">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" ht="15" spans="2:3">
-      <c r="B5" s="61">
-        <v>2</v>
-      </c>
-      <c r="C5" s="61"/>
-    </row>
-    <row r="6" ht="15" spans="2:3">
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-    </row>
-    <row r="7" ht="15" spans="2:3">
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-    </row>
-    <row r="8" ht="15" spans="2:3">
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-    </row>
-    <row r="9" ht="15" spans="2:3">
-      <c r="B9" s="61"/>
-      <c r="C9" s="61"/>
-    </row>
-    <row r="10" ht="15" spans="2:3">
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
+      <c r="C5" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="61">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="2:4">
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="60"/>
+    </row>
+    <row r="7" ht="15" spans="2:4">
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="60"/>
+    </row>
+    <row r="8" ht="15" spans="2:4">
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="60"/>
+    </row>
+    <row r="9" ht="15" spans="2:4">
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="60"/>
+    </row>
+    <row r="10" ht="15" spans="2:4">
+      <c r="B10" s="59"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="60"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3762,47 +3783,47 @@
   <sheetData>
     <row r="1" ht="15" spans="1:11">
       <c r="A1" s="10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="12"/>
       <c r="B2" s="13"/>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" s="14"/>
       <c r="F2" s="12"/>
@@ -3814,28 +3835,28 @@
     </row>
     <row r="3" ht="28.5" spans="1:11">
       <c r="A3" s="12" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B3" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
@@ -3844,28 +3865,28 @@
     </row>
     <row r="4" ht="42.75" spans="1:11">
       <c r="A4" s="12" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B4" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
@@ -3874,28 +3895,28 @@
     </row>
     <row r="5" ht="42.75" spans="1:11">
       <c r="A5" s="12" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B5" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
@@ -3904,28 +3925,28 @@
     </row>
     <row r="6" ht="42.75" spans="1:11">
       <c r="A6" s="12" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B6" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -3934,28 +3955,28 @@
     </row>
     <row r="7" ht="42.75" spans="1:11">
       <c r="A7" s="12" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B7" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -3964,28 +3985,28 @@
     </row>
     <row r="8" ht="42.75" spans="1:11">
       <c r="A8" s="12" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B8" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
@@ -3994,28 +4015,28 @@
     </row>
     <row r="9" ht="42.75" spans="1:11">
       <c r="A9" s="12" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B9" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -4024,28 +4045,28 @@
     </row>
     <row r="10" ht="42.75" spans="1:11">
       <c r="A10" s="12" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B10" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
@@ -4054,28 +4075,28 @@
     </row>
     <row r="11" ht="57" spans="1:11">
       <c r="A11" s="12" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B11" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D11" s="14" t="s">
+        <v>546</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>542</v>
       </c>
-      <c r="E11" s="12" t="s">
-        <v>538</v>
-      </c>
       <c r="F11" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
@@ -4084,28 +4105,28 @@
     </row>
     <row r="12" ht="57" spans="1:11">
       <c r="A12" s="12" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B12" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>542</v>
-      </c>
-      <c r="E12" s="16" t="s">
         <v>546</v>
       </c>
+      <c r="E12" s="14" t="s">
+        <v>550</v>
+      </c>
       <c r="F12" s="12" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
@@ -4114,28 +4135,28 @@
     </row>
     <row r="13" ht="57" spans="1:11">
       <c r="A13" s="12" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B13" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>542</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>551</v>
+        <v>546</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>555</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
@@ -4144,28 +4165,28 @@
     </row>
     <row r="14" ht="57" spans="1:11">
       <c r="A14" s="12" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B14" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C14" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>546</v>
+      </c>
+      <c r="E14" s="14" t="s">
         <v>555</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>542</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>551</v>
-      </c>
       <c r="F14" s="12" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
@@ -4174,28 +4195,28 @@
     </row>
     <row r="15" ht="57" spans="1:11">
       <c r="A15" s="12" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B15" s="13" t="str">
-        <f>"("&amp;Scenario!A17&amp;")"&amp;" 
-"&amp;Scenario!C17</f>
+        <f>"("&amp;Scenario!A20&amp;")"&amp;" 
+"&amp;Scenario!C20</f>
         <v>(TS011) 
 Validate the working of 'Shopping Cart page' functionality</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>542</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>551</v>
+        <v>546</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>555</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
@@ -4204,28 +4225,28 @@
     </row>
     <row r="16" ht="42.75" spans="1:11">
       <c r="A16" s="12" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B16" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>564</v>
+        <v>519</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>568</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
@@ -4234,28 +4255,28 @@
     </row>
     <row r="17" ht="57" spans="1:11">
       <c r="A17" s="12" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B17" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="D17" s="14" t="s">
+        <v>572</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>568</v>
       </c>
-      <c r="E17" s="16" t="s">
-        <v>564</v>
-      </c>
       <c r="F17" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
@@ -4264,25 +4285,25 @@
     </row>
     <row r="18" ht="57" spans="1:11">
       <c r="A18" s="12" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C18" s="14" t="s">
+        <v>576</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>572</v>
       </c>
-      <c r="D18" s="14" t="s">
-        <v>568</v>
-      </c>
       <c r="E18" s="12" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
@@ -4291,25 +4312,25 @@
     </row>
     <row r="19" ht="57" spans="1:11">
       <c r="A19" s="12" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>568</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>576</v>
+        <v>572</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>580</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
@@ -4318,25 +4339,25 @@
     </row>
     <row r="20" ht="57" spans="1:11">
       <c r="A20" s="12" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>568</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>581</v>
+        <v>572</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>585</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
@@ -4345,25 +4366,25 @@
     </row>
     <row r="21" ht="57" spans="1:11">
       <c r="A21" s="12" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
@@ -4372,25 +4393,25 @@
     </row>
     <row r="22" ht="57" spans="1:11">
       <c r="A22" s="12" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>568</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>590</v>
+        <v>572</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>594</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
@@ -4399,25 +4420,25 @@
     </row>
     <row r="23" ht="71.25" spans="1:11">
       <c r="A23" s="12" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>595</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>596</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>597</v>
+        <v>599</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>600</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>601</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
@@ -4426,25 +4447,25 @@
     </row>
     <row r="24" ht="71.25" spans="1:11">
       <c r="A24" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>604</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>599</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>571</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>600</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>595</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>601</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>602</v>
+      <c r="E24" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>606</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
@@ -4453,25 +4474,25 @@
     </row>
     <row r="25" ht="57" spans="1:11">
       <c r="A25" s="12" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>568</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>606</v>
+        <v>572</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>610</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
@@ -4480,25 +4501,25 @@
     </row>
     <row r="26" ht="57" spans="1:11">
       <c r="A26" s="12" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C26" s="14" t="s">
+        <v>614</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>572</v>
+      </c>
+      <c r="E26" s="14" t="s">
         <v>610</v>
       </c>
-      <c r="D26" s="14" t="s">
-        <v>568</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>606</v>
-      </c>
       <c r="F26" s="12" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
@@ -4507,25 +4528,25 @@
     </row>
     <row r="27" ht="57" spans="1:11">
       <c r="A27" s="12" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>568</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>606</v>
+        <v>572</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>610</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
@@ -4534,25 +4555,25 @@
     </row>
     <row r="28" ht="57" spans="1:11">
       <c r="A28" s="12" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>568</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>618</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>619</v>
+        <v>572</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>622</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>623</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
@@ -4561,25 +4582,25 @@
     </row>
     <row r="29" ht="71.25" spans="1:11">
       <c r="A29" s="12" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>623</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>624</v>
+        <v>627</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>628</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
@@ -4588,28 +4609,28 @@
     </row>
     <row r="30" ht="42.75" spans="1:11">
       <c r="A30" s="12" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B30" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>629</v>
+        <v>519</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>633</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
@@ -4618,28 +4639,28 @@
     </row>
     <row r="31" ht="57" spans="1:11">
       <c r="A31" s="12" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B31" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D31" s="14" t="s">
+        <v>637</v>
+      </c>
+      <c r="E31" s="14" t="s">
         <v>633</v>
       </c>
-      <c r="E31" s="16" t="s">
-        <v>629</v>
-      </c>
       <c r="F31" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
@@ -4648,28 +4669,28 @@
     </row>
     <row r="32" ht="57" spans="1:11">
       <c r="A32" s="12" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B32" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>633</v>
-      </c>
-      <c r="E32" s="16" t="s">
         <v>637</v>
       </c>
+      <c r="E32" s="14" t="s">
+        <v>641</v>
+      </c>
       <c r="F32" s="12" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
@@ -4678,28 +4699,28 @@
     </row>
     <row r="33" ht="57" spans="1:11">
       <c r="A33" s="12" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B33" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C33" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>637</v>
+      </c>
+      <c r="E33" s="14" t="s">
         <v>641</v>
       </c>
-      <c r="D33" s="14" t="s">
-        <v>633</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>637</v>
-      </c>
       <c r="F33" s="12" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
@@ -4708,28 +4729,28 @@
     </row>
     <row r="34" ht="42.75" spans="1:11">
       <c r="A34" s="12" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B34" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="12"/>
@@ -4738,28 +4759,28 @@
     </row>
     <row r="35" ht="42.75" spans="1:11">
       <c r="A35" s="12" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B35" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
@@ -4768,28 +4789,28 @@
     </row>
     <row r="36" ht="42.75" spans="1:11">
       <c r="A36" s="12" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B36" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>652</v>
+        <v>519</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>656</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
@@ -4798,28 +4819,28 @@
     </row>
     <row r="37" ht="42.75" spans="1:11">
       <c r="A37" s="12" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B37" s="13" t="str">
-        <f>"("&amp;Scenario!A16&amp;")"&amp;" 
-"&amp;Scenario!C16</f>
+        <f>"("&amp;Scenario!A19&amp;")"&amp;" 
+"&amp;Scenario!C19</f>
         <v>(TS010) 
 Validate the working of 'Shopping Cart' functionality</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>515</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>656</v>
+        <v>519</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>660</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
@@ -4858,42 +4879,42 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -4902,48 +4923,48 @@
     </row>
     <row r="3" ht="42.75" spans="1:11">
       <c r="A3" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="G3" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="4" ht="42.75" spans="1:11">
       <c r="A4" t="s">
+        <v>669</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>659</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>661</v>
-      </c>
       <c r="E4" s="8" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G4" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
     </row>
   </sheetData>
@@ -4961,661 +4982,688 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
     <col min="2" max="2" width="9.875" customWidth="1"/>
     <col min="3" max="3" width="69.75" customWidth="1"/>
-    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="4" max="4" width="31.6333333333333" customWidth="1"/>
     <col min="5" max="5" width="21" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5583333333333" customWidth="1"/>
-    <col min="7" max="7" width="48.625" customWidth="1"/>
+    <col min="7" max="7" width="39.5583333333333" customWidth="1"/>
     <col min="9" max="9" width="69.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:10">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+        <v>6</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
     </row>
     <row r="3" ht="18" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
+        <v>8</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:10">
       <c r="B4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="E5" s="50" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="E6"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <f>COUNTA(E10:E43)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="E5" s="52" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="53" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="53" t="s">
+    <row r="8" spans="1:10">
+      <c r="D8" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E8">
+        <f>COUNTBLANK(E10:E43)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="B9" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="53" t="s">
+      <c r="C9" s="51" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" ht="18" spans="1:10">
-      <c r="A7" s="30" t="s">
+      <c r="D9" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="E9" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="F9" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="31">
+      <c r="G9" s="51" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" ht="18" spans="1:10">
+      <c r="A10" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="30">
         <f>COUNTIF('UserAccountAccess&amp;Validation'!B:B,"*TS001*")</f>
         <v>21</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" ht="18" spans="1:10">
-      <c r="A8" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="39" t="s">
+      <c r="F10" s="12"/>
+      <c r="G10" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" ht="18" spans="1:10">
+      <c r="A11" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="31">
+      <c r="C11" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="30">
         <f>COUNTIF('UserAccountAccess&amp;Validation'!B:B,"*TS002*")</f>
         <v>12</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="39" t="s">
+      <c r="F11" s="12"/>
+      <c r="G11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="31">
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="30">
         <f>COUNTIF('UserAccountAccess&amp;Validation'!B:B,"*TS003*")</f>
         <v>1</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="31">
+      <c r="F12" s="12"/>
+      <c r="G12" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="30">
         <f>COUNTIF('UserAccountAccess&amp;Validation'!B:B,"*TS004*")</f>
         <v>1</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="39" t="s">
+      <c r="F13" s="12"/>
+      <c r="G13" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-    </row>
-    <row r="13" ht="18" spans="1:10">
-      <c r="A13" s="30" t="s">
+      <c r="B14" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="54" t="s">
+      <c r="C14" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="54"/>
-      <c r="E13" s="55">
+      <c r="D14" s="12"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+    </row>
+    <row r="16" ht="18" spans="1:10">
+      <c r="A16" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="52"/>
+      <c r="E16" s="53">
         <f>COUNTA('Product Pages'!A3:A202)</f>
         <v>30</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F16" s="12">
         <f>COUNTIF('Product Pages'!J3:J9999,"Defect")</f>
         <v>1</v>
       </c>
-      <c r="G13" s="12"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="12"/>
       <c r="G16" s="12"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="39" t="s">
+      <c r="B18" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="31">
+      <c r="D18" s="12"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="30">
         <f>COUNTA('Shopping Cart page'!A1:A1008)</f>
         <v>36</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-    </row>
-    <row r="18" customFormat="1" spans="1:7">
-      <c r="A18" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="56" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58">
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+    </row>
+    <row r="21" customFormat="1" spans="1:7">
+      <c r="A21" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56">
         <f>COUNTA(HomePage!A3:A9998)</f>
         <v>11</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F21" s="12">
         <f>COUNTIF(HomePage!J3:J9999,"Defect")</f>
         <v>0</v>
       </c>
-      <c r="G18" s="12"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="12"/>
       <c r="G21" s="12"/>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>54</v>
+        <v>35</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>52</v>
       </c>
       <c r="D22" s="12"/>
-      <c r="E22" s="31"/>
+      <c r="E22" s="30"/>
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>56</v>
+        <v>35</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>54</v>
       </c>
       <c r="D23" s="12"/>
-      <c r="E23" s="31"/>
+      <c r="E23" s="30"/>
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>58</v>
+        <v>35</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>56</v>
       </c>
       <c r="D24" s="12"/>
-      <c r="E24" s="31"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>60</v>
+        <v>35</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>58</v>
       </c>
       <c r="D25" s="12"/>
-      <c r="E25" s="31"/>
+      <c r="E25" s="30"/>
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>62</v>
+        <v>35</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>60</v>
       </c>
       <c r="D26" s="12"/>
-      <c r="E26" s="31"/>
+      <c r="E26" s="30"/>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>64</v>
+        <v>35</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>62</v>
       </c>
       <c r="D27" s="12"/>
-      <c r="E27" s="31"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>66</v>
+        <v>35</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>64</v>
       </c>
       <c r="D28" s="12"/>
-      <c r="E28" s="31"/>
+      <c r="E28" s="30"/>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>68</v>
+        <v>35</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>66</v>
       </c>
       <c r="D29" s="12"/>
-      <c r="E29" s="31"/>
+      <c r="E29" s="30"/>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="39" t="s">
-        <v>70</v>
+        <v>35</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>68</v>
       </c>
       <c r="D30" s="12"/>
-      <c r="E30" s="31"/>
+      <c r="E30" s="30"/>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>72</v>
+        <v>35</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>70</v>
       </c>
       <c r="D31" s="12"/>
-      <c r="E31" s="31"/>
+      <c r="E31" s="30"/>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="56" t="s">
-        <v>74</v>
+        <v>35</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>72</v>
       </c>
       <c r="D32" s="12"/>
-      <c r="E32" s="31"/>
+      <c r="E32" s="30"/>
       <c r="F32" s="12"/>
       <c r="G32" s="12"/>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="56" t="s">
-        <v>76</v>
+        <v>35</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>74</v>
       </c>
       <c r="D33" s="12"/>
-      <c r="E33" s="31"/>
+      <c r="E33" s="30"/>
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="56" t="s">
-        <v>78</v>
+        <v>35</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>76</v>
       </c>
       <c r="D34" s="12"/>
-      <c r="E34" s="31"/>
+      <c r="E34" s="30"/>
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="56" t="s">
-        <v>80</v>
+        <v>35</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>78</v>
       </c>
       <c r="D35" s="12"/>
-      <c r="E35" s="31"/>
+      <c r="E35" s="30"/>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="39" t="s">
-        <v>82</v>
+        <v>35</v>
+      </c>
+      <c r="C36" s="54" t="s">
+        <v>80</v>
       </c>
       <c r="D36" s="12"/>
-      <c r="E36" s="31"/>
+      <c r="E36" s="30"/>
       <c r="F36" s="12"/>
       <c r="G36" s="12"/>
     </row>
-    <row r="37" customFormat="1" spans="1:7">
+    <row r="37" spans="1:7">
       <c r="A37" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" s="12"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="57" t="s">
+      <c r="B38" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58">
+      <c r="D38" s="12"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="12"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+    </row>
+    <row r="40" customFormat="1" spans="1:7">
+      <c r="A40" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56">
         <f>COUNTA(Header!A3:A200)</f>
         <v>19</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F40" s="12">
         <f>COUNTIF(Header!J3:J9999,"Defect")</f>
         <v>0</v>
       </c>
-      <c r="G37" s="12"/>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C38" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="D38" s="54"/>
-      <c r="E38" s="55">
+      <c r="G40" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" s="52"/>
+      <c r="E41" s="53">
         <f>COUNTA('Top Menu'!A3:A201)</f>
         <v>5</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F41" s="12">
         <f>COUNTIF('Top Menu'!J3:J9999,"defect")</f>
         <v>0</v>
       </c>
-      <c r="G38" s="12"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D39" s="54"/>
-      <c r="E39" s="55">
+      <c r="G41" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" s="52" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="52"/>
+      <c r="E42" s="53">
         <f>COUNTA(Footer!A3:A200)</f>
         <v>16</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F42" s="12">
         <f>COUNTIF(Footer!J3:J9999,"defect")</f>
         <v>0</v>
       </c>
-      <c r="G39" s="12"/>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="26"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E41" s="60">
-        <f>SUM(E7:E40)</f>
+      <c r="G42" s="12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="D43" s="12"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="25"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="E44" s="58">
+        <f>SUM(E10:E43)</f>
         <v>152</v>
       </c>
     </row>
@@ -5624,79 +5672,79 @@
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="C13:E13">
-    <cfRule type="expression" dxfId="0" priority="4">
+  <conditionalFormatting sqref="C16:E16">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>'Product Pages'!$D$2="working"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="4">
       <formula>'Product Pages'!$D$2="complete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>'Product Pages'!$D$2="working"</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:E17">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="C20:E20">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>'Shopping Cart page'!$D$2="complete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>'Shopping Cart page'!$D$2="working"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:D18">
-    <cfRule type="expression" dxfId="1" priority="18">
-      <formula>HomePage!$C$2="working"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="17">
+  <conditionalFormatting sqref="C21:D21">
+    <cfRule type="expression" dxfId="1" priority="17">
       <formula>HomePage!$C$2="complete"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E18">
-    <cfRule type="expression" dxfId="0" priority="19">
-      <formula>HomePage!$C$2="complete"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="20">
+    <cfRule type="expression" dxfId="0" priority="18">
       <formula>HomePage!$C$2="working"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C37:D37">
-    <cfRule type="expression" dxfId="0" priority="11">
+  <conditionalFormatting sqref="E21">
+    <cfRule type="expression" dxfId="1" priority="19">
+      <formula>HomePage!$C$2="complete"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="20">
+      <formula>HomePage!$C$2="working"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40:D40">
+    <cfRule type="expression" dxfId="1" priority="11">
       <formula>'Top Menu'!$D$2="complete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="12">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>Header!$D$2="working"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E37">
-    <cfRule type="expression" dxfId="0" priority="13">
+  <conditionalFormatting sqref="E40">
+    <cfRule type="expression" dxfId="1" priority="13">
       <formula>'Top Menu'!$D$2="complete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="14">
+    <cfRule type="expression" dxfId="0" priority="14">
       <formula>Header!$D$2="working"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C38:E38">
-    <cfRule type="expression" dxfId="0" priority="15">
+  <conditionalFormatting sqref="C41:E41">
+    <cfRule type="expression" dxfId="1" priority="15">
       <formula>'Top Menu'!$D$2="Complete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="16">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>'Top Menu'!$D$2="Working"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C39:E39">
-    <cfRule type="expression" dxfId="0" priority="9">
+  <conditionalFormatting sqref="C42:E42">
+    <cfRule type="expression" dxfId="1" priority="9">
       <formula>Footer!$D$2="complete"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="10">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>Footer!$D$2="working"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="A7" location="Register!A1" display="TS001"/>
+    <hyperlink ref="A10" location="Register!A1" display="TS001"/>
     <hyperlink ref="B2" r:id="rId1" display="https://demo.opencart.com/" tooltip="https://demo.opencart.com/"/>
-    <hyperlink ref="A8" location="TS002!A1" display="TS002"/>
+    <hyperlink ref="A11" location="TS002!A1" display="TS002"/>
     <hyperlink ref="B3" r:id="rId2" display="https://drive.google.com/drive/folders/1nBs25k9jTb06qrV-5fTC75gtPOR6uW4V"/>
-    <hyperlink ref="A18" location="HomePage!A1" display="TS012"/>
-    <hyperlink ref="A37" location="Header!A1" display="TS031"/>
-    <hyperlink ref="A38" location="'Top Menu'!A1" display="TS032"/>
-    <hyperlink ref="A13" location="'Product Pages'!A1" display="TS007"/>
+    <hyperlink ref="A21" location="HomePage!A1" display="TS012"/>
+    <hyperlink ref="A40" location="Header!A1" display="TS031"/>
+    <hyperlink ref="A41" location="'Top Menu'!A1" display="TS032"/>
+    <hyperlink ref="A16" location="'Product Pages'!A1" display="TS007"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -5710,7 +5758,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="56.625" style="43" customWidth="1"/>
+    <col min="2" max="2" width="56.625" style="28" customWidth="1"/>
     <col min="3" max="3" width="48.625" customWidth="1"/>
     <col min="4" max="4" width="36.25" customWidth="1"/>
     <col min="5" max="5" width="23.375" customWidth="1"/>
@@ -5724,530 +5772,530 @@
   <sheetData>
     <row r="1" ht="15" spans="1:11">
       <c r="A1" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="C1" s="44" t="s">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>98</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1" s="44" t="s">
-        <v>96</v>
+        <v>99</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>100</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G1" s="44" t="s">
-        <v>98</v>
+        <v>101</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>102</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" ht="36" spans="1:11">
       <c r="A2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="45" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>106</v>
+      </c>
+      <c r="B2" s="43" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A11,Scenario!C11)</f>
         <v>TS002
 Validate the working of 'Login' functionality</v>
       </c>
-      <c r="C2" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" s="29"/>
+      <c r="C2" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="28"/>
     </row>
     <row r="3" ht="28.5" spans="1:11">
       <c r="A3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>108</v>
+      </c>
+      <c r="B3" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A11,Scenario!C11)</f>
         <v>TS002
 Validate the working of 'Login' functionality</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
+        <v>109</v>
+      </c>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
     </row>
     <row r="4" ht="28.5" spans="1:11">
       <c r="A4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>110</v>
+      </c>
+      <c r="B4" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A11,Scenario!C11)</f>
         <v>TS002
 Validate the working of 'Login' functionality</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" ht="28.5" spans="1:11">
       <c r="A5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B5" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>112</v>
+      </c>
+      <c r="B5" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A11,Scenario!C11)</f>
         <v>TS002
 Validate the working of 'Login' functionality</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="29"/>
+        <v>113</v>
+      </c>
+      <c r="D5" s="28"/>
     </row>
     <row r="6" customFormat="1" ht="28.5" spans="1:11">
       <c r="A6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>114</v>
+      </c>
+      <c r="B6" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A11,Scenario!C11)</f>
         <v>TS002
 Validate the working of 'Login' functionality</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" s="29"/>
+        <v>115</v>
+      </c>
+      <c r="D6" s="28"/>
     </row>
     <row r="7" ht="28.5" spans="1:11">
       <c r="A7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B7" s="47" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>116</v>
+      </c>
+      <c r="B7" s="45" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A11,Scenario!C11)</f>
         <v>TS002
 Validate the working of 'Login' functionality</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" s="29"/>
+        <v>117</v>
+      </c>
+      <c r="D7" s="28"/>
     </row>
     <row r="8" ht="28.5" spans="1:11">
       <c r="A8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>118</v>
+      </c>
+      <c r="B8" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A11,Scenario!C11)</f>
         <v>TS002
 Validate the working of 'Login' functionality</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D8" s="29"/>
+        <v>119</v>
+      </c>
+      <c r="D8" s="28"/>
     </row>
     <row r="9" ht="28.5" spans="1:11">
       <c r="A9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B9" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>120</v>
+      </c>
+      <c r="B9" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A11,Scenario!C11)</f>
         <v>TS002
 Validate the working of 'Login' functionality</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" s="29"/>
+        <v>121</v>
+      </c>
+      <c r="D9" s="28"/>
     </row>
     <row r="10" ht="28.5" spans="1:11">
       <c r="A10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>122</v>
+      </c>
+      <c r="B10" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A11,Scenario!C11)</f>
         <v>TS002
 Validate the working of 'Login' functionality</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
-      </c>
-      <c r="D10" s="29"/>
+        <v>123</v>
+      </c>
+      <c r="D10" s="28"/>
     </row>
     <row r="11" ht="28.5" spans="1:11">
       <c r="A11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>124</v>
+      </c>
+      <c r="B11" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A11,Scenario!C11)</f>
         <v>TS002
 Validate the working of 'Login' functionality</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D11" s="29"/>
+        <v>125</v>
+      </c>
+      <c r="D11" s="28"/>
     </row>
     <row r="12" ht="28.5" spans="1:11">
       <c r="A12" t="s">
-        <v>122</v>
-      </c>
-      <c r="B12" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>126</v>
+      </c>
+      <c r="B12" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A11,Scenario!C11)</f>
         <v>TS002
 Validate the working of 'Login' functionality</v>
       </c>
       <c r="C12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="29"/>
+        <v>127</v>
+      </c>
+      <c r="D12" s="28"/>
     </row>
     <row r="13" ht="28.5" spans="1:11">
       <c r="A13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)</f>
+        <v>128</v>
+      </c>
+      <c r="B13" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A11,Scenario!C11)</f>
         <v>TS002
 Validate the working of 'Login' functionality</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
-      </c>
-      <c r="D13" s="29"/>
+        <v>129</v>
+      </c>
+      <c r="D13" s="28"/>
     </row>
     <row r="14" ht="28.5" spans="1:11">
       <c r="A14" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>130</v>
+      </c>
+      <c r="B14" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D14" s="29"/>
+        <v>131</v>
+      </c>
+      <c r="D14" s="28"/>
     </row>
     <row r="15" ht="28.5" spans="1:11">
       <c r="A15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B15" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>132</v>
+      </c>
+      <c r="B15" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D15" s="29"/>
+        <v>133</v>
+      </c>
+      <c r="D15" s="28"/>
     </row>
     <row r="16" ht="28.5" spans="1:11">
       <c r="A16" t="s">
-        <v>130</v>
-      </c>
-      <c r="B16" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>134</v>
+      </c>
+      <c r="B16" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
-      </c>
-      <c r="D16" s="29"/>
+        <v>135</v>
+      </c>
+      <c r="D16" s="28"/>
     </row>
     <row r="17" ht="28.5" spans="1:4">
       <c r="A17" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>136</v>
+      </c>
+      <c r="B17" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
-      </c>
-      <c r="D17" s="29"/>
+        <v>137</v>
+      </c>
+      <c r="D17" s="28"/>
     </row>
     <row r="18" ht="28.5" spans="1:4">
       <c r="A18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B18" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>138</v>
+      </c>
+      <c r="B18" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
-      </c>
-      <c r="D18" s="29"/>
+        <v>139</v>
+      </c>
+      <c r="D18" s="28"/>
     </row>
     <row r="19" ht="28.5" spans="1:4">
       <c r="A19" t="s">
-        <v>136</v>
-      </c>
-      <c r="B19" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>140</v>
+      </c>
+      <c r="B19" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
-      </c>
-      <c r="D19" s="29"/>
+        <v>141</v>
+      </c>
+      <c r="D19" s="28"/>
     </row>
     <row r="20" ht="28.5" spans="1:4">
       <c r="A20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B20" s="46" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>142</v>
+      </c>
+      <c r="B20" s="44" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C20" t="s">
-        <v>139</v>
-      </c>
-      <c r="D20" s="29"/>
+        <v>143</v>
+      </c>
+      <c r="D20" s="28"/>
     </row>
     <row r="21" ht="28.5" spans="1:4">
       <c r="A21" t="s">
-        <v>140</v>
-      </c>
-      <c r="B21" s="47" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>144</v>
+      </c>
+      <c r="B21" s="45" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
-      </c>
-      <c r="D21" s="29"/>
+        <v>145</v>
+      </c>
+      <c r="D21" s="28"/>
     </row>
     <row r="22" ht="28.5" spans="1:4">
       <c r="A22" t="s">
-        <v>142</v>
-      </c>
-      <c r="B22" s="47" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>146</v>
+      </c>
+      <c r="B22" s="45" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C22" t="s">
-        <v>143</v>
-      </c>
-      <c r="D22" s="29"/>
+        <v>147</v>
+      </c>
+      <c r="D22" s="28"/>
     </row>
     <row r="23" ht="28.5" spans="1:4">
       <c r="A23" t="s">
-        <v>144</v>
-      </c>
-      <c r="B23" s="47" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>148</v>
+      </c>
+      <c r="B23" s="45" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C23" t="s">
-        <v>145</v>
-      </c>
-      <c r="D23" s="29"/>
+        <v>149</v>
+      </c>
+      <c r="D23" s="28"/>
     </row>
     <row r="24" ht="28.5" spans="1:4">
       <c r="A24" t="s">
-        <v>146</v>
-      </c>
-      <c r="B24" s="47" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>150</v>
+      </c>
+      <c r="B24" s="45" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C24" t="s">
-        <v>147</v>
-      </c>
-      <c r="D24" s="29"/>
+        <v>151</v>
+      </c>
+      <c r="D24" s="28"/>
     </row>
     <row r="25" ht="28.5" spans="1:4">
       <c r="A25" t="s">
-        <v>148</v>
-      </c>
-      <c r="B25" s="47" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>152</v>
+      </c>
+      <c r="B25" s="45" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C25" t="s">
-        <v>139</v>
-      </c>
-      <c r="D25" s="29"/>
+        <v>143</v>
+      </c>
+      <c r="D25" s="28"/>
     </row>
     <row r="26" ht="33" spans="1:4">
       <c r="A26" t="s">
-        <v>149</v>
-      </c>
-      <c r="B26" s="48" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>153</v>
+      </c>
+      <c r="B26" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
-      </c>
-      <c r="D26" s="29"/>
+        <v>154</v>
+      </c>
+      <c r="D26" s="28"/>
     </row>
     <row r="27" ht="33" spans="1:4">
       <c r="A27" t="s">
-        <v>151</v>
-      </c>
-      <c r="B27" s="48" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>155</v>
+      </c>
+      <c r="B27" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C27" t="s">
-        <v>152</v>
-      </c>
-      <c r="D27" s="29"/>
+        <v>156</v>
+      </c>
+      <c r="D27" s="28"/>
     </row>
     <row r="28" ht="33" spans="1:4">
       <c r="A28" t="s">
-        <v>153</v>
-      </c>
-      <c r="B28" s="48" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>157</v>
+      </c>
+      <c r="B28" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C28" t="s">
-        <v>154</v>
-      </c>
-      <c r="D28" s="29"/>
+        <v>158</v>
+      </c>
+      <c r="D28" s="28"/>
     </row>
     <row r="29" ht="33" spans="1:4">
       <c r="A29" t="s">
-        <v>155</v>
-      </c>
-      <c r="B29" s="48" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>159</v>
+      </c>
+      <c r="B29" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C29" t="s">
-        <v>156</v>
-      </c>
-      <c r="D29" s="29"/>
+        <v>160</v>
+      </c>
+      <c r="D29" s="28"/>
     </row>
     <row r="30" ht="33" spans="1:4">
       <c r="A30" t="s">
-        <v>157</v>
-      </c>
-      <c r="B30" s="48" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>161</v>
+      </c>
+      <c r="B30" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C30" t="s">
-        <v>158</v>
-      </c>
-      <c r="D30" s="29"/>
+        <v>162</v>
+      </c>
+      <c r="D30" s="28"/>
     </row>
     <row r="31" ht="33" spans="1:4">
       <c r="A31" t="s">
-        <v>159</v>
-      </c>
-      <c r="B31" s="48" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>163</v>
+      </c>
+      <c r="B31" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C31" t="s">
-        <v>160</v>
-      </c>
-      <c r="D31" s="29"/>
+        <v>164</v>
+      </c>
+      <c r="D31" s="28"/>
     </row>
     <row r="32" ht="33" spans="1:4">
       <c r="A32" t="s">
-        <v>161</v>
-      </c>
-      <c r="B32" s="48" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>165</v>
+      </c>
+      <c r="B32" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C32" t="s">
-        <v>162</v>
-      </c>
-      <c r="D32" s="29"/>
+        <v>166</v>
+      </c>
+      <c r="D32" s="28"/>
     </row>
     <row r="33" ht="33" spans="1:4">
       <c r="A33" t="s">
-        <v>163</v>
-      </c>
-      <c r="B33" s="48" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>167</v>
+      </c>
+      <c r="B33" s="46" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C33" t="s">
-        <v>164</v>
-      </c>
-      <c r="D33" s="29"/>
+        <v>168</v>
+      </c>
+      <c r="D33" s="28"/>
     </row>
     <row r="34" ht="28.5" spans="1:4">
       <c r="A34" t="s">
-        <v>165</v>
-      </c>
-      <c r="B34" s="43" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A7,Scenario!C7)</f>
+        <v>169</v>
+      </c>
+      <c r="B34" s="28" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
         <v>TS001
 Validate the working of 'Register an account' functionality</v>
       </c>
       <c r="C34" t="s">
-        <v>166</v>
-      </c>
-      <c r="D34" s="29"/>
+        <v>170</v>
+      </c>
+      <c r="D34" s="28"/>
     </row>
     <row r="35" ht="28.5" spans="1:4">
       <c r="A35" t="s">
-        <v>167</v>
-      </c>
-      <c r="B35" s="43" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A9,Scenario!C9)</f>
+        <v>171</v>
+      </c>
+      <c r="B35" s="28" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A12,Scenario!C12)</f>
         <v>TS003
 Validate the working of 'Logout' functionality</v>
       </c>
       <c r="C35" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" ht="28.5" spans="1:4">
       <c r="A36" t="s">
-        <v>169</v>
-      </c>
-      <c r="B36" s="43" t="str">
-        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A10,Scenario!C10)</f>
+        <v>173</v>
+      </c>
+      <c r="B36" s="28" t="str">
+        <f>_xlfn.TEXTJOIN(CHAR(10),,Scenario!A13,Scenario!C13)</f>
         <v>TS004
 Validate the working of 'Forgot Password' functionality</v>
       </c>
       <c r="C36" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" location="Scenario!A1" display="=TEXTJOIN(CHAR(10),,Scenario!A8,Scenario!C8)"/>
+    <hyperlink ref="B2" location="Scenario!A1" display="=TEXTJOIN(CHAR(10),,Scenario!A11,Scenario!C11)"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -6286,72 +6334,72 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:11">
       <c r="A1" s="10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="1" ht="18" spans="1:11">
-      <c r="A2" s="19" t="s">
-        <v>171</v>
+      <c r="A2" s="18" t="s">
+        <v>175</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="142.5" spans="1:11">
       <c r="A3" s="12" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B3" s="13" t="str">
-        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <f>"("&amp;Scenario!$A21&amp;")"&amp;Scenario!$C21</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="D3" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="E3" s="33" t="s">
-        <v>176</v>
+        <v>178</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>180</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="G3" s="33" t="s">
-        <v>178</v>
+        <v>181</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>182</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
@@ -6360,26 +6408,26 @@
     </row>
     <row r="4" ht="71.25" spans="1:11">
       <c r="A4" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="B4" s="13" t="str">
+        <f>"("&amp;Scenario!$A21&amp;")"&amp;Scenario!$C21</f>
+        <v>(TS012)Validate the working of 'Home page' functionality</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="B4" s="13" t="str">
-        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
-        <v>(TS012)Validate the working of 'Home page' functionality</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>175</v>
-      </c>
       <c r="E4" s="14" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>183</v>
+        <v>186</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>187</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
@@ -6388,26 +6436,26 @@
     </row>
     <row r="5" ht="42.75" spans="1:11">
       <c r="A5" s="12" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B5" s="13" t="str">
-        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <f>"("&amp;Scenario!$A21&amp;")"&amp;Scenario!$C21</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>175</v>
+        <v>189</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>179</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="G5" s="33" t="s">
-        <v>187</v>
+        <v>181</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>191</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
@@ -6416,26 +6464,26 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="12" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B6" s="13" t="str">
-        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <f>"("&amp;Scenario!$A21&amp;")"&amp;Scenario!$C21</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>175</v>
+        <v>193</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>179</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="G6" s="32" t="s">
-        <v>191</v>
+        <v>181</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>195</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -6444,26 +6492,26 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="12" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B7" s="13" t="str">
-        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <f>"("&amp;Scenario!$A21&amp;")"&amp;Scenario!$C21</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>175</v>
+        <v>197</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>179</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="G7" s="32" t="s">
-        <v>195</v>
+        <v>181</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>199</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -6472,26 +6520,26 @@
     </row>
     <row r="8" ht="28.5" spans="1:11">
       <c r="A8" s="12" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B8" s="13" t="str">
-        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <f>"("&amp;Scenario!$A21&amp;")"&amp;Scenario!$C21</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>175</v>
+        <v>201</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>179</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="G8" s="33" t="s">
-        <v>199</v>
+        <v>181</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>203</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
@@ -6500,26 +6548,26 @@
     </row>
     <row r="9" ht="28.5" spans="1:11">
       <c r="A9" s="12" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B9" s="13" t="str">
-        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <f>"("&amp;Scenario!$A21&amp;")"&amp;Scenario!$C21</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>175</v>
+        <v>205</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>179</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="G9" s="32" t="s">
-        <v>204</v>
+        <v>207</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>208</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -6528,26 +6576,26 @@
     </row>
     <row r="10" ht="114" spans="1:11">
       <c r="A10" s="12" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B10" s="13" t="str">
-        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <f>"("&amp;Scenario!$A21&amp;")"&amp;Scenario!$C21</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>175</v>
+        <v>210</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>179</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="G10" s="42" t="s">
-        <v>208</v>
+        <v>181</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>212</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
@@ -6556,26 +6604,26 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="12" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B11" s="13" t="str">
-        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <f>"("&amp;Scenario!$A21&amp;")"&amp;Scenario!$C21</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>211</v>
+        <v>214</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>215</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="G11" s="33" t="s">
-        <v>212</v>
+        <v>181</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>216</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
@@ -6584,26 +6632,26 @@
     </row>
     <row r="12" ht="28.5" spans="1:11">
       <c r="A12" s="12" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B12" s="13" t="str">
-        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <f>"("&amp;Scenario!$A21&amp;")"&amp;Scenario!$C21</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
-      <c r="C12" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>215</v>
+      <c r="C12" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>219</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>204</v>
+        <v>220</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>208</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
@@ -6612,26 +6660,26 @@
     </row>
     <row r="13" ht="71.25" spans="1:11">
       <c r="A13" s="12" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B13" s="13" t="str">
-        <f>"("&amp;Scenario!$A18&amp;")"&amp;Scenario!$C18</f>
+        <f>"("&amp;Scenario!$A21&amp;")"&amp;Scenario!$C21</f>
         <v>(TS012)Validate the working of 'Home page' functionality</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>219</v>
+      <c r="C13" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>223</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="G13" s="33" t="s">
-        <v>220</v>
+        <v>181</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>224</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
@@ -6717,49 +6765,49 @@
   <sheetData>
     <row r="1" ht="15" spans="1:11">
       <c r="A1" s="10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" ht="37" customHeight="1" spans="1:11">
       <c r="A2" s="12"/>
       <c r="B2" s="13"/>
       <c r="C2" s="12" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="33"/>
+        <v>13</v>
+      </c>
+      <c r="E2" s="32"/>
       <c r="F2" s="12"/>
       <c r="G2" s="14"/>
       <c r="H2" s="12"/>
@@ -6769,28 +6817,28 @@
     </row>
     <row r="3" ht="69" customHeight="1" spans="1:11">
       <c r="A3" s="12" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B3" s="13" t="str">
-        <f>"("&amp;Scenario!A38&amp;")"&amp;" 
-"&amp;Scenario!C38</f>
+        <f>"("&amp;Scenario!A41&amp;")"&amp;" 
+"&amp;Scenario!C41</f>
         <v>(TS032) 
 Validate the working of 'Top Menu' options' functionality</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="E3" s="33" t="s">
-        <v>224</v>
+        <v>226</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>228</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
@@ -6799,28 +6847,28 @@
     </row>
     <row r="4" ht="128.25" spans="1:11">
       <c r="A4" s="12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B4" s="13" t="str">
-        <f>"("&amp;Scenario!A38&amp;")"&amp;" 
-"&amp;Scenario!C38</f>
+        <f>"("&amp;Scenario!A41&amp;")"&amp;" 
+"&amp;Scenario!C41</f>
         <v>(TS032) 
 Validate the working of 'Top Menu' options' functionality</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>175</v>
+        <v>231</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>179</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
@@ -6829,28 +6877,28 @@
     </row>
     <row r="5" ht="42.75" spans="1:11">
       <c r="A5" s="12" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B5" s="13" t="str">
-        <f>"("&amp;Scenario!A38&amp;")"&amp;" 
-"&amp;Scenario!C38</f>
+        <f>"("&amp;Scenario!A41&amp;")"&amp;" 
+"&amp;Scenario!C41</f>
         <v>(TS032) 
 Validate the working of 'Top Menu' options' functionality</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>175</v>
+        <v>235</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>179</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
@@ -6859,28 +6907,28 @@
     </row>
     <row r="6" ht="42.75" spans="1:11">
       <c r="A6" s="12" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B6" s="13" t="str">
-        <f>"("&amp;Scenario!A38&amp;")"&amp;" 
-"&amp;Scenario!C38</f>
+        <f>"("&amp;Scenario!A41&amp;")"&amp;" 
+"&amp;Scenario!C41</f>
         <v>(TS032) 
 Validate the working of 'Top Menu' options' functionality</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>175</v>
+        <v>240</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>179</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -6889,28 +6937,28 @@
     </row>
     <row r="7" ht="42.75" spans="1:11">
       <c r="A7" s="12" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B7" s="13" t="str">
-        <f>"("&amp;Scenario!A38&amp;")"&amp;" 
-"&amp;Scenario!C38</f>
+        <f>"("&amp;Scenario!A41&amp;")"&amp;" 
+"&amp;Scenario!C41</f>
         <v>(TS032) 
 Validate the working of 'Top Menu' options' functionality</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>242</v>
+        <v>245</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>246</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -6973,8 +7021,8 @@
     <col min="4" max="4" width="38.3833333333333" customWidth="1"/>
     <col min="5" max="5" width="53.025" style="3" customWidth="1"/>
     <col min="6" max="6" width="24.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="72.85" style="18" customWidth="1"/>
-    <col min="8" max="8" width="19.2916666666667" style="29" customWidth="1"/>
+    <col min="7" max="7" width="72.85" style="17" customWidth="1"/>
+    <col min="8" max="8" width="19.2916666666667" style="28" customWidth="1"/>
     <col min="9" max="9" width="7.75" customWidth="1"/>
     <col min="10" max="10" width="7.125" customWidth="1"/>
     <col min="11" max="11" width="41.125" customWidth="1"/>
@@ -6982,53 +7030,53 @@
   <sheetData>
     <row r="1" ht="15" spans="1:11">
       <c r="A1" s="10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F1" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" ht="18" spans="1:11">
+      <c r="A2" s="29" t="s">
         <v>97</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" ht="18" spans="1:11">
-      <c r="A2" s="30" t="s">
-        <v>93</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" s="12"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="21"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="20"/>
       <c r="H2" s="14"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12"/>
@@ -7036,25 +7084,25 @@
     </row>
     <row r="3" ht="114" spans="1:11">
       <c r="A3" s="12" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>249</v>
-      </c>
-      <c r="E3" s="33" t="s">
-        <v>250</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="G3" s="22" t="s">
         <v>251</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>252</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>255</v>
       </c>
       <c r="H3" s="14"/>
       <c r="I3" s="12"/>
@@ -7063,25 +7111,25 @@
     </row>
     <row r="4" ht="42.75" spans="1:11">
       <c r="A4" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="C4" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="D4" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="D4" s="33" t="s">
-        <v>249</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>254</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>255</v>
+      <c r="E4" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>259</v>
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="12"/>
@@ -7090,25 +7138,25 @@
     </row>
     <row r="5" ht="42.75" spans="1:11">
       <c r="A5" s="12" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>257</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>258</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>259</v>
+        <v>251</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>261</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>263</v>
       </c>
       <c r="H5" s="14"/>
       <c r="I5" s="12"/>
@@ -7117,25 +7165,25 @@
     </row>
     <row r="6" ht="42.75" spans="1:11">
       <c r="A6" s="12" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>261</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>262</v>
-      </c>
-      <c r="F6" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>263</v>
+        <v>251</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>265</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>266</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>267</v>
       </c>
       <c r="H6" s="14"/>
       <c r="I6" s="12"/>
@@ -7144,25 +7192,25 @@
     </row>
     <row r="7" ht="42.75" spans="1:11">
       <c r="A7" s="12" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>266</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>267</v>
+        <v>251</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>271</v>
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="12"/>
@@ -7171,379 +7219,379 @@
     </row>
     <row r="8" ht="42.75" spans="1:11">
       <c r="A8" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>269</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>266</v>
-      </c>
-      <c r="F8" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="G8" s="37" t="s">
+        <v>272</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="33" t="s">
         <v>270</v>
       </c>
-      <c r="H8" s="38"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="38"/>
+      <c r="F8" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="H8" s="37"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="37"/>
     </row>
     <row r="9" ht="42.75" spans="1:11">
       <c r="A9" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>266</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="H9" s="38"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
+        <v>275</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="G9" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="H9" s="37"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
     </row>
     <row r="10" ht="42.75" spans="1:11">
       <c r="A10" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>275</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>276</v>
-      </c>
-      <c r="F10" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="H10" s="38"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="38"/>
+        <v>278</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="G10" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="H10" s="37"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="37"/>
     </row>
     <row r="11" ht="42.75" spans="1:11">
       <c r="A11" s="12" t="s">
-        <v>278</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>279</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="F11" s="40" t="s">
-        <v>281</v>
-      </c>
-      <c r="G11" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="H11" s="38"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="38"/>
+      <c r="B11" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>284</v>
+      </c>
+      <c r="F11" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="G11" s="40" t="s">
+        <v>286</v>
+      </c>
+      <c r="H11" s="37"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="37"/>
     </row>
     <row r="12" ht="57" spans="1:11">
       <c r="A12" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>284</v>
-      </c>
-      <c r="D12" s="36" t="s">
+        <v>287</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>289</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="F12" s="39" t="s">
         <v>285</v>
       </c>
-      <c r="E12" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="F12" s="40" t="s">
-        <v>281</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>287</v>
-      </c>
-      <c r="H12" s="38"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="38"/>
+      <c r="G12" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="H12" s="37"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="37"/>
     </row>
     <row r="13" ht="57" spans="1:11">
       <c r="A13" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C13" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="D13" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="D13" s="36" t="s">
-        <v>285</v>
-      </c>
-      <c r="E13" s="36" t="s">
-        <v>290</v>
-      </c>
-      <c r="F13" s="35" t="s">
-        <v>291</v>
-      </c>
-      <c r="G13" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="H13" s="38"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="38"/>
+      <c r="E13" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>296</v>
+      </c>
+      <c r="H13" s="37"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="37"/>
     </row>
     <row r="14" ht="57" spans="1:11">
       <c r="A14" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>294</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>296</v>
-      </c>
-      <c r="F14" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="G14" s="37" t="s">
         <v>297</v>
       </c>
-      <c r="H14" s="38"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="38"/>
+      <c r="B14" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>299</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>300</v>
+      </c>
+      <c r="F14" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>301</v>
+      </c>
+      <c r="H14" s="37"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="37"/>
     </row>
     <row r="15" ht="42.75" spans="1:11">
       <c r="A15" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>299</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="F15" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="G15" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="H15" s="38"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="38"/>
+        <v>302</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>304</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>305</v>
+      </c>
+      <c r="H15" s="37"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="37"/>
     </row>
     <row r="16" ht="42.75" spans="1:11">
       <c r="A16" s="12" t="s">
-        <v>302</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="D16" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>304</v>
-      </c>
-      <c r="F16" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>305</v>
-      </c>
-      <c r="H16" s="38"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="38"/>
+        <v>306</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="G16" s="36" t="s">
+        <v>309</v>
+      </c>
+      <c r="H16" s="37"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="37"/>
     </row>
     <row r="17" ht="42.75" spans="1:11">
       <c r="A17" s="12" t="s">
-        <v>306</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>307</v>
-      </c>
-      <c r="D17" s="36" t="s">
+        <v>310</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="E17" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="E17" s="34" t="s">
-        <v>304</v>
-      </c>
-      <c r="F17" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="G17" s="41" t="s">
-        <v>309</v>
-      </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="38"/>
+      <c r="F17" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="G17" s="40" t="s">
+        <v>313</v>
+      </c>
+      <c r="H17" s="37"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="37"/>
     </row>
     <row r="18" ht="42.75" spans="1:11">
       <c r="A18" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>311</v>
-      </c>
-      <c r="D18" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="E18" s="36" t="s">
-        <v>312</v>
-      </c>
-      <c r="F18" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="H18" s="38"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="38"/>
-    </row>
-    <row r="19" s="29" customFormat="1" ht="42.75" spans="1:11">
+        <v>314</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>316</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="G18" s="36" t="s">
+        <v>317</v>
+      </c>
+      <c r="H18" s="37"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="37"/>
+    </row>
+    <row r="19" s="28" customFormat="1" ht="42.75" spans="1:11">
       <c r="A19" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C19" s="34" t="s">
-        <v>315</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>316</v>
-      </c>
-      <c r="F19" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>317</v>
-      </c>
-      <c r="H19" s="38"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39"/>
-      <c r="K19" s="38"/>
-    </row>
-    <row r="20" s="29" customFormat="1" ht="42.75" spans="1:11">
+        <v>318</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="G19" s="36" t="s">
+        <v>321</v>
+      </c>
+      <c r="H19" s="37"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="37"/>
+    </row>
+    <row r="20" s="28" customFormat="1" ht="42.75" spans="1:11">
       <c r="A20" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>319</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>320</v>
-      </c>
-      <c r="F20" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="G20" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="38"/>
+      <c r="B20" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>323</v>
+      </c>
+      <c r="D20" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>326</v>
+      </c>
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
     </row>
     <row r="21" customFormat="1" ht="71.25" spans="1:11">
       <c r="A21" s="12" t="s">
-        <v>323</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C21" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>328</v>
+      </c>
+      <c r="D21" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="E21" s="35" t="s">
         <v>324</v>
       </c>
-      <c r="D21" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>320</v>
-      </c>
-      <c r="F21" s="35" t="s">
-        <v>325</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>326</v>
+      <c r="F21" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>330</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
@@ -7667,116 +7715,116 @@
   <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" style="26" customWidth="1"/>
-    <col min="2" max="2" width="25.875" style="27" customWidth="1"/>
-    <col min="3" max="3" width="32.625" style="26" customWidth="1"/>
-    <col min="4" max="4" width="30.875" style="26" customWidth="1"/>
-    <col min="5" max="5" width="42.35" style="26" customWidth="1"/>
-    <col min="6" max="6" width="15.2916666666667" style="26" customWidth="1"/>
-    <col min="7" max="7" width="86.6" style="26" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="26" customWidth="1"/>
-    <col min="9" max="9" width="7.75" style="26" customWidth="1"/>
-    <col min="10" max="10" width="7.125" style="26" customWidth="1"/>
-    <col min="11" max="11" width="10.875" style="26" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="26"/>
+    <col min="1" max="1" width="13.125" style="25" customWidth="1"/>
+    <col min="2" max="2" width="25.875" style="26" customWidth="1"/>
+    <col min="3" max="3" width="32.625" style="25" customWidth="1"/>
+    <col min="4" max="4" width="30.875" style="25" customWidth="1"/>
+    <col min="5" max="5" width="42.35" style="25" customWidth="1"/>
+    <col min="6" max="6" width="15.2916666666667" style="25" customWidth="1"/>
+    <col min="7" max="7" width="86.6" style="25" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="25" customWidth="1"/>
+    <col min="9" max="9" width="7.75" style="25" customWidth="1"/>
+    <col min="10" max="10" width="7.125" style="25" customWidth="1"/>
+    <col min="11" max="11" width="10.875" style="25" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" s="26" customFormat="1" ht="15" spans="1:11">
+    <row r="1" s="25" customFormat="1" ht="15" spans="1:11">
       <c r="A1" s="10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F1" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" s="25" customFormat="1" spans="1:11">
+      <c r="A2" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" s="26" customFormat="1" spans="1:11">
-      <c r="A2" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="B2" s="21"/>
+      <c r="B2" s="20"/>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-    </row>
-    <row r="3" s="26" customFormat="1" ht="128.25" spans="1:11">
+        <v>13</v>
+      </c>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+    </row>
+    <row r="3" s="25" customFormat="1" ht="128.25" spans="1:11">
       <c r="A3" s="12" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
       <c r="K3" s="12"/>
     </row>
-    <row r="4" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="4" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A4" s="12" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C4" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>331</v>
-      </c>
       <c r="E4" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F4" s="12" t="str">
         <f>SUBSTITUTE(MID(C4,22,30),"'","")</f>
@@ -7791,21 +7839,21 @@
       <c r="J4" s="12"/>
       <c r="K4" s="12"/>
     </row>
-    <row r="5" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="5" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A5" s="12" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F5" s="12" t="str">
         <f t="shared" ref="F5:F18" si="0">SUBSTITUTE(MID(C5,22,30),"'","")</f>
@@ -7820,21 +7868,21 @@
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
     </row>
-    <row r="6" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="6" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A6" s="12" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>340</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>336</v>
       </c>
       <c r="F6" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7849,21 +7897,21 @@
       <c r="J6" s="12"/>
       <c r="K6" s="12"/>
     </row>
-    <row r="7" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="7" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A7" s="12" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F7" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7878,21 +7926,21 @@
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
     </row>
-    <row r="8" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="8" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A8" s="12" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F8" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7907,21 +7955,21 @@
       <c r="J8" s="12"/>
       <c r="K8" s="12"/>
     </row>
-    <row r="9" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="9" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A9" s="12" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F9" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7936,21 +7984,21 @@
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="10" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A10" s="12" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F10" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7965,21 +8013,21 @@
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="11" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A11" s="12" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F11" s="12" t="str">
         <f t="shared" si="0"/>
@@ -7994,21 +8042,21 @@
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
     </row>
-    <row r="12" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="12" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A12" s="12" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F12" s="12" t="str">
         <f t="shared" si="0"/>
@@ -8023,21 +8071,21 @@
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="13" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A13" s="12" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F13" s="12" t="str">
         <f t="shared" si="0"/>
@@ -8052,21 +8100,21 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="14" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A14" s="12" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F14" s="12" t="str">
         <f t="shared" si="0"/>
@@ -8081,21 +8129,21 @@
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="15" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A15" s="12" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F15" s="12" t="str">
         <f t="shared" si="0"/>
@@ -8110,21 +8158,21 @@
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
     </row>
-    <row r="16" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="16" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A16" s="12" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F16" s="12" t="str">
         <f t="shared" si="0"/>
@@ -8139,21 +8187,21 @@
       <c r="J16" s="12"/>
       <c r="K16" s="12"/>
     </row>
-    <row r="17" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="17" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A17" s="12" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F17" s="12" t="str">
         <f t="shared" si="0"/>
@@ -8168,21 +8216,21 @@
       <c r="J17" s="12"/>
       <c r="K17" s="12"/>
     </row>
-    <row r="18" s="26" customFormat="1" ht="42.75" spans="1:11">
+    <row r="18" s="25" customFormat="1" ht="42.75" spans="1:11">
       <c r="A18" s="12" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F18" s="12" t="str">
         <f t="shared" si="0"/>
@@ -8198,58 +8246,58 @@
       <c r="K18" s="12"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="B19" s="28"/>
+      <c r="B19" s="27"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="B20" s="28"/>
+      <c r="B20" s="27"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="B21" s="28"/>
+      <c r="B21" s="27"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="B22" s="28"/>
+      <c r="B22" s="27"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="B23" s="28"/>
+      <c r="B23" s="27"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="B24" s="28"/>
+      <c r="B24" s="27"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="B25" s="28"/>
+      <c r="B25" s="27"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="B26" s="28"/>
+      <c r="B26" s="27"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="B27" s="28"/>
+      <c r="B27" s="27"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="B28" s="28"/>
+      <c r="B28" s="27"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="B29" s="28"/>
+      <c r="B29" s="27"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="B30" s="28"/>
+      <c r="B30" s="27"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="B31" s="28"/>
+      <c r="B31" s="27"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="B32" s="28"/>
+      <c r="B32" s="27"/>
     </row>
     <row r="33" spans="2:2">
-      <c r="B33" s="28"/>
+      <c r="B33" s="27"/>
     </row>
     <row r="34" spans="2:2">
-      <c r="B34" s="28"/>
+      <c r="B34" s="27"/>
     </row>
     <row r="35" spans="2:2">
-      <c r="B35" s="28"/>
+      <c r="B35" s="27"/>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" s="28"/>
+      <c r="B36" s="27"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -8272,8 +8320,8 @@
     <col min="2" max="2" width="28.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="72.125" customWidth="1"/>
     <col min="4" max="4" width="38.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="61.625" style="17" customWidth="1"/>
-    <col min="6" max="6" width="28.75" style="18" customWidth="1"/>
+    <col min="5" max="5" width="61.625" style="16" customWidth="1"/>
+    <col min="6" max="6" width="28.75" style="17" customWidth="1"/>
     <col min="7" max="7" width="64.75" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
     <col min="9" max="9" width="7.75" customWidth="1"/>
@@ -8283,74 +8331,74 @@
   <sheetData>
     <row r="1" ht="15" spans="1:11">
       <c r="A1" s="10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F1" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" ht="18" spans="1:11">
+      <c r="A2" s="18" t="s">
         <v>97</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" ht="18" spans="1:11">
-      <c r="A2" s="19" t="s">
-        <v>93</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2"/>
       <c r="F2"/>
     </row>
     <row r="3" ht="57" spans="1:11">
       <c r="A3" s="12" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>378</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>380</v>
+        <v>382</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
@@ -8359,25 +8407,25 @@
     </row>
     <row r="4" ht="57" spans="1:11">
       <c r="A4" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>378</v>
-      </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="F4" s="20" t="s">
         <v>384</v>
       </c>
-      <c r="F4" s="21" t="s">
-        <v>380</v>
-      </c>
       <c r="G4" s="14" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
@@ -8386,25 +8434,25 @@
     </row>
     <row r="5" ht="57" spans="1:11">
       <c r="A5" s="12" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>388</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>380</v>
+        <v>392</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
@@ -8413,25 +8461,25 @@
     </row>
     <row r="6" ht="57" spans="1:11">
       <c r="A6" s="12" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>378</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>380</v>
+        <v>382</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -8440,25 +8488,25 @@
     </row>
     <row r="7" ht="57" spans="1:11">
       <c r="A7" s="12" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>397</v>
+        <v>400</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>401</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -8467,25 +8515,25 @@
     </row>
     <row r="8" ht="57" spans="1:11">
       <c r="A8" s="12" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>378</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>396</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>401</v>
+      <c r="F8" s="21" t="s">
+        <v>405</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
@@ -8494,25 +8542,25 @@
     </row>
     <row r="9" ht="57" spans="1:11">
       <c r="A9" s="12" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>405</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>406</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>380</v>
+        <v>409</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -8521,25 +8569,25 @@
     </row>
     <row r="10" ht="57" spans="1:11">
       <c r="A10" s="12" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D10" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>410</v>
       </c>
-      <c r="E10" s="20" t="s">
-        <v>406</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>380</v>
+      <c r="F10" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
@@ -8548,25 +8596,25 @@
     </row>
     <row r="11" ht="57" spans="1:11">
       <c r="A11" s="12" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>380</v>
+        <v>418</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
@@ -8575,25 +8623,25 @@
     </row>
     <row r="12" ht="57" spans="1:11">
       <c r="A12" s="12" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>418</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>380</v>
+        <v>422</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
@@ -8602,25 +8650,25 @@
     </row>
     <row r="13" ht="57" spans="1:11">
       <c r="A13" s="12" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>422</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>380</v>
+        <v>426</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
@@ -8629,25 +8677,25 @@
     </row>
     <row r="14" ht="57" spans="1:11">
       <c r="A14" s="12" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>380</v>
+        <v>430</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
@@ -8656,25 +8704,25 @@
     </row>
     <row r="15" ht="57" spans="1:11">
       <c r="A15" s="12" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>378</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>430</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>380</v>
+        <v>382</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
@@ -8683,25 +8731,25 @@
     </row>
     <row r="16" ht="57" spans="1:11">
       <c r="A16" s="12" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F16" s="62" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
@@ -8710,25 +8758,25 @@
     </row>
     <row r="17" ht="57" spans="1:11">
       <c r="A17" s="12" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>380</v>
+        <v>443</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
@@ -8737,25 +8785,25 @@
     </row>
     <row r="18" ht="57" spans="1:11">
       <c r="A18" s="12" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>444</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>380</v>
+        <v>448</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
@@ -8764,25 +8812,25 @@
     </row>
     <row r="19" ht="57" spans="1:11">
       <c r="A19" s="12" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C19" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>443</v>
-      </c>
       <c r="E19" s="12" t="s">
-        <v>448</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>380</v>
+        <v>452</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
@@ -8791,25 +8839,25 @@
     </row>
     <row r="20" ht="57" spans="1:11">
       <c r="A20" s="12" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
@@ -8818,25 +8866,25 @@
     </row>
     <row r="21" ht="57" spans="1:11">
       <c r="A21" s="12" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
@@ -8845,25 +8893,25 @@
     </row>
     <row r="22" ht="57" spans="1:11">
       <c r="A22" s="12" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>462</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>380</v>
+        <v>466</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
@@ -8872,25 +8920,25 @@
     </row>
     <row r="23" ht="57" spans="1:11">
       <c r="A23" s="12" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="12"/>
@@ -8899,25 +8947,25 @@
     </row>
     <row r="24" ht="57" spans="1:11">
       <c r="A24" s="12" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>471</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>380</v>
+        <v>475</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
@@ -8926,25 +8974,25 @@
     </row>
     <row r="25" ht="57" spans="1:11">
       <c r="A25" s="12" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
@@ -8953,25 +9001,25 @@
     </row>
     <row r="26" ht="57" spans="1:11">
       <c r="A26" s="12" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>380</v>
+        <v>484</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
@@ -8980,25 +9028,25 @@
     </row>
     <row r="27" ht="57" spans="1:11">
       <c r="A27" s="12" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
@@ -9007,25 +9055,25 @@
     </row>
     <row r="28" ht="57" spans="1:11">
       <c r="A28" s="12" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="C28" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="E28" s="14" t="s">
         <v>488</v>
       </c>
-      <c r="D28" s="14" t="s">
-        <v>443</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>484</v>
-      </c>
       <c r="F28" s="12" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
@@ -9033,49 +9081,49 @@
       <c r="K28" s="12"/>
     </row>
     <row r="29" ht="57" spans="1:11">
-      <c r="A29" s="23" t="s">
-        <v>491</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>376</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>492</v>
+      <c r="A29" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>496</v>
       </c>
       <c r="D29" s="15"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23" t="s">
-        <v>493</v>
-      </c>
-      <c r="K29" s="23" t="s">
-        <v>494</v>
+      <c r="E29" s="22"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="K29" s="22" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="30" ht="57" spans="1:11">
       <c r="A30" s="12" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>462</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>380</v>
+        <v>466</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>384</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="12"/>
@@ -9084,25 +9132,25 @@
     </row>
     <row r="31" ht="57" spans="1:11">
       <c r="A31" s="12" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
@@ -9111,25 +9159,25 @@
     </row>
     <row r="32" ht="57" spans="1:11">
       <c r="A32" s="12" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="12"/>
